--- a/scripts/restaurant_variables.xlsx
+++ b/scripts/restaurant_variables.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{0F366A8D-A54C-4401-A490-1D25C47DCBF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="19420" tabRatio="851" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="19420" tabRatio="851" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tables_selection" sheetId="11" r:id="rId1"/>
@@ -24,7 +24,6 @@
     <definedName name="DatiEsterni_3" localSheetId="0" hidden="1">tables_selection!$B$1:$G$11</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -713,57 +712,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="21">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="none">
@@ -877,13 +843,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <top style="thin">
           <color theme="9" tint="0.39997558519241921"/>
         </top>
@@ -893,7 +852,43 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -921,6 +916,9 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
@@ -981,10 +979,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{7D1585E5-EB18-4555-BFB4-AB049789BB50}" name="tables_selection" displayName="tables_selection" ref="A1:J11" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:J11" xr:uid="{7D1585E5-EB18-4555-BFB4-AB049789BB50}"/>
   <tableColumns count="10">
-    <tableColumn id="10" xr3:uid="{1ADF8E6C-C756-4DB0-AF29-730090E9A389}" uniqueName="10" name="scenario" queryTableFieldId="10" dataDxfId="20"/>
-    <tableColumn id="1" xr3:uid="{9DF6AF6D-4327-4E8B-A17C-4CE32200A2CC}" uniqueName="1" name="start_timestamp" queryTableFieldId="1" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{DB186560-5030-4DB1-A6BD-A74C44B2F90A}" uniqueName="2" name="end_timestamp" queryTableFieldId="2" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{6CE09762-A225-468B-8C15-326E109C4C41}" uniqueName="3" name="period" queryTableFieldId="3" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{1ADF8E6C-C756-4DB0-AF29-730090E9A389}" uniqueName="10" name="scenario" queryTableFieldId="10" dataDxfId="19"/>
+    <tableColumn id="1" xr3:uid="{9DF6AF6D-4327-4E8B-A17C-4CE32200A2CC}" uniqueName="1" name="start_timestamp" queryTableFieldId="1" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{DB186560-5030-4DB1-A6BD-A74C44B2F90A}" uniqueName="2" name="end_timestamp" queryTableFieldId="2" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{6CE09762-A225-468B-8C15-326E109C4C41}" uniqueName="3" name="period" queryTableFieldId="3" dataDxfId="16"/>
     <tableColumn id="4" xr3:uid="{90771DE1-93AE-42DD-88DE-8292168CC27F}" uniqueName="4" name="bar_on" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{2D6F5E1B-E207-46D0-A78B-EA6977317860}" uniqueName="5" name="inside_on" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{5AFB94CB-8BB6-4AE5-B6B3-D1BD6C86A1FB}" uniqueName="6" name="outside_on" queryTableFieldId="6"/>
@@ -1000,12 +998,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{54D2211C-274A-47E4-BDD0-4C0951D8DD68}" name="employees_schedule" displayName="employees_schedule" ref="A1:H71" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:H71" xr:uid="{54D2211C-274A-47E4-BDD0-4C0951D8DD68}"/>
   <tableColumns count="8">
-    <tableColumn id="15" xr3:uid="{C7ED7AB4-5A31-4D81-834A-B6E64F7023C8}" uniqueName="15" name="scenario" queryTableFieldId="9" dataDxfId="16"/>
-    <tableColumn id="1" xr3:uid="{1826F0BC-F6D0-44C5-8A93-C7D99BD8CB8B}" uniqueName="1" name="start_timestamp" queryTableFieldId="1" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{75D23335-1496-4011-81D1-D6034B72FF11}" uniqueName="2" name="end_timestamp" queryTableFieldId="2" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{92C90E84-B1B0-4866-9DDC-2A2B72F890FA}" uniqueName="4" name="weekday" queryTableFieldId="4" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{954429F6-A3DE-46A7-885B-49BC6CAF5664}" uniqueName="5" name="hour" queryTableFieldId="5" dataDxfId="12"/>
-    <tableColumn id="6" xr3:uid="{D0D42E6A-14B4-4741-A3F6-DD9143A88038}" uniqueName="6" name="period" queryTableFieldId="6" dataDxfId="11"/>
+    <tableColumn id="15" xr3:uid="{C7ED7AB4-5A31-4D81-834A-B6E64F7023C8}" uniqueName="15" name="scenario" queryTableFieldId="9" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{1826F0BC-F6D0-44C5-8A93-C7D99BD8CB8B}" uniqueName="1" name="start_timestamp" queryTableFieldId="1" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{75D23335-1496-4011-81D1-D6034B72FF11}" uniqueName="2" name="end_timestamp" queryTableFieldId="2" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{92C90E84-B1B0-4866-9DDC-2A2B72F890FA}" uniqueName="4" name="weekday" queryTableFieldId="4" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{954429F6-A3DE-46A7-885B-49BC6CAF5664}" uniqueName="5" name="hour" queryTableFieldId="5" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{D0D42E6A-14B4-4741-A3F6-DD9143A88038}" uniqueName="6" name="period" queryTableFieldId="6" dataDxfId="10"/>
     <tableColumn id="7" xr3:uid="{DC0D317B-9907-4E39-BD04-56F982B6DFC4}" uniqueName="7" name="waiters" queryTableFieldId="7"/>
     <tableColumn id="8" xr3:uid="{5822B03F-BA67-4CAF-8288-1B9FA740A60F}" uniqueName="8" name="cooks" queryTableFieldId="8"/>
   </tableColumns>
@@ -1014,14 +1012,14 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D544813D-DF99-41C8-AE8A-38BE1FAF9E94}" name="Tabella3" displayName="Tabella3" ref="A1:E11" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" headerRowBorderDxfId="8" tableBorderDxfId="9" totalsRowBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D544813D-DF99-41C8-AE8A-38BE1FAF9E94}" name="Tabella3" displayName="Tabella3" ref="A1:E11" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5">
   <autoFilter ref="A1:E11" xr:uid="{D544813D-DF99-41C8-AE8A-38BE1FAF9E94}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{5F6DE45A-D069-49C3-A965-E57C526C9F10}" name="scenario" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{4D8F0B29-A4FF-499D-9A3B-DCD79E56771F}" name="start_timestamp" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{73FD92A6-7E32-4F59-A6D2-E391CC1529B2}" name="end_timestamp" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{E9B6B43D-80B9-448F-8CE5-DB0428CE9192}" name="period" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{FA561D75-B96F-4DC4-B290-98BCE5AF9EBB}" name="time_avg" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{5F6DE45A-D069-49C3-A965-E57C526C9F10}" name="scenario" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{4D8F0B29-A4FF-499D-9A3B-DCD79E56771F}" name="start_timestamp" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{73FD92A6-7E32-4F59-A6D2-E391CC1529B2}" name="end_timestamp" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{E9B6B43D-80B9-448F-8CE5-DB0428CE9192}" name="period" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{FA561D75-B96F-4DC4-B290-98BCE5AF9EBB}" name="time_avg" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1034,7 +1032,7 @@
     <tableColumn id="1" xr3:uid="{C0C152CA-AC82-4A38-9515-01F93B55CD35}" name="scenario"/>
     <tableColumn id="2" xr3:uid="{A9274257-0F1F-4EC5-AEAD-2D02ED20F27D}" name="start_timestamp"/>
     <tableColumn id="3" xr3:uid="{8EBF5A3E-33DA-4E63-85B2-6A750FD2B59E}" name="end_timestamp"/>
-    <tableColumn id="4" xr3:uid="{1B570803-0CC6-4039-83E4-466D06E97DE8}" name="arrival_rate" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{1B570803-0CC6-4039-83E4-466D06E97DE8}" name="arrival_rate" dataDxfId="20"/>
     <tableColumn id="5" xr3:uid="{2330BE18-97F9-494B-A0D2-BC6CD4BE5D26}" name="weekday"/>
     <tableColumn id="6" xr3:uid="{511C9B76-5714-4C6E-B45F-24A76465D0A2}" name="hour"/>
     <tableColumn id="7" xr3:uid="{DDB83C9A-5515-4339-958C-0504A36D7FBA}" name="avg_group_size"/>
@@ -3561,189 +3559,189 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
+      <c r="C1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="5">
-        <v>1</v>
-      </c>
-      <c r="B2" s="6">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5">
         <v>25573.291666666668</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="6">
         <v>25573.458333333332</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="4">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="5">
-        <v>1</v>
-      </c>
-      <c r="B3" s="6">
+      <c r="A3" s="4">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5">
         <v>25573.458333333332</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="6">
         <v>25573.625</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="4">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="5">
-        <v>1</v>
-      </c>
-      <c r="B4" s="6">
+      <c r="A4" s="4">
+        <v>1</v>
+      </c>
+      <c r="B4" s="5">
         <v>25573.625</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="6">
         <v>25573.791666666668</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="4">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="5">
-        <v>1</v>
-      </c>
-      <c r="B5" s="6">
+      <c r="A5" s="4">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5">
         <v>25573.791666666668</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="6">
         <v>25573.958333333332</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="4">
         <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="5">
-        <v>1</v>
-      </c>
-      <c r="B6" s="6">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="5">
         <v>25573.958333333332</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="6">
         <v>25574.291666666668</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="5">
-        <v>2</v>
-      </c>
-      <c r="B7" s="6">
+      <c r="A7" s="4">
+        <v>2</v>
+      </c>
+      <c r="B7" s="5">
         <v>25573.291666666668</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="6">
         <v>25573.458333333332</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="5">
-        <v>2</v>
-      </c>
-      <c r="B8" s="6">
+      <c r="A8" s="4">
+        <v>2</v>
+      </c>
+      <c r="B8" s="5">
         <v>25573.458333333332</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="6">
         <v>25573.625</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="5">
-        <v>2</v>
-      </c>
-      <c r="B9" s="6">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="5">
         <v>25573.625</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="6">
         <v>25573.791666666668</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="5">
-        <v>2</v>
-      </c>
-      <c r="B10" s="6">
+      <c r="A10" s="4">
+        <v>2</v>
+      </c>
+      <c r="B10" s="5">
         <v>25573.791666666668</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="6">
         <v>25573.958333333332</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="10">
-        <v>2</v>
-      </c>
-      <c r="B11" s="11">
+      <c r="A11" s="9">
+        <v>2</v>
+      </c>
+      <c r="B11" s="10">
         <v>25573.958333333332</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="11">
         <v>25574.291666666668</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="9">
         <v>100</v>
       </c>
     </row>
@@ -3868,7 +3866,7 @@
       <c r="C5" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5">
         <v>8</v>
       </c>
       <c r="E5" t="s">
@@ -3891,7 +3889,7 @@
       <c r="C6" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6">
         <v>6</v>
       </c>
       <c r="E6" t="s">
@@ -3914,7 +3912,7 @@
       <c r="C7" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7">
         <v>18</v>
       </c>
       <c r="E7" t="s">
@@ -3937,7 +3935,7 @@
       <c r="C8" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8">
         <v>28</v>
       </c>
       <c r="E8" t="s">
@@ -3960,7 +3958,7 @@
       <c r="C9" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9">
         <v>16</v>
       </c>
       <c r="E9" t="s">
@@ -3983,7 +3981,7 @@
       <c r="C10" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10">
         <v>4</v>
       </c>
       <c r="E10" t="s">
@@ -4006,7 +4004,7 @@
       <c r="C11" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11">
         <v>3</v>
       </c>
       <c r="E11" t="s">
@@ -4029,7 +4027,7 @@
       <c r="C12" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12">
         <v>5</v>
       </c>
       <c r="E12" t="s">
@@ -4052,7 +4050,7 @@
       <c r="C13" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13">
         <v>12</v>
       </c>
       <c r="E13" t="s">
@@ -4075,7 +4073,7 @@
       <c r="C14" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14">
         <v>18</v>
       </c>
       <c r="E14" t="s">
@@ -4098,7 +4096,7 @@
       <c r="C15" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15">
         <v>20</v>
       </c>
       <c r="E15" t="s">
@@ -4121,7 +4119,7 @@
       <c r="C16" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16">
         <v>12</v>
       </c>
       <c r="E16" t="s">
@@ -4144,7 +4142,7 @@
       <c r="C17" t="s">
         <v>44</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17">
         <v>5</v>
       </c>
       <c r="E17" t="s">
@@ -4167,7 +4165,7 @@
       <c r="C18" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18">
         <v>0</v>
       </c>
       <c r="E18" t="s">
@@ -4190,7 +4188,7 @@
       <c r="C19" t="s">
         <v>48</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19">
         <v>5</v>
       </c>
       <c r="E19" t="s">
@@ -4213,7 +4211,7 @@
       <c r="C20" t="s">
         <v>49</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20">
         <v>14</v>
       </c>
       <c r="E20" t="s">
@@ -4236,7 +4234,7 @@
       <c r="C21" t="s">
         <v>50</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21">
         <v>15</v>
       </c>
       <c r="E21" t="s">
@@ -4259,7 +4257,7 @@
       <c r="C22" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22">
         <v>8</v>
       </c>
       <c r="E22" t="s">
@@ -4282,7 +4280,7 @@
       <c r="C23" t="s">
         <v>52</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23">
         <v>6</v>
       </c>
       <c r="E23" t="s">
@@ -4305,7 +4303,7 @@
       <c r="C24" t="s">
         <v>53</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24">
         <v>19</v>
       </c>
       <c r="E24" t="s">
@@ -4328,7 +4326,7 @@
       <c r="C25" t="s">
         <v>54</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25">
         <v>29</v>
       </c>
       <c r="E25" t="s">
@@ -4351,7 +4349,7 @@
       <c r="C26" t="s">
         <v>55</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26">
         <v>16</v>
       </c>
       <c r="E26" t="s">
@@ -4374,7 +4372,7 @@
       <c r="C27" t="s">
         <v>56</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27">
         <v>4</v>
       </c>
       <c r="E27" t="s">
@@ -4397,7 +4395,7 @@
       <c r="C28" t="s">
         <v>57</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28">
         <v>3</v>
       </c>
       <c r="E28" t="s">
@@ -4420,7 +4418,7 @@
       <c r="C29" t="s">
         <v>58</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29">
         <v>6</v>
       </c>
       <c r="E29" t="s">
@@ -4443,7 +4441,7 @@
       <c r="C30" t="s">
         <v>59</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D30">
         <v>12</v>
       </c>
       <c r="E30" t="s">
@@ -4466,7 +4464,7 @@
       <c r="C31" t="s">
         <v>60</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31">
         <v>19</v>
       </c>
       <c r="E31" t="s">
@@ -4489,7 +4487,7 @@
       <c r="C32" t="s">
         <v>61</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D32">
         <v>25</v>
       </c>
       <c r="E32" t="s">
@@ -4512,7 +4510,7 @@
       <c r="C33" t="s">
         <v>62</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D33">
         <v>12</v>
       </c>
       <c r="E33" t="s">
@@ -4535,7 +4533,7 @@
       <c r="C34" t="s">
         <v>63</v>
       </c>
-      <c r="D34" s="4">
+      <c r="D34">
         <v>5</v>
       </c>
       <c r="E34" t="s">
@@ -4558,7 +4556,7 @@
       <c r="C35" t="s">
         <v>64</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D35">
         <v>0</v>
       </c>
       <c r="E35" t="s">
@@ -4581,7 +4579,7 @@
       <c r="C36" t="s">
         <v>65</v>
       </c>
-      <c r="D36" s="4">
+      <c r="D36">
         <v>5</v>
       </c>
       <c r="E36" t="s">
@@ -4604,7 +4602,7 @@
       <c r="C37" t="s">
         <v>66</v>
       </c>
-      <c r="D37" s="4">
+      <c r="D37">
         <v>13</v>
       </c>
       <c r="E37" t="s">
@@ -4627,7 +4625,7 @@
       <c r="C38" t="s">
         <v>67</v>
       </c>
-      <c r="D38" s="4">
+      <c r="D38">
         <v>15</v>
       </c>
       <c r="E38" t="s">
@@ -4650,7 +4648,7 @@
       <c r="C39" t="s">
         <v>68</v>
       </c>
-      <c r="D39" s="4">
+      <c r="D39">
         <v>8</v>
       </c>
       <c r="E39" t="s">
@@ -4673,7 +4671,7 @@
       <c r="C40" t="s">
         <v>69</v>
       </c>
-      <c r="D40" s="4">
+      <c r="D40">
         <v>6</v>
       </c>
       <c r="E40" t="s">
@@ -4696,7 +4694,7 @@
       <c r="C41" t="s">
         <v>70</v>
       </c>
-      <c r="D41" s="4">
+      <c r="D41">
         <v>20</v>
       </c>
       <c r="E41" t="s">
@@ -4719,7 +4717,7 @@
       <c r="C42" t="s">
         <v>71</v>
       </c>
-      <c r="D42" s="4">
+      <c r="D42">
         <v>29</v>
       </c>
       <c r="E42" t="s">
@@ -4742,7 +4740,7 @@
       <c r="C43" t="s">
         <v>72</v>
       </c>
-      <c r="D43" s="4">
+      <c r="D43">
         <v>16</v>
       </c>
       <c r="E43" t="s">
@@ -4765,7 +4763,7 @@
       <c r="C44" t="s">
         <v>73</v>
       </c>
-      <c r="D44" s="4">
+      <c r="D44">
         <v>4</v>
       </c>
       <c r="E44" t="s">
@@ -4788,7 +4786,7 @@
       <c r="C45" t="s">
         <v>74</v>
       </c>
-      <c r="D45" s="4">
+      <c r="D45">
         <v>3</v>
       </c>
       <c r="E45" t="s">
@@ -4811,7 +4809,7 @@
       <c r="C46" t="s">
         <v>75</v>
       </c>
-      <c r="D46" s="4">
+      <c r="D46">
         <v>6</v>
       </c>
       <c r="E46" t="s">
@@ -4834,7 +4832,7 @@
       <c r="C47" t="s">
         <v>76</v>
       </c>
-      <c r="D47" s="4">
+      <c r="D47">
         <v>13</v>
       </c>
       <c r="E47" t="s">
@@ -4857,7 +4855,7 @@
       <c r="C48" t="s">
         <v>77</v>
       </c>
-      <c r="D48" s="4">
+      <c r="D48">
         <v>19</v>
       </c>
       <c r="E48" t="s">
@@ -4880,7 +4878,7 @@
       <c r="C49" t="s">
         <v>78</v>
       </c>
-      <c r="D49" s="4">
+      <c r="D49">
         <v>21</v>
       </c>
       <c r="E49" t="s">
@@ -4903,7 +4901,7 @@
       <c r="C50" t="s">
         <v>79</v>
       </c>
-      <c r="D50" s="4">
+      <c r="D50">
         <v>13</v>
       </c>
       <c r="E50" t="s">
@@ -4926,7 +4924,7 @@
       <c r="C51" t="s">
         <v>80</v>
       </c>
-      <c r="D51" s="4">
+      <c r="D51">
         <v>6</v>
       </c>
       <c r="E51" t="s">
@@ -4949,7 +4947,7 @@
       <c r="C52" t="s">
         <v>81</v>
       </c>
-      <c r="D52" s="4">
+      <c r="D52">
         <v>0</v>
       </c>
       <c r="E52" t="s">
@@ -4972,7 +4970,7 @@
       <c r="C53" t="s">
         <v>82</v>
       </c>
-      <c r="D53" s="4">
+      <c r="D53">
         <v>6</v>
       </c>
       <c r="E53" t="s">
@@ -4995,7 +4993,7 @@
       <c r="C54" t="s">
         <v>83</v>
       </c>
-      <c r="D54" s="4">
+      <c r="D54">
         <v>14</v>
       </c>
       <c r="E54" t="s">
@@ -5018,7 +5016,7 @@
       <c r="C55" t="s">
         <v>84</v>
       </c>
-      <c r="D55" s="4">
+      <c r="D55">
         <v>16</v>
       </c>
       <c r="E55" t="s">
@@ -5041,7 +5039,7 @@
       <c r="C56" t="s">
         <v>85</v>
       </c>
-      <c r="D56" s="4">
+      <c r="D56">
         <v>9</v>
       </c>
       <c r="E56" t="s">
@@ -5064,7 +5062,7 @@
       <c r="C57" t="s">
         <v>86</v>
       </c>
-      <c r="D57" s="4">
+      <c r="D57">
         <v>7</v>
       </c>
       <c r="E57" t="s">
@@ -5087,7 +5085,7 @@
       <c r="C58" t="s">
         <v>87</v>
       </c>
-      <c r="D58" s="4">
+      <c r="D58">
         <v>20</v>
       </c>
       <c r="E58" t="s">
@@ -5110,7 +5108,7 @@
       <c r="C59" t="s">
         <v>88</v>
       </c>
-      <c r="D59" s="4">
+      <c r="D59">
         <v>30</v>
       </c>
       <c r="E59" t="s">
@@ -5133,7 +5131,7 @@
       <c r="C60" t="s">
         <v>89</v>
       </c>
-      <c r="D60" s="4">
+      <c r="D60">
         <v>17</v>
       </c>
       <c r="E60" t="s">
@@ -5156,7 +5154,7 @@
       <c r="C61" t="s">
         <v>90</v>
       </c>
-      <c r="D61" s="4">
+      <c r="D61">
         <v>5</v>
       </c>
       <c r="E61" t="s">
@@ -5179,7 +5177,7 @@
       <c r="C62" t="s">
         <v>91</v>
       </c>
-      <c r="D62" s="4">
+      <c r="D62">
         <v>4</v>
       </c>
       <c r="E62" t="s">
@@ -5202,7 +5200,7 @@
       <c r="C63" t="s">
         <v>92</v>
       </c>
-      <c r="D63" s="4">
+      <c r="D63">
         <v>7</v>
       </c>
       <c r="E63" t="s">
@@ -5225,7 +5223,7 @@
       <c r="C64" t="s">
         <v>93</v>
       </c>
-      <c r="D64" s="4">
+      <c r="D64">
         <v>15</v>
       </c>
       <c r="E64" t="s">
@@ -5248,7 +5246,7 @@
       <c r="C65" t="s">
         <v>94</v>
       </c>
-      <c r="D65" s="4">
+      <c r="D65">
         <v>20</v>
       </c>
       <c r="E65" t="s">
@@ -5271,7 +5269,7 @@
       <c r="C66" t="s">
         <v>95</v>
       </c>
-      <c r="D66" s="4">
+      <c r="D66">
         <v>22</v>
       </c>
       <c r="E66" t="s">
@@ -5294,7 +5292,7 @@
       <c r="C67" t="s">
         <v>96</v>
       </c>
-      <c r="D67" s="4">
+      <c r="D67">
         <v>15</v>
       </c>
       <c r="E67" t="s">
@@ -5317,7 +5315,7 @@
       <c r="C68" t="s">
         <v>97</v>
       </c>
-      <c r="D68" s="4">
+      <c r="D68">
         <v>7</v>
       </c>
       <c r="E68" t="s">
@@ -5340,7 +5338,7 @@
       <c r="C69" t="s">
         <v>98</v>
       </c>
-      <c r="D69" s="4">
+      <c r="D69">
         <v>0</v>
       </c>
       <c r="E69" t="s">
@@ -5363,7 +5361,7 @@
       <c r="C70" t="s">
         <v>99</v>
       </c>
-      <c r="D70" s="4">
+      <c r="D70">
         <v>6</v>
       </c>
       <c r="E70" t="s">
@@ -5386,7 +5384,7 @@
       <c r="C71" t="s">
         <v>100</v>
       </c>
-      <c r="D71" s="4">
+      <c r="D71">
         <v>15</v>
       </c>
       <c r="E71" t="s">
@@ -5409,7 +5407,7 @@
       <c r="C72" t="s">
         <v>101</v>
       </c>
-      <c r="D72" s="4">
+      <c r="D72">
         <v>17</v>
       </c>
       <c r="E72" t="s">
@@ -5432,7 +5430,7 @@
       <c r="C73" t="s">
         <v>102</v>
       </c>
-      <c r="D73" s="4">
+      <c r="D73">
         <v>10</v>
       </c>
       <c r="E73" t="s">
@@ -5455,7 +5453,7 @@
       <c r="C74" t="s">
         <v>103</v>
       </c>
-      <c r="D74" s="4">
+      <c r="D74">
         <v>9</v>
       </c>
       <c r="E74" t="s">
@@ -5478,7 +5476,7 @@
       <c r="C75" t="s">
         <v>104</v>
       </c>
-      <c r="D75" s="4">
+      <c r="D75">
         <v>22</v>
       </c>
       <c r="E75" t="s">
@@ -5501,7 +5499,7 @@
       <c r="C76" t="s">
         <v>105</v>
       </c>
-      <c r="D76" s="4">
+      <c r="D76">
         <v>32</v>
       </c>
       <c r="E76" t="s">
@@ -5524,7 +5522,7 @@
       <c r="C77" t="s">
         <v>106</v>
       </c>
-      <c r="D77" s="4">
+      <c r="D77">
         <v>20</v>
       </c>
       <c r="E77" t="s">
@@ -5547,7 +5545,7 @@
       <c r="C78" t="s">
         <v>107</v>
       </c>
-      <c r="D78" s="4">
+      <c r="D78">
         <v>6</v>
       </c>
       <c r="E78" t="s">
@@ -5570,7 +5568,7 @@
       <c r="C79" t="s">
         <v>108</v>
       </c>
-      <c r="D79" s="4">
+      <c r="D79">
         <v>7</v>
       </c>
       <c r="E79" t="s">
@@ -5593,7 +5591,7 @@
       <c r="C80" t="s">
         <v>109</v>
       </c>
-      <c r="D80" s="4">
+      <c r="D80">
         <v>12</v>
       </c>
       <c r="E80" t="s">
@@ -5616,7 +5614,7 @@
       <c r="C81" t="s">
         <v>110</v>
       </c>
-      <c r="D81" s="4">
+      <c r="D81">
         <v>18</v>
       </c>
       <c r="E81" t="s">
@@ -5639,7 +5637,7 @@
       <c r="C82" t="s">
         <v>111</v>
       </c>
-      <c r="D82" s="4">
+      <c r="D82">
         <v>26</v>
       </c>
       <c r="E82" t="s">
@@ -5662,7 +5660,7 @@
       <c r="C83" t="s">
         <v>112</v>
       </c>
-      <c r="D83" s="4">
+      <c r="D83">
         <v>28</v>
       </c>
       <c r="E83" t="s">
@@ -5685,7 +5683,7 @@
       <c r="C84" t="s">
         <v>113</v>
       </c>
-      <c r="D84" s="4">
+      <c r="D84">
         <v>22</v>
       </c>
       <c r="E84" t="s">
@@ -5708,7 +5706,7 @@
       <c r="C85" t="s">
         <v>114</v>
       </c>
-      <c r="D85" s="4">
+      <c r="D85">
         <v>12</v>
       </c>
       <c r="E85" t="s">
@@ -5731,7 +5729,7 @@
       <c r="C86" t="s">
         <v>115</v>
       </c>
-      <c r="D86" s="4">
+      <c r="D86">
         <v>0</v>
       </c>
       <c r="E86" t="s">
@@ -5754,7 +5752,7 @@
       <c r="C87" t="s">
         <v>116</v>
       </c>
-      <c r="D87" s="4">
+      <c r="D87">
         <v>3</v>
       </c>
       <c r="E87" t="s">
@@ -5777,7 +5775,7 @@
       <c r="C88" t="s">
         <v>117</v>
       </c>
-      <c r="D88" s="4">
+      <c r="D88">
         <v>6</v>
       </c>
       <c r="E88" t="s">
@@ -5800,7 +5798,7 @@
       <c r="C89" t="s">
         <v>118</v>
       </c>
-      <c r="D89" s="4">
+      <c r="D89">
         <v>16</v>
       </c>
       <c r="E89" t="s">
@@ -5823,7 +5821,7 @@
       <c r="C90" t="s">
         <v>119</v>
       </c>
-      <c r="D90" s="4">
+      <c r="D90">
         <v>24</v>
       </c>
       <c r="E90" t="s">
@@ -5846,7 +5844,7 @@
       <c r="C91" t="s">
         <v>120</v>
       </c>
-      <c r="D91" s="4">
+      <c r="D91">
         <v>26</v>
       </c>
       <c r="E91" t="s">
@@ -5869,7 +5867,7 @@
       <c r="C92" t="s">
         <v>121</v>
       </c>
-      <c r="D92" s="4">
+      <c r="D92">
         <v>24</v>
       </c>
       <c r="E92" t="s">
@@ -5892,7 +5890,7 @@
       <c r="C93" t="s">
         <v>122</v>
       </c>
-      <c r="D93" s="4">
+      <c r="D93">
         <v>28</v>
       </c>
       <c r="E93" t="s">
@@ -5915,7 +5913,7 @@
       <c r="C94" t="s">
         <v>123</v>
       </c>
-      <c r="D94" s="4">
+      <c r="D94">
         <v>24</v>
       </c>
       <c r="E94" t="s">
@@ -5938,7 +5936,7 @@
       <c r="C95" t="s">
         <v>124</v>
       </c>
-      <c r="D95" s="4">
+      <c r="D95">
         <v>12</v>
       </c>
       <c r="E95" t="s">
@@ -5961,7 +5959,7 @@
       <c r="C96" t="s">
         <v>125</v>
       </c>
-      <c r="D96" s="4">
+      <c r="D96">
         <v>10</v>
       </c>
       <c r="E96" t="s">
@@ -5984,7 +5982,7 @@
       <c r="C97" t="s">
         <v>126</v>
       </c>
-      <c r="D97" s="4">
+      <c r="D97">
         <v>14</v>
       </c>
       <c r="E97" t="s">
@@ -6007,7 +6005,7 @@
       <c r="C98" t="s">
         <v>127</v>
       </c>
-      <c r="D98" s="4">
+      <c r="D98">
         <v>22</v>
       </c>
       <c r="E98" t="s">
@@ -6030,7 +6028,7 @@
       <c r="C99" t="s">
         <v>128</v>
       </c>
-      <c r="D99" s="4">
+      <c r="D99">
         <v>30</v>
       </c>
       <c r="E99" t="s">
@@ -6053,7 +6051,7 @@
       <c r="C100" t="s">
         <v>129</v>
       </c>
-      <c r="D100" s="4">
+      <c r="D100">
         <v>32</v>
       </c>
       <c r="E100" t="s">
@@ -6076,7 +6074,7 @@
       <c r="C101" t="s">
         <v>130</v>
       </c>
-      <c r="D101" s="4">
+      <c r="D101">
         <v>26</v>
       </c>
       <c r="E101" t="s">
@@ -6099,7 +6097,7 @@
       <c r="C102" t="s">
         <v>131</v>
       </c>
-      <c r="D102" s="4">
+      <c r="D102">
         <v>16</v>
       </c>
       <c r="E102" t="s">
@@ -6122,7 +6120,7 @@
       <c r="C103" t="s">
         <v>132</v>
       </c>
-      <c r="D103" s="4">
+      <c r="D103">
         <v>0</v>
       </c>
       <c r="E103" t="s">
@@ -6145,7 +6143,7 @@
       <c r="C104" t="s">
         <v>133</v>
       </c>
-      <c r="D104" s="4">
+      <c r="D104">
         <v>3</v>
       </c>
       <c r="E104" t="s">
@@ -6168,7 +6166,7 @@
       <c r="C105" t="s">
         <v>134</v>
       </c>
-      <c r="D105" s="4">
+      <c r="D105">
         <v>5</v>
       </c>
       <c r="E105" t="s">
@@ -6191,7 +6189,7 @@
       <c r="C106" t="s">
         <v>135</v>
       </c>
-      <c r="D106" s="4">
+      <c r="D106">
         <v>14</v>
       </c>
       <c r="E106" t="s">
@@ -6214,7 +6212,7 @@
       <c r="C107" t="s">
         <v>136</v>
       </c>
-      <c r="D107" s="4">
+      <c r="D107">
         <v>20</v>
       </c>
       <c r="E107" t="s">
@@ -6237,7 +6235,7 @@
       <c r="C108" t="s">
         <v>137</v>
       </c>
-      <c r="D108" s="4">
+      <c r="D108">
         <v>22</v>
       </c>
       <c r="E108" t="s">
@@ -6260,7 +6258,7 @@
       <c r="C109" t="s">
         <v>138</v>
       </c>
-      <c r="D109" s="4">
+      <c r="D109">
         <v>26</v>
       </c>
       <c r="E109" t="s">
@@ -6283,7 +6281,7 @@
       <c r="C110" t="s">
         <v>139</v>
       </c>
-      <c r="D110" s="4">
+      <c r="D110">
         <v>28</v>
       </c>
       <c r="E110" t="s">
@@ -6306,7 +6304,7 @@
       <c r="C111" t="s">
         <v>140</v>
       </c>
-      <c r="D111" s="4">
+      <c r="D111">
         <v>24</v>
       </c>
       <c r="E111" t="s">
@@ -6329,7 +6327,7 @@
       <c r="C112" t="s">
         <v>141</v>
       </c>
-      <c r="D112" s="4">
+      <c r="D112">
         <v>14</v>
       </c>
       <c r="E112" t="s">
@@ -6352,7 +6350,7 @@
       <c r="C113" t="s">
         <v>142</v>
       </c>
-      <c r="D113" s="4">
+      <c r="D113">
         <v>10</v>
       </c>
       <c r="E113" t="s">
@@ -6375,7 +6373,7 @@
       <c r="C114" t="s">
         <v>143</v>
       </c>
-      <c r="D114" s="4">
+      <c r="D114">
         <v>10</v>
       </c>
       <c r="E114" t="s">
@@ -6398,7 +6396,7 @@
       <c r="C115" t="s">
         <v>144</v>
       </c>
-      <c r="D115" s="4">
+      <c r="D115">
         <v>18</v>
       </c>
       <c r="E115" t="s">
@@ -6421,7 +6419,7 @@
       <c r="C116" t="s">
         <v>145</v>
       </c>
-      <c r="D116" s="4">
+      <c r="D116">
         <v>22</v>
       </c>
       <c r="E116" t="s">
@@ -6444,7 +6442,7 @@
       <c r="C117" t="s">
         <v>146</v>
       </c>
-      <c r="D117" s="4">
+      <c r="D117">
         <v>24</v>
       </c>
       <c r="E117" t="s">
@@ -6467,7 +6465,7 @@
       <c r="C118" t="s">
         <v>147</v>
       </c>
-      <c r="D118" s="4">
+      <c r="D118">
         <v>18</v>
       </c>
       <c r="E118" t="s">
@@ -6490,7 +6488,7 @@
       <c r="C119" t="s">
         <v>148</v>
       </c>
-      <c r="D119" s="4">
+      <c r="D119">
         <v>10</v>
       </c>
       <c r="E119" t="s">
@@ -6513,7 +6511,7 @@
       <c r="C120" t="s">
         <v>149</v>
       </c>
-      <c r="D120" s="4">
+      <c r="D120">
         <v>0</v>
       </c>
       <c r="E120" t="s">
@@ -6536,7 +6534,7 @@
       <c r="C121" t="s">
         <v>14</v>
       </c>
-      <c r="D121" s="4">
+      <c r="D121">
         <v>5</v>
       </c>
       <c r="E121" t="s">
@@ -6559,7 +6557,7 @@
       <c r="C122" t="s">
         <v>16</v>
       </c>
-      <c r="D122" s="4">
+      <c r="D122">
         <v>12</v>
       </c>
       <c r="E122" t="s">
@@ -6582,7 +6580,7 @@
       <c r="C123" t="s">
         <v>18</v>
       </c>
-      <c r="D123" s="4">
+      <c r="D123">
         <v>14</v>
       </c>
       <c r="E123" t="s">
@@ -6605,7 +6603,7 @@
       <c r="C124" t="s">
         <v>20</v>
       </c>
-      <c r="D124" s="4">
+      <c r="D124">
         <v>8</v>
       </c>
       <c r="E124" t="s">
@@ -6628,7 +6626,7 @@
       <c r="C125" t="s">
         <v>22</v>
       </c>
-      <c r="D125" s="4">
+      <c r="D125">
         <v>6</v>
       </c>
       <c r="E125" t="s">
@@ -6651,7 +6649,7 @@
       <c r="C126" t="s">
         <v>24</v>
       </c>
-      <c r="D126" s="4">
+      <c r="D126">
         <v>18</v>
       </c>
       <c r="E126" t="s">
@@ -6674,7 +6672,7 @@
       <c r="C127" t="s">
         <v>26</v>
       </c>
-      <c r="D127" s="4">
+      <c r="D127">
         <v>28</v>
       </c>
       <c r="E127" t="s">
@@ -6697,7 +6695,7 @@
       <c r="C128" t="s">
         <v>28</v>
       </c>
-      <c r="D128" s="4">
+      <c r="D128">
         <v>16</v>
       </c>
       <c r="E128" t="s">
@@ -6720,7 +6718,7 @@
       <c r="C129" t="s">
         <v>30</v>
       </c>
-      <c r="D129" s="4">
+      <c r="D129">
         <v>4</v>
       </c>
       <c r="E129" t="s">
@@ -6743,7 +6741,7 @@
       <c r="C130" t="s">
         <v>32</v>
       </c>
-      <c r="D130" s="4">
+      <c r="D130">
         <v>3</v>
       </c>
       <c r="E130" t="s">
@@ -6766,7 +6764,7 @@
       <c r="C131" t="s">
         <v>34</v>
       </c>
-      <c r="D131" s="4">
+      <c r="D131">
         <v>5</v>
       </c>
       <c r="E131" t="s">
@@ -6789,7 +6787,7 @@
       <c r="C132" t="s">
         <v>36</v>
       </c>
-      <c r="D132" s="4">
+      <c r="D132">
         <v>12</v>
       </c>
       <c r="E132" t="s">
@@ -6812,7 +6810,7 @@
       <c r="C133" t="s">
         <v>38</v>
       </c>
-      <c r="D133" s="4">
+      <c r="D133">
         <v>18</v>
       </c>
       <c r="E133" t="s">
@@ -6835,7 +6833,7 @@
       <c r="C134" t="s">
         <v>40</v>
       </c>
-      <c r="D134" s="4">
+      <c r="D134">
         <v>20</v>
       </c>
       <c r="E134" t="s">
@@ -6858,7 +6856,7 @@
       <c r="C135" t="s">
         <v>42</v>
       </c>
-      <c r="D135" s="4">
+      <c r="D135">
         <v>12</v>
       </c>
       <c r="E135" t="s">
@@ -6881,7 +6879,7 @@
       <c r="C136" t="s">
         <v>44</v>
       </c>
-      <c r="D136" s="4">
+      <c r="D136">
         <v>5</v>
       </c>
       <c r="E136" t="s">
@@ -6904,7 +6902,7 @@
       <c r="C137" t="s">
         <v>46</v>
       </c>
-      <c r="D137" s="4">
+      <c r="D137">
         <v>0</v>
       </c>
       <c r="E137" t="s">
@@ -6927,7 +6925,7 @@
       <c r="C138" t="s">
         <v>48</v>
       </c>
-      <c r="D138" s="4">
+      <c r="D138">
         <v>5</v>
       </c>
       <c r="E138" t="s">
@@ -6950,7 +6948,7 @@
       <c r="C139" t="s">
         <v>49</v>
       </c>
-      <c r="D139" s="4">
+      <c r="D139">
         <v>14</v>
       </c>
       <c r="E139" t="s">
@@ -6973,7 +6971,7 @@
       <c r="C140" t="s">
         <v>50</v>
       </c>
-      <c r="D140" s="4">
+      <c r="D140">
         <v>15</v>
       </c>
       <c r="E140" t="s">
@@ -6996,7 +6994,7 @@
       <c r="C141" t="s">
         <v>51</v>
       </c>
-      <c r="D141" s="4">
+      <c r="D141">
         <v>8</v>
       </c>
       <c r="E141" t="s">
@@ -7019,7 +7017,7 @@
       <c r="C142" t="s">
         <v>52</v>
       </c>
-      <c r="D142" s="4">
+      <c r="D142">
         <v>6</v>
       </c>
       <c r="E142" t="s">
@@ -7042,7 +7040,7 @@
       <c r="C143" t="s">
         <v>53</v>
       </c>
-      <c r="D143" s="4">
+      <c r="D143">
         <v>19</v>
       </c>
       <c r="E143" t="s">
@@ -7065,7 +7063,7 @@
       <c r="C144" t="s">
         <v>54</v>
       </c>
-      <c r="D144" s="4">
+      <c r="D144">
         <v>29</v>
       </c>
       <c r="E144" t="s">
@@ -7088,7 +7086,7 @@
       <c r="C145" t="s">
         <v>55</v>
       </c>
-      <c r="D145" s="4">
+      <c r="D145">
         <v>16</v>
       </c>
       <c r="E145" t="s">
@@ -7111,7 +7109,7 @@
       <c r="C146" t="s">
         <v>56</v>
       </c>
-      <c r="D146" s="4">
+      <c r="D146">
         <v>4</v>
       </c>
       <c r="E146" t="s">
@@ -7134,7 +7132,7 @@
       <c r="C147" t="s">
         <v>57</v>
       </c>
-      <c r="D147" s="4">
+      <c r="D147">
         <v>3</v>
       </c>
       <c r="E147" t="s">
@@ -7157,7 +7155,7 @@
       <c r="C148" t="s">
         <v>58</v>
       </c>
-      <c r="D148" s="4">
+      <c r="D148">
         <v>6</v>
       </c>
       <c r="E148" t="s">
@@ -7180,7 +7178,7 @@
       <c r="C149" t="s">
         <v>59</v>
       </c>
-      <c r="D149" s="4">
+      <c r="D149">
         <v>12</v>
       </c>
       <c r="E149" t="s">
@@ -7203,7 +7201,7 @@
       <c r="C150" t="s">
         <v>60</v>
       </c>
-      <c r="D150" s="4">
+      <c r="D150">
         <v>19</v>
       </c>
       <c r="E150" t="s">
@@ -7226,7 +7224,7 @@
       <c r="C151" t="s">
         <v>61</v>
       </c>
-      <c r="D151" s="4">
+      <c r="D151">
         <v>25</v>
       </c>
       <c r="E151" t="s">
@@ -7249,7 +7247,7 @@
       <c r="C152" t="s">
         <v>62</v>
       </c>
-      <c r="D152" s="4">
+      <c r="D152">
         <v>12</v>
       </c>
       <c r="E152" t="s">
@@ -7272,7 +7270,7 @@
       <c r="C153" t="s">
         <v>63</v>
       </c>
-      <c r="D153" s="4">
+      <c r="D153">
         <v>5</v>
       </c>
       <c r="E153" t="s">
@@ -7295,7 +7293,7 @@
       <c r="C154" t="s">
         <v>64</v>
       </c>
-      <c r="D154" s="4">
+      <c r="D154">
         <v>0</v>
       </c>
       <c r="E154" t="s">
@@ -7318,7 +7316,7 @@
       <c r="C155" t="s">
         <v>65</v>
       </c>
-      <c r="D155" s="4">
+      <c r="D155">
         <v>5</v>
       </c>
       <c r="E155" t="s">
@@ -7341,7 +7339,7 @@
       <c r="C156" t="s">
         <v>66</v>
       </c>
-      <c r="D156" s="4">
+      <c r="D156">
         <v>13</v>
       </c>
       <c r="E156" t="s">
@@ -7364,7 +7362,7 @@
       <c r="C157" t="s">
         <v>67</v>
       </c>
-      <c r="D157" s="4">
+      <c r="D157">
         <v>15</v>
       </c>
       <c r="E157" t="s">
@@ -7387,7 +7385,7 @@
       <c r="C158" t="s">
         <v>68</v>
       </c>
-      <c r="D158" s="4">
+      <c r="D158">
         <v>8</v>
       </c>
       <c r="E158" t="s">
@@ -7410,7 +7408,7 @@
       <c r="C159" t="s">
         <v>69</v>
       </c>
-      <c r="D159" s="4">
+      <c r="D159">
         <v>6</v>
       </c>
       <c r="E159" t="s">
@@ -7433,7 +7431,7 @@
       <c r="C160" t="s">
         <v>70</v>
       </c>
-      <c r="D160" s="4">
+      <c r="D160">
         <v>20</v>
       </c>
       <c r="E160" t="s">
@@ -7456,7 +7454,7 @@
       <c r="C161" t="s">
         <v>71</v>
       </c>
-      <c r="D161" s="4">
+      <c r="D161">
         <v>29</v>
       </c>
       <c r="E161" t="s">
@@ -7479,7 +7477,7 @@
       <c r="C162" t="s">
         <v>72</v>
       </c>
-      <c r="D162" s="4">
+      <c r="D162">
         <v>16</v>
       </c>
       <c r="E162" t="s">
@@ -7502,7 +7500,7 @@
       <c r="C163" t="s">
         <v>73</v>
       </c>
-      <c r="D163" s="4">
+      <c r="D163">
         <v>4</v>
       </c>
       <c r="E163" t="s">
@@ -7525,7 +7523,7 @@
       <c r="C164" t="s">
         <v>74</v>
       </c>
-      <c r="D164" s="4">
+      <c r="D164">
         <v>3</v>
       </c>
       <c r="E164" t="s">
@@ -7548,7 +7546,7 @@
       <c r="C165" t="s">
         <v>75</v>
       </c>
-      <c r="D165" s="4">
+      <c r="D165">
         <v>6</v>
       </c>
       <c r="E165" t="s">
@@ -7571,7 +7569,7 @@
       <c r="C166" t="s">
         <v>76</v>
       </c>
-      <c r="D166" s="4">
+      <c r="D166">
         <v>13</v>
       </c>
       <c r="E166" t="s">
@@ -7594,7 +7592,7 @@
       <c r="C167" t="s">
         <v>77</v>
       </c>
-      <c r="D167" s="4">
+      <c r="D167">
         <v>19</v>
       </c>
       <c r="E167" t="s">
@@ -7617,7 +7615,7 @@
       <c r="C168" t="s">
         <v>78</v>
       </c>
-      <c r="D168" s="4">
+      <c r="D168">
         <v>21</v>
       </c>
       <c r="E168" t="s">
@@ -7640,7 +7638,7 @@
       <c r="C169" t="s">
         <v>79</v>
       </c>
-      <c r="D169" s="4">
+      <c r="D169">
         <v>13</v>
       </c>
       <c r="E169" t="s">
@@ -7663,7 +7661,7 @@
       <c r="C170" t="s">
         <v>80</v>
       </c>
-      <c r="D170" s="4">
+      <c r="D170">
         <v>6</v>
       </c>
       <c r="E170" t="s">
@@ -7686,7 +7684,7 @@
       <c r="C171" t="s">
         <v>81</v>
       </c>
-      <c r="D171" s="4">
+      <c r="D171">
         <v>0</v>
       </c>
       <c r="E171" t="s">
@@ -7709,7 +7707,7 @@
       <c r="C172" t="s">
         <v>82</v>
       </c>
-      <c r="D172" s="4">
+      <c r="D172">
         <v>6</v>
       </c>
       <c r="E172" t="s">
@@ -7732,7 +7730,7 @@
       <c r="C173" t="s">
         <v>83</v>
       </c>
-      <c r="D173" s="4">
+      <c r="D173">
         <v>14</v>
       </c>
       <c r="E173" t="s">
@@ -7755,7 +7753,7 @@
       <c r="C174" t="s">
         <v>84</v>
       </c>
-      <c r="D174" s="4">
+      <c r="D174">
         <v>16</v>
       </c>
       <c r="E174" t="s">
@@ -7778,7 +7776,7 @@
       <c r="C175" t="s">
         <v>85</v>
       </c>
-      <c r="D175" s="4">
+      <c r="D175">
         <v>9</v>
       </c>
       <c r="E175" t="s">
@@ -7801,7 +7799,7 @@
       <c r="C176" t="s">
         <v>86</v>
       </c>
-      <c r="D176" s="4">
+      <c r="D176">
         <v>7</v>
       </c>
       <c r="E176" t="s">
@@ -7824,7 +7822,7 @@
       <c r="C177" t="s">
         <v>87</v>
       </c>
-      <c r="D177" s="4">
+      <c r="D177">
         <v>20</v>
       </c>
       <c r="E177" t="s">
@@ -7847,7 +7845,7 @@
       <c r="C178" t="s">
         <v>88</v>
       </c>
-      <c r="D178" s="4">
+      <c r="D178">
         <v>30</v>
       </c>
       <c r="E178" t="s">
@@ -7870,7 +7868,7 @@
       <c r="C179" t="s">
         <v>89</v>
       </c>
-      <c r="D179" s="4">
+      <c r="D179">
         <v>17</v>
       </c>
       <c r="E179" t="s">
@@ -7893,7 +7891,7 @@
       <c r="C180" t="s">
         <v>90</v>
       </c>
-      <c r="D180" s="4">
+      <c r="D180">
         <v>5</v>
       </c>
       <c r="E180" t="s">
@@ -7916,7 +7914,7 @@
       <c r="C181" t="s">
         <v>91</v>
       </c>
-      <c r="D181" s="4">
+      <c r="D181">
         <v>4</v>
       </c>
       <c r="E181" t="s">
@@ -7939,7 +7937,7 @@
       <c r="C182" t="s">
         <v>92</v>
       </c>
-      <c r="D182" s="4">
+      <c r="D182">
         <v>7</v>
       </c>
       <c r="E182" t="s">
@@ -7962,7 +7960,7 @@
       <c r="C183" t="s">
         <v>93</v>
       </c>
-      <c r="D183" s="4">
+      <c r="D183">
         <v>15</v>
       </c>
       <c r="E183" t="s">
@@ -7985,7 +7983,7 @@
       <c r="C184" t="s">
         <v>94</v>
       </c>
-      <c r="D184" s="4">
+      <c r="D184">
         <v>20</v>
       </c>
       <c r="E184" t="s">
@@ -8008,7 +8006,7 @@
       <c r="C185" t="s">
         <v>95</v>
       </c>
-      <c r="D185" s="4">
+      <c r="D185">
         <v>22</v>
       </c>
       <c r="E185" t="s">
@@ -8031,7 +8029,7 @@
       <c r="C186" t="s">
         <v>96</v>
       </c>
-      <c r="D186" s="4">
+      <c r="D186">
         <v>15</v>
       </c>
       <c r="E186" t="s">
@@ -8054,7 +8052,7 @@
       <c r="C187" t="s">
         <v>97</v>
       </c>
-      <c r="D187" s="4">
+      <c r="D187">
         <v>7</v>
       </c>
       <c r="E187" t="s">
@@ -8077,7 +8075,7 @@
       <c r="C188" t="s">
         <v>98</v>
       </c>
-      <c r="D188" s="4">
+      <c r="D188">
         <v>0</v>
       </c>
       <c r="E188" t="s">
@@ -8100,7 +8098,7 @@
       <c r="C189" t="s">
         <v>99</v>
       </c>
-      <c r="D189" s="4">
+      <c r="D189">
         <v>6</v>
       </c>
       <c r="E189" t="s">
@@ -8123,7 +8121,7 @@
       <c r="C190" t="s">
         <v>100</v>
       </c>
-      <c r="D190" s="4">
+      <c r="D190">
         <v>15</v>
       </c>
       <c r="E190" t="s">
@@ -8146,7 +8144,7 @@
       <c r="C191" t="s">
         <v>101</v>
       </c>
-      <c r="D191" s="4">
+      <c r="D191">
         <v>17</v>
       </c>
       <c r="E191" t="s">
@@ -8169,7 +8167,7 @@
       <c r="C192" t="s">
         <v>102</v>
       </c>
-      <c r="D192" s="4">
+      <c r="D192">
         <v>10</v>
       </c>
       <c r="E192" t="s">
@@ -8192,7 +8190,7 @@
       <c r="C193" t="s">
         <v>103</v>
       </c>
-      <c r="D193" s="4">
+      <c r="D193">
         <v>9</v>
       </c>
       <c r="E193" t="s">
@@ -8215,7 +8213,7 @@
       <c r="C194" t="s">
         <v>104</v>
       </c>
-      <c r="D194" s="4">
+      <c r="D194">
         <v>22</v>
       </c>
       <c r="E194" t="s">
@@ -8238,7 +8236,7 @@
       <c r="C195" t="s">
         <v>105</v>
       </c>
-      <c r="D195" s="4">
+      <c r="D195">
         <v>32</v>
       </c>
       <c r="E195" t="s">
@@ -8261,7 +8259,7 @@
       <c r="C196" t="s">
         <v>106</v>
       </c>
-      <c r="D196" s="4">
+      <c r="D196">
         <v>20</v>
       </c>
       <c r="E196" t="s">
@@ -8284,7 +8282,7 @@
       <c r="C197" t="s">
         <v>107</v>
       </c>
-      <c r="D197" s="4">
+      <c r="D197">
         <v>6</v>
       </c>
       <c r="E197" t="s">
@@ -8307,7 +8305,7 @@
       <c r="C198" t="s">
         <v>108</v>
       </c>
-      <c r="D198" s="4">
+      <c r="D198">
         <v>7</v>
       </c>
       <c r="E198" t="s">
@@ -8330,7 +8328,7 @@
       <c r="C199" t="s">
         <v>109</v>
       </c>
-      <c r="D199" s="4">
+      <c r="D199">
         <v>12</v>
       </c>
       <c r="E199" t="s">
@@ -8353,7 +8351,7 @@
       <c r="C200" t="s">
         <v>110</v>
       </c>
-      <c r="D200" s="4">
+      <c r="D200">
         <v>18</v>
       </c>
       <c r="E200" t="s">
@@ -8376,7 +8374,7 @@
       <c r="C201" t="s">
         <v>111</v>
       </c>
-      <c r="D201" s="4">
+      <c r="D201">
         <v>26</v>
       </c>
       <c r="E201" t="s">
@@ -8399,7 +8397,7 @@
       <c r="C202" t="s">
         <v>112</v>
       </c>
-      <c r="D202" s="4">
+      <c r="D202">
         <v>28</v>
       </c>
       <c r="E202" t="s">
@@ -8422,7 +8420,7 @@
       <c r="C203" t="s">
         <v>113</v>
       </c>
-      <c r="D203" s="4">
+      <c r="D203">
         <v>22</v>
       </c>
       <c r="E203" t="s">
@@ -8445,7 +8443,7 @@
       <c r="C204" t="s">
         <v>114</v>
       </c>
-      <c r="D204" s="4">
+      <c r="D204">
         <v>12</v>
       </c>
       <c r="E204" t="s">
@@ -8468,7 +8466,7 @@
       <c r="C205" t="s">
         <v>115</v>
       </c>
-      <c r="D205" s="4">
+      <c r="D205">
         <v>0</v>
       </c>
       <c r="E205" t="s">
@@ -8491,7 +8489,7 @@
       <c r="C206" t="s">
         <v>116</v>
       </c>
-      <c r="D206" s="4">
+      <c r="D206">
         <v>3</v>
       </c>
       <c r="E206" t="s">
@@ -8514,7 +8512,7 @@
       <c r="C207" t="s">
         <v>117</v>
       </c>
-      <c r="D207" s="4">
+      <c r="D207">
         <v>6</v>
       </c>
       <c r="E207" t="s">
@@ -8537,7 +8535,7 @@
       <c r="C208" t="s">
         <v>118</v>
       </c>
-      <c r="D208" s="4">
+      <c r="D208">
         <v>16</v>
       </c>
       <c r="E208" t="s">
@@ -8560,7 +8558,7 @@
       <c r="C209" t="s">
         <v>119</v>
       </c>
-      <c r="D209" s="4">
+      <c r="D209">
         <v>24</v>
       </c>
       <c r="E209" t="s">
@@ -8583,7 +8581,7 @@
       <c r="C210" t="s">
         <v>120</v>
       </c>
-      <c r="D210" s="4">
+      <c r="D210">
         <v>26</v>
       </c>
       <c r="E210" t="s">
@@ -8606,7 +8604,7 @@
       <c r="C211" t="s">
         <v>121</v>
       </c>
-      <c r="D211" s="4">
+      <c r="D211">
         <v>24</v>
       </c>
       <c r="E211" t="s">
@@ -8629,7 +8627,7 @@
       <c r="C212" t="s">
         <v>122</v>
       </c>
-      <c r="D212" s="4">
+      <c r="D212">
         <v>28</v>
       </c>
       <c r="E212" t="s">
@@ -8652,7 +8650,7 @@
       <c r="C213" t="s">
         <v>123</v>
       </c>
-      <c r="D213" s="4">
+      <c r="D213">
         <v>24</v>
       </c>
       <c r="E213" t="s">
@@ -8675,7 +8673,7 @@
       <c r="C214" t="s">
         <v>124</v>
       </c>
-      <c r="D214" s="4">
+      <c r="D214">
         <v>12</v>
       </c>
       <c r="E214" t="s">
@@ -8698,7 +8696,7 @@
       <c r="C215" t="s">
         <v>125</v>
       </c>
-      <c r="D215" s="4">
+      <c r="D215">
         <v>10</v>
       </c>
       <c r="E215" t="s">
@@ -8721,7 +8719,7 @@
       <c r="C216" t="s">
         <v>126</v>
       </c>
-      <c r="D216" s="4">
+      <c r="D216">
         <v>14</v>
       </c>
       <c r="E216" t="s">
@@ -8744,7 +8742,7 @@
       <c r="C217" t="s">
         <v>127</v>
       </c>
-      <c r="D217" s="4">
+      <c r="D217">
         <v>22</v>
       </c>
       <c r="E217" t="s">
@@ -8767,7 +8765,7 @@
       <c r="C218" t="s">
         <v>128</v>
       </c>
-      <c r="D218" s="4">
+      <c r="D218">
         <v>30</v>
       </c>
       <c r="E218" t="s">
@@ -8790,7 +8788,7 @@
       <c r="C219" t="s">
         <v>129</v>
       </c>
-      <c r="D219" s="4">
+      <c r="D219">
         <v>32</v>
       </c>
       <c r="E219" t="s">
@@ -8813,7 +8811,7 @@
       <c r="C220" t="s">
         <v>130</v>
       </c>
-      <c r="D220" s="4">
+      <c r="D220">
         <v>26</v>
       </c>
       <c r="E220" t="s">
@@ -8836,7 +8834,7 @@
       <c r="C221" t="s">
         <v>131</v>
       </c>
-      <c r="D221" s="4">
+      <c r="D221">
         <v>16</v>
       </c>
       <c r="E221" t="s">
@@ -8859,7 +8857,7 @@
       <c r="C222" t="s">
         <v>132</v>
       </c>
-      <c r="D222" s="4">
+      <c r="D222">
         <v>0</v>
       </c>
       <c r="E222" t="s">
@@ -8882,7 +8880,7 @@
       <c r="C223" t="s">
         <v>133</v>
       </c>
-      <c r="D223" s="4">
+      <c r="D223">
         <v>3</v>
       </c>
       <c r="E223" t="s">
@@ -8905,7 +8903,7 @@
       <c r="C224" t="s">
         <v>134</v>
       </c>
-      <c r="D224" s="4">
+      <c r="D224">
         <v>5</v>
       </c>
       <c r="E224" t="s">
@@ -8928,7 +8926,7 @@
       <c r="C225" t="s">
         <v>135</v>
       </c>
-      <c r="D225" s="4">
+      <c r="D225">
         <v>14</v>
       </c>
       <c r="E225" t="s">
@@ -8951,7 +8949,7 @@
       <c r="C226" t="s">
         <v>136</v>
       </c>
-      <c r="D226" s="4">
+      <c r="D226">
         <v>20</v>
       </c>
       <c r="E226" t="s">
@@ -8974,7 +8972,7 @@
       <c r="C227" t="s">
         <v>137</v>
       </c>
-      <c r="D227" s="4">
+      <c r="D227">
         <v>22</v>
       </c>
       <c r="E227" t="s">
@@ -8997,7 +8995,7 @@
       <c r="C228" t="s">
         <v>138</v>
       </c>
-      <c r="D228" s="4">
+      <c r="D228">
         <v>26</v>
       </c>
       <c r="E228" t="s">
@@ -9020,7 +9018,7 @@
       <c r="C229" t="s">
         <v>139</v>
       </c>
-      <c r="D229" s="4">
+      <c r="D229">
         <v>28</v>
       </c>
       <c r="E229" t="s">
@@ -9043,7 +9041,7 @@
       <c r="C230" t="s">
         <v>140</v>
       </c>
-      <c r="D230" s="4">
+      <c r="D230">
         <v>24</v>
       </c>
       <c r="E230" t="s">
@@ -9066,7 +9064,7 @@
       <c r="C231" t="s">
         <v>141</v>
       </c>
-      <c r="D231" s="4">
+      <c r="D231">
         <v>14</v>
       </c>
       <c r="E231" t="s">
@@ -9089,7 +9087,7 @@
       <c r="C232" t="s">
         <v>142</v>
       </c>
-      <c r="D232" s="4">
+      <c r="D232">
         <v>10</v>
       </c>
       <c r="E232" t="s">
@@ -9112,7 +9110,7 @@
       <c r="C233" t="s">
         <v>143</v>
       </c>
-      <c r="D233" s="4">
+      <c r="D233">
         <v>10</v>
       </c>
       <c r="E233" t="s">
@@ -9135,7 +9133,7 @@
       <c r="C234" t="s">
         <v>144</v>
       </c>
-      <c r="D234" s="4">
+      <c r="D234">
         <v>18</v>
       </c>
       <c r="E234" t="s">
@@ -9158,7 +9156,7 @@
       <c r="C235" t="s">
         <v>145</v>
       </c>
-      <c r="D235" s="4">
+      <c r="D235">
         <v>22</v>
       </c>
       <c r="E235" t="s">
@@ -9181,7 +9179,7 @@
       <c r="C236" t="s">
         <v>146</v>
       </c>
-      <c r="D236" s="4">
+      <c r="D236">
         <v>24</v>
       </c>
       <c r="E236" t="s">
@@ -9204,7 +9202,7 @@
       <c r="C237" t="s">
         <v>147</v>
       </c>
-      <c r="D237" s="4">
+      <c r="D237">
         <v>18</v>
       </c>
       <c r="E237" t="s">
@@ -9227,7 +9225,7 @@
       <c r="C238" t="s">
         <v>148</v>
       </c>
-      <c r="D238" s="4">
+      <c r="D238">
         <v>10</v>
       </c>
       <c r="E238" t="s">
@@ -9250,7 +9248,7 @@
       <c r="C239" t="s">
         <v>149</v>
       </c>
-      <c r="D239" s="4">
+      <c r="D239">
         <v>0</v>
       </c>
       <c r="E239" t="s">

--- a/scripts/restaurant_variables.xlsx
+++ b/scripts/restaurant_variables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\loren\Desktop\Simulation\Progetto\Restaurant_2025\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{0F366A8D-A54C-4401-A490-1D25C47DCBF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D054DCA-0056-46BE-A4A1-1143255696F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="19420" tabRatio="851" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="19420" tabRatio="851" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tables_selection" sheetId="11" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <definedName name="DatiEsterni_3" localSheetId="0" hidden="1">tables_selection!$B$1:$G$11</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -95,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="168">
   <si>
     <t>start_timestamp</t>
   </si>
@@ -596,6 +597,9 @@
   </si>
   <si>
     <t>scenario</t>
+  </si>
+  <si>
+    <t>2_size_perc</t>
   </si>
 </sst>
 </file>
@@ -730,6 +734,21 @@
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="21">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="none">
@@ -908,21 +927,6 @@
     <dxf>
       <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
     </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -938,7 +942,7 @@
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="DatiEsterni_3" connectionId="19" xr16:uid="{31982ACB-6682-4EA9-8905-53237B301B53}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="11" unboundColumnsLeft="1" unboundColumnsRight="3">
+  <queryTableRefresh nextId="17" unboundColumnsLeft="1" unboundColumnsRight="3">
     <queryTableFields count="10">
       <queryTableField id="10" dataBound="0" tableColumnId="10"/>
       <queryTableField id="1" name="start_timestamp" tableColumnId="1"/>
@@ -979,10 +983,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{7D1585E5-EB18-4555-BFB4-AB049789BB50}" name="tables_selection" displayName="tables_selection" ref="A1:J11" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:J11" xr:uid="{7D1585E5-EB18-4555-BFB4-AB049789BB50}"/>
   <tableColumns count="10">
-    <tableColumn id="10" xr3:uid="{1ADF8E6C-C756-4DB0-AF29-730090E9A389}" uniqueName="10" name="scenario" queryTableFieldId="10" dataDxfId="19"/>
-    <tableColumn id="1" xr3:uid="{9DF6AF6D-4327-4E8B-A17C-4CE32200A2CC}" uniqueName="1" name="start_timestamp" queryTableFieldId="1" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{DB186560-5030-4DB1-A6BD-A74C44B2F90A}" uniqueName="2" name="end_timestamp" queryTableFieldId="2" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{6CE09762-A225-468B-8C15-326E109C4C41}" uniqueName="3" name="period" queryTableFieldId="3" dataDxfId="16"/>
+    <tableColumn id="10" xr3:uid="{1ADF8E6C-C756-4DB0-AF29-730090E9A389}" uniqueName="10" name="scenario" queryTableFieldId="10" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{9DF6AF6D-4327-4E8B-A17C-4CE32200A2CC}" uniqueName="1" name="start_timestamp" queryTableFieldId="1" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{DB186560-5030-4DB1-A6BD-A74C44B2F90A}" uniqueName="2" name="end_timestamp" queryTableFieldId="2" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{6CE09762-A225-468B-8C15-326E109C4C41}" uniqueName="3" name="period" queryTableFieldId="3" dataDxfId="0"/>
     <tableColumn id="4" xr3:uid="{90771DE1-93AE-42DD-88DE-8292168CC27F}" uniqueName="4" name="bar_on" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{2D6F5E1B-E207-46D0-A78B-EA6977317860}" uniqueName="5" name="inside_on" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{5AFB94CB-8BB6-4AE5-B6B3-D1BD6C86A1FB}" uniqueName="6" name="outside_on" queryTableFieldId="6"/>
@@ -998,12 +1002,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{54D2211C-274A-47E4-BDD0-4C0951D8DD68}" name="employees_schedule" displayName="employees_schedule" ref="A1:H71" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:H71" xr:uid="{54D2211C-274A-47E4-BDD0-4C0951D8DD68}"/>
   <tableColumns count="8">
-    <tableColumn id="15" xr3:uid="{C7ED7AB4-5A31-4D81-834A-B6E64F7023C8}" uniqueName="15" name="scenario" queryTableFieldId="9" dataDxfId="15"/>
-    <tableColumn id="1" xr3:uid="{1826F0BC-F6D0-44C5-8A93-C7D99BD8CB8B}" uniqueName="1" name="start_timestamp" queryTableFieldId="1" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{75D23335-1496-4011-81D1-D6034B72FF11}" uniqueName="2" name="end_timestamp" queryTableFieldId="2" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{92C90E84-B1B0-4866-9DDC-2A2B72F890FA}" uniqueName="4" name="weekday" queryTableFieldId="4" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{954429F6-A3DE-46A7-885B-49BC6CAF5664}" uniqueName="5" name="hour" queryTableFieldId="5" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{D0D42E6A-14B4-4741-A3F6-DD9143A88038}" uniqueName="6" name="period" queryTableFieldId="6" dataDxfId="10"/>
+    <tableColumn id="15" xr3:uid="{C7ED7AB4-5A31-4D81-834A-B6E64F7023C8}" uniqueName="15" name="scenario" queryTableFieldId="9" dataDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{1826F0BC-F6D0-44C5-8A93-C7D99BD8CB8B}" uniqueName="1" name="start_timestamp" queryTableFieldId="1" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{75D23335-1496-4011-81D1-D6034B72FF11}" uniqueName="2" name="end_timestamp" queryTableFieldId="2" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{92C90E84-B1B0-4866-9DDC-2A2B72F890FA}" uniqueName="4" name="weekday" queryTableFieldId="4" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{954429F6-A3DE-46A7-885B-49BC6CAF5664}" uniqueName="5" name="hour" queryTableFieldId="5" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{D0D42E6A-14B4-4741-A3F6-DD9143A88038}" uniqueName="6" name="period" queryTableFieldId="6" dataDxfId="15"/>
     <tableColumn id="7" xr3:uid="{DC0D317B-9907-4E39-BD04-56F982B6DFC4}" uniqueName="7" name="waiters" queryTableFieldId="7"/>
     <tableColumn id="8" xr3:uid="{5822B03F-BA67-4CAF-8288-1B9FA740A60F}" uniqueName="8" name="cooks" queryTableFieldId="8"/>
   </tableColumns>
@@ -1012,14 +1016,14 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D544813D-DF99-41C8-AE8A-38BE1FAF9E94}" name="Tabella3" displayName="Tabella3" ref="A1:E11" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D544813D-DF99-41C8-AE8A-38BE1FAF9E94}" name="Tabella3" displayName="Tabella3" ref="A1:E11" totalsRowShown="0" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11" totalsRowBorderDxfId="10">
   <autoFilter ref="A1:E11" xr:uid="{D544813D-DF99-41C8-AE8A-38BE1FAF9E94}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{5F6DE45A-D069-49C3-A965-E57C526C9F10}" name="scenario" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{4D8F0B29-A4FF-499D-9A3B-DCD79E56771F}" name="start_timestamp" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{73FD92A6-7E32-4F59-A6D2-E391CC1529B2}" name="end_timestamp" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{E9B6B43D-80B9-448F-8CE5-DB0428CE9192}" name="period" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{FA561D75-B96F-4DC4-B290-98BCE5AF9EBB}" name="time_avg" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{5F6DE45A-D069-49C3-A965-E57C526C9F10}" name="scenario" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{4D8F0B29-A4FF-499D-9A3B-DCD79E56771F}" name="start_timestamp" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{73FD92A6-7E32-4F59-A6D2-E391CC1529B2}" name="end_timestamp" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{E9B6B43D-80B9-448F-8CE5-DB0428CE9192}" name="period" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{FA561D75-B96F-4DC4-B290-98BCE5AF9EBB}" name="time_avg" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1032,7 +1036,7 @@
     <tableColumn id="1" xr3:uid="{C0C152CA-AC82-4A38-9515-01F93B55CD35}" name="scenario"/>
     <tableColumn id="2" xr3:uid="{A9274257-0F1F-4EC5-AEAD-2D02ED20F27D}" name="start_timestamp"/>
     <tableColumn id="3" xr3:uid="{8EBF5A3E-33DA-4E63-85B2-6A750FD2B59E}" name="end_timestamp"/>
-    <tableColumn id="4" xr3:uid="{1B570803-0CC6-4039-83E4-466D06E97DE8}" name="arrival_rate" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{1B570803-0CC6-4039-83E4-466D06E97DE8}" name="arrival_rate" dataDxfId="4"/>
     <tableColumn id="5" xr3:uid="{2330BE18-97F9-494B-A0D2-BC6CD4BE5D26}" name="weekday"/>
     <tableColumn id="6" xr3:uid="{511C9B76-5714-4C6E-B45F-24A76465D0A2}" name="hour"/>
     <tableColumn id="7" xr3:uid="{DDB83C9A-5515-4339-958C-0504A36D7FBA}" name="avg_group_size"/>
@@ -1304,7 +1308,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2489A5EA-DD05-4EB8-ADF0-37ED0B27C5D1}">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.26953125" style="3" bestFit="1" customWidth="1"/>
@@ -1314,7 +1318,10 @@
     <col min="6" max="6" width="12.54296875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.26953125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.54296875" style="3" customWidth="1"/>
+    <col min="12" max="14" width="12.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.81640625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">

--- a/scripts/restaurant_variables.xlsx
+++ b/scripts/restaurant_variables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\loren\Desktop\Simulation\Progetto\Restaurant_2025\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D054DCA-0056-46BE-A4A1-1143255696F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69032B05-EF17-43C2-AFC7-8DDD5062390A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="19420" tabRatio="851" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="19420" tabRatio="851" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tables_selection" sheetId="11" r:id="rId1"/>
@@ -23,11 +23,21 @@
     <definedName name="DatiEsterni_2" localSheetId="3" hidden="1">arrival_rate_week_groupsize!$B$1:$G$239</definedName>
     <definedName name="DatiEsterni_3" localSheetId="0" hidden="1">tables_selection!$B$1:$G$11</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -96,7 +106,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="167">
   <si>
     <t>start_timestamp</t>
   </si>
@@ -597,17 +607,15 @@
   </si>
   <si>
     <t>scenario</t>
-  </si>
-  <si>
-    <t>2_size_perc</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -640,7 +648,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -712,11 +720,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -729,25 +748,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="23">
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
+      <numFmt numFmtId="165" formatCode="0.0"/>
     </dxf>
     <dxf>
       <fill>
@@ -927,6 +943,18 @@
     <dxf>
       <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -983,10 +1011,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{7D1585E5-EB18-4555-BFB4-AB049789BB50}" name="tables_selection" displayName="tables_selection" ref="A1:J11" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:J11" xr:uid="{7D1585E5-EB18-4555-BFB4-AB049789BB50}"/>
   <tableColumns count="10">
-    <tableColumn id="10" xr3:uid="{1ADF8E6C-C756-4DB0-AF29-730090E9A389}" uniqueName="10" name="scenario" queryTableFieldId="10" dataDxfId="3"/>
-    <tableColumn id="1" xr3:uid="{9DF6AF6D-4327-4E8B-A17C-4CE32200A2CC}" uniqueName="1" name="start_timestamp" queryTableFieldId="1" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{DB186560-5030-4DB1-A6BD-A74C44B2F90A}" uniqueName="2" name="end_timestamp" queryTableFieldId="2" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{6CE09762-A225-468B-8C15-326E109C4C41}" uniqueName="3" name="period" queryTableFieldId="3" dataDxfId="0"/>
+    <tableColumn id="10" xr3:uid="{1ADF8E6C-C756-4DB0-AF29-730090E9A389}" uniqueName="10" name="scenario" queryTableFieldId="10" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{9DF6AF6D-4327-4E8B-A17C-4CE32200A2CC}" uniqueName="1" name="start_timestamp" queryTableFieldId="1" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{DB186560-5030-4DB1-A6BD-A74C44B2F90A}" uniqueName="2" name="end_timestamp" queryTableFieldId="2" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{6CE09762-A225-468B-8C15-326E109C4C41}" uniqueName="3" name="period" queryTableFieldId="3" dataDxfId="19"/>
     <tableColumn id="4" xr3:uid="{90771DE1-93AE-42DD-88DE-8292168CC27F}" uniqueName="4" name="bar_on" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{2D6F5E1B-E207-46D0-A78B-EA6977317860}" uniqueName="5" name="inside_on" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{5AFB94CB-8BB6-4AE5-B6B3-D1BD6C86A1FB}" uniqueName="6" name="outside_on" queryTableFieldId="6"/>
@@ -1002,12 +1030,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{54D2211C-274A-47E4-BDD0-4C0951D8DD68}" name="employees_schedule" displayName="employees_schedule" ref="A1:H71" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:H71" xr:uid="{54D2211C-274A-47E4-BDD0-4C0951D8DD68}"/>
   <tableColumns count="8">
-    <tableColumn id="15" xr3:uid="{C7ED7AB4-5A31-4D81-834A-B6E64F7023C8}" uniqueName="15" name="scenario" queryTableFieldId="9" dataDxfId="20"/>
-    <tableColumn id="1" xr3:uid="{1826F0BC-F6D0-44C5-8A93-C7D99BD8CB8B}" uniqueName="1" name="start_timestamp" queryTableFieldId="1" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{75D23335-1496-4011-81D1-D6034B72FF11}" uniqueName="2" name="end_timestamp" queryTableFieldId="2" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{92C90E84-B1B0-4866-9DDC-2A2B72F890FA}" uniqueName="4" name="weekday" queryTableFieldId="4" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{954429F6-A3DE-46A7-885B-49BC6CAF5664}" uniqueName="5" name="hour" queryTableFieldId="5" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{D0D42E6A-14B4-4741-A3F6-DD9143A88038}" uniqueName="6" name="period" queryTableFieldId="6" dataDxfId="15"/>
+    <tableColumn id="15" xr3:uid="{C7ED7AB4-5A31-4D81-834A-B6E64F7023C8}" uniqueName="15" name="scenario" queryTableFieldId="9" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{1826F0BC-F6D0-44C5-8A93-C7D99BD8CB8B}" uniqueName="1" name="start_timestamp" queryTableFieldId="1" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{75D23335-1496-4011-81D1-D6034B72FF11}" uniqueName="2" name="end_timestamp" queryTableFieldId="2" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{92C90E84-B1B0-4866-9DDC-2A2B72F890FA}" uniqueName="4" name="weekday" queryTableFieldId="4" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{954429F6-A3DE-46A7-885B-49BC6CAF5664}" uniqueName="5" name="hour" queryTableFieldId="5" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{D0D42E6A-14B4-4741-A3F6-DD9143A88038}" uniqueName="6" name="period" queryTableFieldId="6" dataDxfId="13"/>
     <tableColumn id="7" xr3:uid="{DC0D317B-9907-4E39-BD04-56F982B6DFC4}" uniqueName="7" name="waiters" queryTableFieldId="7"/>
     <tableColumn id="8" xr3:uid="{5822B03F-BA67-4CAF-8288-1B9FA740A60F}" uniqueName="8" name="cooks" queryTableFieldId="8"/>
   </tableColumns>
@@ -1016,14 +1044,14 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D544813D-DF99-41C8-AE8A-38BE1FAF9E94}" name="Tabella3" displayName="Tabella3" ref="A1:E11" totalsRowShown="0" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11" totalsRowBorderDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D544813D-DF99-41C8-AE8A-38BE1FAF9E94}" name="Tabella3" displayName="Tabella3" ref="A1:E11" totalsRowShown="0" headerRowDxfId="12" dataDxfId="10" headerRowBorderDxfId="11" tableBorderDxfId="9" totalsRowBorderDxfId="8">
   <autoFilter ref="A1:E11" xr:uid="{D544813D-DF99-41C8-AE8A-38BE1FAF9E94}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{5F6DE45A-D069-49C3-A965-E57C526C9F10}" name="scenario" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{4D8F0B29-A4FF-499D-9A3B-DCD79E56771F}" name="start_timestamp" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{73FD92A6-7E32-4F59-A6D2-E391CC1529B2}" name="end_timestamp" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{E9B6B43D-80B9-448F-8CE5-DB0428CE9192}" name="period" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{FA561D75-B96F-4DC4-B290-98BCE5AF9EBB}" name="time_avg" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{5F6DE45A-D069-49C3-A965-E57C526C9F10}" name="scenario" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{4D8F0B29-A4FF-499D-9A3B-DCD79E56771F}" name="start_timestamp" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{73FD92A6-7E32-4F59-A6D2-E391CC1529B2}" name="end_timestamp" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{E9B6B43D-80B9-448F-8CE5-DB0428CE9192}" name="period" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{FA561D75-B96F-4DC4-B290-98BCE5AF9EBB}" name="time_avg" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1034,9 +1062,9 @@
   <autoFilter ref="A1:G239" xr:uid="{E79869A8-51C0-465F-A154-CE9C9BB79619}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{C0C152CA-AC82-4A38-9515-01F93B55CD35}" name="scenario"/>
-    <tableColumn id="2" xr3:uid="{A9274257-0F1F-4EC5-AEAD-2D02ED20F27D}" name="start_timestamp"/>
-    <tableColumn id="3" xr3:uid="{8EBF5A3E-33DA-4E63-85B2-6A750FD2B59E}" name="end_timestamp"/>
-    <tableColumn id="4" xr3:uid="{1B570803-0CC6-4039-83E4-466D06E97DE8}" name="arrival_rate" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{A9274257-0F1F-4EC5-AEAD-2D02ED20F27D}" name="start_timestamp" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{8EBF5A3E-33DA-4E63-85B2-6A750FD2B59E}" name="end_timestamp" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{1B570803-0CC6-4039-83E4-466D06E97DE8}" name="arrival_rate" dataDxfId="2"/>
     <tableColumn id="5" xr3:uid="{2330BE18-97F9-494B-A0D2-BC6CD4BE5D26}" name="weekday"/>
     <tableColumn id="6" xr3:uid="{511C9B76-5714-4C6E-B45F-24A76465D0A2}" name="hour"/>
     <tableColumn id="7" xr3:uid="{DDB83C9A-5515-4339-958C-0504A36D7FBA}" name="avg_group_size"/>
@@ -1849,10 +1877,10 @@
         <v>158</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -1979,10 +2007,10 @@
         <v>158</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -2109,10 +2137,10 @@
         <v>158</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
@@ -2239,10 +2267,10 @@
         <v>158</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
@@ -2369,10 +2397,10 @@
         <v>158</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
@@ -2499,10 +2527,10 @@
         <v>158</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
@@ -2629,10 +2657,10 @@
         <v>158</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
@@ -2759,10 +2787,10 @@
         <v>158</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
@@ -2889,10 +2917,10 @@
         <v>158</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
@@ -3019,10 +3047,10 @@
         <v>158</v>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
@@ -3149,10 +3177,10 @@
         <v>158</v>
       </c>
       <c r="G56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.35">
@@ -3279,10 +3307,10 @@
         <v>158</v>
       </c>
       <c r="G61">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.35">
@@ -3409,10 +3437,10 @@
         <v>158</v>
       </c>
       <c r="G66">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H66">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.35">
@@ -3539,10 +3567,10 @@
         <v>158</v>
       </c>
       <c r="G71">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H71">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -3762,11 +3790,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BD3D082-868C-448F-9F19-732771E93A1D}">
-  <dimension ref="A1:G239"/>
+  <dimension ref="A1:J239"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="3" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.453125" style="3" customWidth="1"/>
+    <col min="1" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.81640625" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.453125" style="13" customWidth="1"/>
     <col min="5" max="5" width="10.6328125" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="16" bestFit="1" customWidth="1"/>
   </cols>
@@ -3778,10 +3807,10 @@
       <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="C1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="13" t="s">
         <v>2</v>
       </c>
       <c r="E1" t="s">
@@ -3798,13 +3827,13 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="13">
         <v>5</v>
       </c>
       <c r="E2" t="s">
@@ -3821,13 +3850,13 @@
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="13">
         <v>12</v>
       </c>
       <c r="E3" t="s">
@@ -3844,13 +3873,13 @@
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="13">
         <v>14</v>
       </c>
       <c r="E4" t="s">
@@ -3867,13 +3896,13 @@
       <c r="A5">
         <v>1</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="13">
         <v>8</v>
       </c>
       <c r="E5" t="s">
@@ -3890,13 +3919,13 @@
       <c r="A6">
         <v>1</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="13">
         <v>6</v>
       </c>
       <c r="E6" t="s">
@@ -3913,13 +3942,13 @@
       <c r="A7">
         <v>1</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="13">
         <v>18</v>
       </c>
       <c r="E7" t="s">
@@ -3936,13 +3965,13 @@
       <c r="A8">
         <v>1</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="13">
         <v>28</v>
       </c>
       <c r="E8" t="s">
@@ -3959,13 +3988,13 @@
       <c r="A9">
         <v>1</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="13">
         <v>16</v>
       </c>
       <c r="E9" t="s">
@@ -3982,13 +4011,13 @@
       <c r="A10">
         <v>1</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="13">
         <v>4</v>
       </c>
       <c r="E10" t="s">
@@ -4005,13 +4034,13 @@
       <c r="A11">
         <v>1</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="13">
         <v>3</v>
       </c>
       <c r="E11" t="s">
@@ -4028,13 +4057,13 @@
       <c r="A12">
         <v>1</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="13">
         <v>5</v>
       </c>
       <c r="E12" t="s">
@@ -4051,13 +4080,13 @@
       <c r="A13">
         <v>1</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="13">
         <v>12</v>
       </c>
       <c r="E13" t="s">
@@ -4074,13 +4103,13 @@
       <c r="A14">
         <v>1</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="13">
         <v>18</v>
       </c>
       <c r="E14" t="s">
@@ -4097,13 +4126,13 @@
       <c r="A15">
         <v>1</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="13">
         <v>20</v>
       </c>
       <c r="E15" t="s">
@@ -4120,13 +4149,13 @@
       <c r="A16">
         <v>1</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="13">
         <v>12</v>
       </c>
       <c r="E16" t="s">
@@ -4143,13 +4172,13 @@
       <c r="A17">
         <v>1</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="13">
         <v>5</v>
       </c>
       <c r="E17" t="s">
@@ -4166,13 +4195,13 @@
       <c r="A18">
         <v>1</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="13">
         <v>0</v>
       </c>
       <c r="E18" t="s">
@@ -4189,13 +4218,13 @@
       <c r="A19">
         <v>1</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="13">
         <v>5</v>
       </c>
       <c r="E19" t="s">
@@ -4212,13 +4241,13 @@
       <c r="A20">
         <v>1</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="13">
         <v>14</v>
       </c>
       <c r="E20" t="s">
@@ -4235,13 +4264,13 @@
       <c r="A21">
         <v>1</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="13">
         <v>15</v>
       </c>
       <c r="E21" t="s">
@@ -4258,13 +4287,13 @@
       <c r="A22">
         <v>1</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="13">
         <v>8</v>
       </c>
       <c r="E22" t="s">
@@ -4281,13 +4310,13 @@
       <c r="A23">
         <v>1</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="13">
         <v>6</v>
       </c>
       <c r="E23" t="s">
@@ -4304,13 +4333,13 @@
       <c r="A24">
         <v>1</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="13">
         <v>19</v>
       </c>
       <c r="E24" t="s">
@@ -4327,13 +4356,13 @@
       <c r="A25">
         <v>1</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="13">
         <v>29</v>
       </c>
       <c r="E25" t="s">
@@ -4350,13 +4379,13 @@
       <c r="A26">
         <v>1</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="13">
         <v>16</v>
       </c>
       <c r="E26" t="s">
@@ -4373,13 +4402,13 @@
       <c r="A27">
         <v>1</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="13">
         <v>4</v>
       </c>
       <c r="E27" t="s">
@@ -4396,13 +4425,13 @@
       <c r="A28">
         <v>1</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="13">
         <v>3</v>
       </c>
       <c r="E28" t="s">
@@ -4419,13 +4448,13 @@
       <c r="A29">
         <v>1</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="13">
         <v>6</v>
       </c>
       <c r="E29" t="s">
@@ -4442,13 +4471,13 @@
       <c r="A30">
         <v>1</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="13">
         <v>12</v>
       </c>
       <c r="E30" t="s">
@@ -4465,13 +4494,13 @@
       <c r="A31">
         <v>1</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="13">
         <v>19</v>
       </c>
       <c r="E31" t="s">
@@ -4488,13 +4517,13 @@
       <c r="A32">
         <v>1</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="13">
         <v>25</v>
       </c>
       <c r="E32" t="s">
@@ -4511,13 +4540,13 @@
       <c r="A33">
         <v>1</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="13">
         <v>12</v>
       </c>
       <c r="E33" t="s">
@@ -4534,13 +4563,13 @@
       <c r="A34">
         <v>1</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="13">
         <v>5</v>
       </c>
       <c r="E34" t="s">
@@ -4557,13 +4586,13 @@
       <c r="A35">
         <v>1</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="13">
         <v>0</v>
       </c>
       <c r="E35" t="s">
@@ -4580,13 +4609,13 @@
       <c r="A36">
         <v>1</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="13">
         <v>5</v>
       </c>
       <c r="E36" t="s">
@@ -4603,13 +4632,13 @@
       <c r="A37">
         <v>1</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="13">
         <v>13</v>
       </c>
       <c r="E37" t="s">
@@ -4626,13 +4655,13 @@
       <c r="A38">
         <v>1</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="13">
         <v>15</v>
       </c>
       <c r="E38" t="s">
@@ -4649,13 +4678,13 @@
       <c r="A39">
         <v>1</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="13">
         <v>8</v>
       </c>
       <c r="E39" t="s">
@@ -4672,13 +4701,13 @@
       <c r="A40">
         <v>1</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="13">
         <v>6</v>
       </c>
       <c r="E40" t="s">
@@ -4695,13 +4724,13 @@
       <c r="A41">
         <v>1</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="13">
         <v>20</v>
       </c>
       <c r="E41" t="s">
@@ -4718,13 +4747,13 @@
       <c r="A42">
         <v>1</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="13">
         <v>29</v>
       </c>
       <c r="E42" t="s">
@@ -4741,13 +4770,13 @@
       <c r="A43">
         <v>1</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="13">
         <v>16</v>
       </c>
       <c r="E43" t="s">
@@ -4764,13 +4793,13 @@
       <c r="A44">
         <v>1</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="13">
         <v>4</v>
       </c>
       <c r="E44" t="s">
@@ -4787,13 +4816,13 @@
       <c r="A45">
         <v>1</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="13">
         <v>3</v>
       </c>
       <c r="E45" t="s">
@@ -4810,13 +4839,13 @@
       <c r="A46">
         <v>1</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="13">
         <v>6</v>
       </c>
       <c r="E46" t="s">
@@ -4833,13 +4862,13 @@
       <c r="A47">
         <v>1</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="13">
         <v>13</v>
       </c>
       <c r="E47" t="s">
@@ -4856,13 +4885,13 @@
       <c r="A48">
         <v>1</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="13">
         <v>19</v>
       </c>
       <c r="E48" t="s">
@@ -4879,13 +4908,13 @@
       <c r="A49">
         <v>1</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="D49">
+      <c r="D49" s="13">
         <v>21</v>
       </c>
       <c r="E49" t="s">
@@ -4902,13 +4931,13 @@
       <c r="A50">
         <v>1</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="D50">
+      <c r="D50" s="13">
         <v>13</v>
       </c>
       <c r="E50" t="s">
@@ -4925,13 +4954,13 @@
       <c r="A51">
         <v>1</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="D51">
+      <c r="D51" s="13">
         <v>6</v>
       </c>
       <c r="E51" t="s">
@@ -4948,13 +4977,13 @@
       <c r="A52">
         <v>1</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="13">
         <v>0</v>
       </c>
       <c r="E52" t="s">
@@ -4971,13 +5000,13 @@
       <c r="A53">
         <v>1</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="13">
         <v>6</v>
       </c>
       <c r="E53" t="s">
@@ -4994,13 +5023,13 @@
       <c r="A54">
         <v>1</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="13">
         <v>14</v>
       </c>
       <c r="E54" t="s">
@@ -5017,13 +5046,13 @@
       <c r="A55">
         <v>1</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D55">
+      <c r="D55" s="13">
         <v>16</v>
       </c>
       <c r="E55" t="s">
@@ -5040,13 +5069,13 @@
       <c r="A56">
         <v>1</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="13">
         <v>9</v>
       </c>
       <c r="E56" t="s">
@@ -5063,13 +5092,13 @@
       <c r="A57">
         <v>1</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C57" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="13">
         <v>7</v>
       </c>
       <c r="E57" t="s">
@@ -5086,13 +5115,13 @@
       <c r="A58">
         <v>1</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="13">
         <v>20</v>
       </c>
       <c r="E58" t="s">
@@ -5109,13 +5138,13 @@
       <c r="A59">
         <v>1</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="D59">
+      <c r="D59" s="13">
         <v>30</v>
       </c>
       <c r="E59" t="s">
@@ -5132,13 +5161,13 @@
       <c r="A60">
         <v>1</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="D60">
+      <c r="D60" s="13">
         <v>17</v>
       </c>
       <c r="E60" t="s">
@@ -5155,13 +5184,13 @@
       <c r="A61">
         <v>1</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="13">
         <v>5</v>
       </c>
       <c r="E61" t="s">
@@ -5178,13 +5207,13 @@
       <c r="A62">
         <v>1</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="D62">
+      <c r="D62" s="13">
         <v>4</v>
       </c>
       <c r="E62" t="s">
@@ -5201,13 +5230,13 @@
       <c r="A63">
         <v>1</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="13">
         <v>7</v>
       </c>
       <c r="E63" t="s">
@@ -5224,13 +5253,13 @@
       <c r="A64">
         <v>1</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="13">
         <v>15</v>
       </c>
       <c r="E64" t="s">
@@ -5247,13 +5276,13 @@
       <c r="A65">
         <v>1</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="D65">
+      <c r="D65" s="13">
         <v>20</v>
       </c>
       <c r="E65" t="s">
@@ -5270,13 +5299,13 @@
       <c r="A66">
         <v>1</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C66" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="D66">
+      <c r="D66" s="13">
         <v>22</v>
       </c>
       <c r="E66" t="s">
@@ -5293,13 +5322,13 @@
       <c r="A67">
         <v>1</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C67" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="D67">
+      <c r="D67" s="13">
         <v>15</v>
       </c>
       <c r="E67" t="s">
@@ -5316,13 +5345,13 @@
       <c r="A68">
         <v>1</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C68" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D68">
+      <c r="D68" s="13">
         <v>7</v>
       </c>
       <c r="E68" t="s">
@@ -5339,13 +5368,13 @@
       <c r="A69">
         <v>1</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C69" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="D69">
+      <c r="D69" s="13">
         <v>0</v>
       </c>
       <c r="E69" t="s">
@@ -5362,13 +5391,13 @@
       <c r="A70">
         <v>1</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C70" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="D70">
+      <c r="D70" s="13">
         <v>6</v>
       </c>
       <c r="E70" t="s">
@@ -5385,13 +5414,13 @@
       <c r="A71">
         <v>1</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C71" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="D71">
+      <c r="D71" s="13">
         <v>15</v>
       </c>
       <c r="E71" t="s">
@@ -5408,13 +5437,13 @@
       <c r="A72">
         <v>1</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C72" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="D72">
+      <c r="D72" s="13">
         <v>17</v>
       </c>
       <c r="E72" t="s">
@@ -5431,13 +5460,13 @@
       <c r="A73">
         <v>1</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C73" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="D73">
+      <c r="D73" s="13">
         <v>10</v>
       </c>
       <c r="E73" t="s">
@@ -5454,13 +5483,13 @@
       <c r="A74">
         <v>1</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C74" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="D74">
+      <c r="D74" s="13">
         <v>9</v>
       </c>
       <c r="E74" t="s">
@@ -5477,13 +5506,13 @@
       <c r="A75">
         <v>1</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C75" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="D75">
+      <c r="D75" s="13">
         <v>22</v>
       </c>
       <c r="E75" t="s">
@@ -5500,13 +5529,13 @@
       <c r="A76">
         <v>1</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C76" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="D76">
+      <c r="D76" s="13">
         <v>32</v>
       </c>
       <c r="E76" t="s">
@@ -5523,13 +5552,13 @@
       <c r="A77">
         <v>1</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C77" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="D77">
+      <c r="D77" s="13">
         <v>20</v>
       </c>
       <c r="E77" t="s">
@@ -5546,13 +5575,13 @@
       <c r="A78">
         <v>1</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C78" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="D78">
+      <c r="D78" s="13">
         <v>6</v>
       </c>
       <c r="E78" t="s">
@@ -5569,13 +5598,13 @@
       <c r="A79">
         <v>1</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C79" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="D79">
+      <c r="D79" s="13">
         <v>7</v>
       </c>
       <c r="E79" t="s">
@@ -5592,13 +5621,13 @@
       <c r="A80">
         <v>1</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C80" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="D80">
+      <c r="D80" s="13">
         <v>12</v>
       </c>
       <c r="E80" t="s">
@@ -5615,13 +5644,13 @@
       <c r="A81">
         <v>1</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C81" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="D81">
+      <c r="D81" s="13">
         <v>18</v>
       </c>
       <c r="E81" t="s">
@@ -5638,13 +5667,13 @@
       <c r="A82">
         <v>1</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C82" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="D82">
+      <c r="D82" s="13">
         <v>26</v>
       </c>
       <c r="E82" t="s">
@@ -5661,13 +5690,13 @@
       <c r="A83">
         <v>1</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C83" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="D83">
+      <c r="D83" s="13">
         <v>28</v>
       </c>
       <c r="E83" t="s">
@@ -5684,13 +5713,13 @@
       <c r="A84">
         <v>1</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C84" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="D84">
+      <c r="D84" s="13">
         <v>22</v>
       </c>
       <c r="E84" t="s">
@@ -5707,13 +5736,13 @@
       <c r="A85">
         <v>1</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="C85" t="s">
+      <c r="C85" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="D85">
+      <c r="D85" s="13">
         <v>12</v>
       </c>
       <c r="E85" t="s">
@@ -5730,13 +5759,13 @@
       <c r="A86">
         <v>1</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C86" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="D86">
+      <c r="D86" s="13">
         <v>0</v>
       </c>
       <c r="E86" t="s">
@@ -5753,13 +5782,13 @@
       <c r="A87">
         <v>1</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C87" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="D87">
+      <c r="D87" s="13">
         <v>3</v>
       </c>
       <c r="E87" t="s">
@@ -5776,13 +5805,13 @@
       <c r="A88">
         <v>1</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C88" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="D88">
+      <c r="D88" s="13">
         <v>6</v>
       </c>
       <c r="E88" t="s">
@@ -5799,13 +5828,13 @@
       <c r="A89">
         <v>1</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C89" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="D89">
+      <c r="D89" s="13">
         <v>16</v>
       </c>
       <c r="E89" t="s">
@@ -5822,13 +5851,13 @@
       <c r="A90">
         <v>1</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C90" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="D90">
+      <c r="D90" s="13">
         <v>24</v>
       </c>
       <c r="E90" t="s">
@@ -5845,13 +5874,13 @@
       <c r="A91">
         <v>1</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C91" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D91">
+      <c r="D91" s="13">
         <v>26</v>
       </c>
       <c r="E91" t="s">
@@ -5868,13 +5897,13 @@
       <c r="A92">
         <v>1</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C92" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="D92">
+      <c r="D92" s="13">
         <v>24</v>
       </c>
       <c r="E92" t="s">
@@ -5891,13 +5920,13 @@
       <c r="A93">
         <v>1</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C93" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="D93">
+      <c r="D93" s="13">
         <v>28</v>
       </c>
       <c r="E93" t="s">
@@ -5914,13 +5943,13 @@
       <c r="A94">
         <v>1</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C94" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="D94">
+      <c r="D94" s="13">
         <v>24</v>
       </c>
       <c r="E94" t="s">
@@ -5937,13 +5966,13 @@
       <c r="A95">
         <v>1</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C95" t="s">
+      <c r="C95" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="D95">
+      <c r="D95" s="13">
         <v>12</v>
       </c>
       <c r="E95" t="s">
@@ -5960,13 +5989,13 @@
       <c r="A96">
         <v>1</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C96" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="D96">
+      <c r="D96" s="13">
         <v>10</v>
       </c>
       <c r="E96" t="s">
@@ -5983,13 +6012,13 @@
       <c r="A97">
         <v>1</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C97" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="D97">
+      <c r="D97" s="13">
         <v>14</v>
       </c>
       <c r="E97" t="s">
@@ -6006,13 +6035,13 @@
       <c r="A98">
         <v>1</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C98" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="D98">
+      <c r="D98" s="13">
         <v>22</v>
       </c>
       <c r="E98" t="s">
@@ -6029,13 +6058,13 @@
       <c r="A99">
         <v>1</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="C99" t="s">
+      <c r="C99" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="D99">
+      <c r="D99" s="13">
         <v>30</v>
       </c>
       <c r="E99" t="s">
@@ -6052,13 +6081,13 @@
       <c r="A100">
         <v>1</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="C100" t="s">
+      <c r="C100" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="D100">
+      <c r="D100" s="13">
         <v>32</v>
       </c>
       <c r="E100" t="s">
@@ -6075,13 +6104,13 @@
       <c r="A101">
         <v>1</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C101" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="D101">
+      <c r="D101" s="13">
         <v>26</v>
       </c>
       <c r="E101" t="s">
@@ -6098,13 +6127,13 @@
       <c r="A102">
         <v>1</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C102" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="D102">
+      <c r="D102" s="13">
         <v>16</v>
       </c>
       <c r="E102" t="s">
@@ -6121,13 +6150,13 @@
       <c r="A103">
         <v>1</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C103" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="D103">
+      <c r="D103" s="13">
         <v>0</v>
       </c>
       <c r="E103" t="s">
@@ -6144,13 +6173,13 @@
       <c r="A104">
         <v>1</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="C104" t="s">
+      <c r="C104" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="D104">
+      <c r="D104" s="13">
         <v>3</v>
       </c>
       <c r="E104" t="s">
@@ -6167,13 +6196,13 @@
       <c r="A105">
         <v>1</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C105" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="D105">
+      <c r="D105" s="13">
         <v>5</v>
       </c>
       <c r="E105" t="s">
@@ -6190,13 +6219,13 @@
       <c r="A106">
         <v>1</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="C106" t="s">
+      <c r="C106" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="D106">
+      <c r="D106" s="13">
         <v>14</v>
       </c>
       <c r="E106" t="s">
@@ -6213,13 +6242,13 @@
       <c r="A107">
         <v>1</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="C107" t="s">
+      <c r="C107" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="D107">
+      <c r="D107" s="13">
         <v>20</v>
       </c>
       <c r="E107" t="s">
@@ -6236,13 +6265,13 @@
       <c r="A108">
         <v>1</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="C108" t="s">
+      <c r="C108" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="D108">
+      <c r="D108" s="13">
         <v>22</v>
       </c>
       <c r="E108" t="s">
@@ -6259,13 +6288,13 @@
       <c r="A109">
         <v>1</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="C109" t="s">
+      <c r="C109" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="D109">
+      <c r="D109" s="13">
         <v>26</v>
       </c>
       <c r="E109" t="s">
@@ -6282,13 +6311,13 @@
       <c r="A110">
         <v>1</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="C110" t="s">
+      <c r="C110" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="D110">
+      <c r="D110" s="13">
         <v>28</v>
       </c>
       <c r="E110" t="s">
@@ -6305,13 +6334,13 @@
       <c r="A111">
         <v>1</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="C111" t="s">
+      <c r="C111" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="D111">
+      <c r="D111" s="13">
         <v>24</v>
       </c>
       <c r="E111" t="s">
@@ -6328,13 +6357,13 @@
       <c r="A112">
         <v>1</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="C112" t="s">
+      <c r="C112" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="D112">
+      <c r="D112" s="13">
         <v>14</v>
       </c>
       <c r="E112" t="s">
@@ -6347,17 +6376,17 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>1</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="C113" t="s">
+      <c r="C113" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="D113">
+      <c r="D113" s="13">
         <v>10</v>
       </c>
       <c r="E113" t="s">
@@ -6370,17 +6399,17 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>1</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="C114" t="s">
+      <c r="C114" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="D114">
+      <c r="D114" s="13">
         <v>10</v>
       </c>
       <c r="E114" t="s">
@@ -6393,17 +6422,17 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>1</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="C115" t="s">
+      <c r="C115" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="D115">
+      <c r="D115" s="13">
         <v>18</v>
       </c>
       <c r="E115" t="s">
@@ -6416,17 +6445,17 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>1</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="C116" t="s">
+      <c r="C116" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="D116">
+      <c r="D116" s="13">
         <v>22</v>
       </c>
       <c r="E116" t="s">
@@ -6439,17 +6468,17 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>1</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="C117" t="s">
+      <c r="C117" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="D117">
+      <c r="D117" s="13">
         <v>24</v>
       </c>
       <c r="E117" t="s">
@@ -6462,17 +6491,17 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>1</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="C118" t="s">
+      <c r="C118" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="D118">
+      <c r="D118" s="13">
         <v>18</v>
       </c>
       <c r="E118" t="s">
@@ -6485,17 +6514,17 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>1</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="C119" t="s">
+      <c r="C119" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="D119">
+      <c r="D119" s="13">
         <v>10</v>
       </c>
       <c r="E119" t="s">
@@ -6508,17 +6537,17 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>1</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="C120" t="s">
+      <c r="C120" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="D120">
+      <c r="D120" s="13">
         <v>0</v>
       </c>
       <c r="E120" t="s">
@@ -6531,18 +6560,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>2</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C121" t="s">
+      <c r="C121" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="D121">
-        <v>5</v>
+      <c r="D121" s="13">
+        <v>2.5</v>
       </c>
       <c r="E121" t="s">
         <v>5</v>
@@ -6553,19 +6582,20 @@
       <c r="G121">
         <v>1.3</v>
       </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J121" s="12"/>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>2</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C122" t="s">
+      <c r="C122" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D122">
-        <v>12</v>
+      <c r="D122" s="13">
+        <v>6</v>
       </c>
       <c r="E122" t="s">
         <v>5</v>
@@ -6576,19 +6606,20 @@
       <c r="G122">
         <v>1.3</v>
       </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J122" s="12"/>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>2</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C123" t="s">
+      <c r="C123" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D123">
-        <v>14</v>
+      <c r="D123" s="13">
+        <v>7</v>
       </c>
       <c r="E123" t="s">
         <v>5</v>
@@ -6599,19 +6630,20 @@
       <c r="G123">
         <v>1.3</v>
       </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J123" s="12"/>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>2</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C124" t="s">
+      <c r="C124" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D124">
-        <v>8</v>
+      <c r="D124" s="13">
+        <v>4</v>
       </c>
       <c r="E124" t="s">
         <v>5</v>
@@ -6622,19 +6654,20 @@
       <c r="G124">
         <v>1.3</v>
       </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J124" s="12"/>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>2</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C125" t="s">
+      <c r="C125" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="D125">
-        <v>6</v>
+      <c r="D125" s="13">
+        <v>3</v>
       </c>
       <c r="E125" t="s">
         <v>5</v>
@@ -6645,19 +6678,20 @@
       <c r="G125">
         <v>2.2000000000000002</v>
       </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J125" s="12"/>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>2</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C126" t="s">
+      <c r="C126" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D126">
-        <v>18</v>
+      <c r="D126" s="13">
+        <v>9</v>
       </c>
       <c r="E126" t="s">
         <v>5</v>
@@ -6668,19 +6702,20 @@
       <c r="G126">
         <v>2.2000000000000002</v>
       </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J126" s="12"/>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>2</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C127" t="s">
+      <c r="C127" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="D127">
-        <v>28</v>
+      <c r="D127" s="13">
+        <v>14</v>
       </c>
       <c r="E127" t="s">
         <v>5</v>
@@ -6691,19 +6726,20 @@
       <c r="G127">
         <v>2.2000000000000002</v>
       </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J127" s="12"/>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>2</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="C128" t="s">
+      <c r="C128" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="D128">
-        <v>16</v>
+      <c r="D128" s="13">
+        <v>8</v>
       </c>
       <c r="E128" t="s">
         <v>5</v>
@@ -6714,19 +6750,20 @@
       <c r="G128">
         <v>2.2000000000000002</v>
       </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J128" s="12"/>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>2</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C129" t="s">
+      <c r="C129" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D129">
-        <v>4</v>
+      <c r="D129" s="13">
+        <v>2</v>
       </c>
       <c r="E129" t="s">
         <v>5</v>
@@ -6737,19 +6774,20 @@
       <c r="G129">
         <v>1.8</v>
       </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J129" s="12"/>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>2</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C130" t="s">
+      <c r="C130" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="D130">
-        <v>3</v>
+      <c r="D130" s="13">
+        <v>1.5</v>
       </c>
       <c r="E130" t="s">
         <v>5</v>
@@ -6760,19 +6798,20 @@
       <c r="G130">
         <v>1.8</v>
       </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J130" s="12"/>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>2</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C131" t="s">
+      <c r="C131" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D131">
-        <v>5</v>
+      <c r="D131" s="13">
+        <v>2.5</v>
       </c>
       <c r="E131" t="s">
         <v>5</v>
@@ -6783,19 +6822,20 @@
       <c r="G131">
         <v>1.8</v>
       </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J131" s="12"/>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>2</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="C132" t="s">
+      <c r="C132" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D132">
-        <v>12</v>
+      <c r="D132" s="13">
+        <v>6</v>
       </c>
       <c r="E132" t="s">
         <v>5</v>
@@ -6806,19 +6846,20 @@
       <c r="G132">
         <v>1.8</v>
       </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J132" s="12"/>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>2</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C133" t="s">
+      <c r="C133" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D133">
-        <v>18</v>
+      <c r="D133" s="13">
+        <v>9</v>
       </c>
       <c r="E133" t="s">
         <v>5</v>
@@ -6829,19 +6870,20 @@
       <c r="G133">
         <v>2.8</v>
       </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J133" s="12"/>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>2</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C134" t="s">
+      <c r="C134" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D134">
-        <v>20</v>
+      <c r="D134" s="13">
+        <v>10</v>
       </c>
       <c r="E134" t="s">
         <v>5</v>
@@ -6852,19 +6894,20 @@
       <c r="G134">
         <v>2.8</v>
       </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J134" s="12"/>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>2</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C135" t="s">
+      <c r="C135" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="D135">
-        <v>12</v>
+      <c r="D135" s="13">
+        <v>6</v>
       </c>
       <c r="E135" t="s">
         <v>5</v>
@@ -6875,19 +6918,20 @@
       <c r="G135">
         <v>2.8</v>
       </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J135" s="12"/>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>2</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C136" t="s">
+      <c r="C136" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="D136">
-        <v>5</v>
+      <c r="D136" s="13">
+        <v>2.5</v>
       </c>
       <c r="E136" t="s">
         <v>5</v>
@@ -6898,18 +6942,19 @@
       <c r="G136">
         <v>2.8</v>
       </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J136" s="12"/>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>2</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="C137" t="s">
+      <c r="C137" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="D137">
+      <c r="D137" s="13">
         <v>0</v>
       </c>
       <c r="E137" t="s">
@@ -6921,19 +6966,20 @@
       <c r="G137">
         <v>2</v>
       </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J137" s="12"/>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>2</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C138" t="s">
+      <c r="C138" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="D138">
-        <v>5</v>
+      <c r="D138" s="13">
+        <v>2.5</v>
       </c>
       <c r="E138" t="s">
         <v>6</v>
@@ -6944,19 +6990,20 @@
       <c r="G138">
         <v>1.3</v>
       </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J138" s="12"/>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>2</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B139" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="C139" t="s">
+      <c r="C139" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="D139">
-        <v>14</v>
+      <c r="D139" s="13">
+        <v>7</v>
       </c>
       <c r="E139" t="s">
         <v>6</v>
@@ -6967,19 +7014,20 @@
       <c r="G139">
         <v>1.3</v>
       </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J139" s="12"/>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>2</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C140" t="s">
+      <c r="C140" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D140">
-        <v>15</v>
+      <c r="D140" s="13">
+        <v>7.5</v>
       </c>
       <c r="E140" t="s">
         <v>6</v>
@@ -6990,19 +7038,20 @@
       <c r="G140">
         <v>1.3</v>
       </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J140" s="12"/>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>2</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B141" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C141" t="s">
+      <c r="C141" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D141">
-        <v>8</v>
+      <c r="D141" s="13">
+        <v>4</v>
       </c>
       <c r="E141" t="s">
         <v>6</v>
@@ -7013,19 +7062,20 @@
       <c r="G141">
         <v>1.3</v>
       </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J141" s="12"/>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>2</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B142" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="C142" t="s">
+      <c r="C142" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="D142">
-        <v>6</v>
+      <c r="D142" s="13">
+        <v>3</v>
       </c>
       <c r="E142" t="s">
         <v>6</v>
@@ -7036,19 +7086,20 @@
       <c r="G142">
         <v>2.2000000000000002</v>
       </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J142" s="12"/>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>2</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B143" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="C143" t="s">
+      <c r="C143" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="D143">
-        <v>19</v>
+      <c r="D143" s="13">
+        <v>9.5</v>
       </c>
       <c r="E143" t="s">
         <v>6</v>
@@ -7059,19 +7110,20 @@
       <c r="G143">
         <v>2.2000000000000002</v>
       </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J143" s="12"/>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>2</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B144" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="C144" t="s">
+      <c r="C144" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="D144">
-        <v>29</v>
+      <c r="D144" s="13">
+        <v>14.5</v>
       </c>
       <c r="E144" t="s">
         <v>6</v>
@@ -7082,19 +7134,20 @@
       <c r="G144">
         <v>2.2000000000000002</v>
       </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J144" s="12"/>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>2</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B145" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="C145" t="s">
+      <c r="C145" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D145">
-        <v>16</v>
+      <c r="D145" s="13">
+        <v>8</v>
       </c>
       <c r="E145" t="s">
         <v>6</v>
@@ -7105,19 +7158,20 @@
       <c r="G145">
         <v>2.2000000000000002</v>
       </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J145" s="12"/>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>2</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B146" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="C146" t="s">
+      <c r="C146" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D146">
-        <v>4</v>
+      <c r="D146" s="13">
+        <v>2</v>
       </c>
       <c r="E146" t="s">
         <v>6</v>
@@ -7128,19 +7182,20 @@
       <c r="G146">
         <v>1.8</v>
       </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J146" s="12"/>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>2</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B147" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="C147" t="s">
+      <c r="C147" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="D147">
-        <v>3</v>
+      <c r="D147" s="13">
+        <v>1.5</v>
       </c>
       <c r="E147" t="s">
         <v>6</v>
@@ -7151,19 +7206,20 @@
       <c r="G147">
         <v>1.8</v>
       </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J147" s="12"/>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>2</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B148" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C148" t="s">
+      <c r="C148" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="D148">
-        <v>6</v>
+      <c r="D148" s="13">
+        <v>3</v>
       </c>
       <c r="E148" t="s">
         <v>6</v>
@@ -7174,19 +7230,20 @@
       <c r="G148">
         <v>1.8</v>
       </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J148" s="12"/>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>2</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B149" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="C149" t="s">
+      <c r="C149" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D149">
-        <v>12</v>
+      <c r="D149" s="13">
+        <v>6</v>
       </c>
       <c r="E149" t="s">
         <v>6</v>
@@ -7197,19 +7254,20 @@
       <c r="G149">
         <v>1.8</v>
       </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J149" s="12"/>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>2</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B150" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C150" t="s">
+      <c r="C150" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="D150">
-        <v>19</v>
+      <c r="D150" s="13">
+        <v>9.5</v>
       </c>
       <c r="E150" t="s">
         <v>6</v>
@@ -7220,19 +7278,20 @@
       <c r="G150">
         <v>2.8</v>
       </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J150" s="12"/>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>2</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B151" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C151" t="s">
+      <c r="C151" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="D151">
-        <v>25</v>
+      <c r="D151" s="13">
+        <v>12.5</v>
       </c>
       <c r="E151" t="s">
         <v>6</v>
@@ -7243,19 +7302,20 @@
       <c r="G151">
         <v>2.8</v>
       </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J151" s="12"/>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>2</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B152" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="C152" t="s">
+      <c r="C152" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D152">
-        <v>12</v>
+      <c r="D152" s="13">
+        <v>6</v>
       </c>
       <c r="E152" t="s">
         <v>6</v>
@@ -7266,19 +7326,20 @@
       <c r="G152">
         <v>2.8</v>
       </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J152" s="12"/>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>2</v>
       </c>
-      <c r="B153" t="s">
+      <c r="B153" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C153" t="s">
+      <c r="C153" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="D153">
-        <v>5</v>
+      <c r="D153" s="13">
+        <v>2.5</v>
       </c>
       <c r="E153" t="s">
         <v>6</v>
@@ -7289,18 +7350,19 @@
       <c r="G153">
         <v>2.8</v>
       </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J153" s="12"/>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>2</v>
       </c>
-      <c r="B154" t="s">
+      <c r="B154" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="C154" t="s">
+      <c r="C154" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="D154">
+      <c r="D154" s="13">
         <v>0</v>
       </c>
       <c r="E154" t="s">
@@ -7312,19 +7374,20 @@
       <c r="G154">
         <v>2</v>
       </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J154" s="12"/>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>2</v>
       </c>
-      <c r="B155" t="s">
+      <c r="B155" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="C155" t="s">
+      <c r="C155" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="D155">
-        <v>5</v>
+      <c r="D155" s="13">
+        <v>2.5</v>
       </c>
       <c r="E155" t="s">
         <v>7</v>
@@ -7335,19 +7398,20 @@
       <c r="G155">
         <v>1.3</v>
       </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J155" s="12"/>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>2</v>
       </c>
-      <c r="B156" t="s">
+      <c r="B156" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="C156" t="s">
+      <c r="C156" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="D156">
-        <v>13</v>
+      <c r="D156" s="13">
+        <v>6.5</v>
       </c>
       <c r="E156" t="s">
         <v>7</v>
@@ -7358,19 +7422,20 @@
       <c r="G156">
         <v>1.3</v>
       </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J156" s="12"/>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>2</v>
       </c>
-      <c r="B157" t="s">
+      <c r="B157" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="C157" t="s">
+      <c r="C157" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="D157">
-        <v>15</v>
+      <c r="D157" s="13">
+        <v>7.5</v>
       </c>
       <c r="E157" t="s">
         <v>7</v>
@@ -7381,19 +7446,20 @@
       <c r="G157">
         <v>1.3</v>
       </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J157" s="12"/>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>2</v>
       </c>
-      <c r="B158" t="s">
+      <c r="B158" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="C158" t="s">
+      <c r="C158" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="D158">
-        <v>8</v>
+      <c r="D158" s="13">
+        <v>4</v>
       </c>
       <c r="E158" t="s">
         <v>7</v>
@@ -7404,19 +7470,20 @@
       <c r="G158">
         <v>1.3</v>
       </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J158" s="12"/>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>2</v>
       </c>
-      <c r="B159" t="s">
+      <c r="B159" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="C159" t="s">
+      <c r="C159" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="D159">
-        <v>6</v>
+      <c r="D159" s="13">
+        <v>3</v>
       </c>
       <c r="E159" t="s">
         <v>7</v>
@@ -7427,19 +7494,20 @@
       <c r="G159">
         <v>2.2000000000000002</v>
       </c>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J159" s="12"/>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>2</v>
       </c>
-      <c r="B160" t="s">
+      <c r="B160" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="C160" t="s">
+      <c r="C160" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="D160">
-        <v>20</v>
+      <c r="D160" s="13">
+        <v>10</v>
       </c>
       <c r="E160" t="s">
         <v>7</v>
@@ -7450,19 +7518,20 @@
       <c r="G160">
         <v>2.2000000000000002</v>
       </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J160" s="12"/>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>2</v>
       </c>
-      <c r="B161" t="s">
+      <c r="B161" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="C161" t="s">
+      <c r="C161" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="D161">
-        <v>29</v>
+      <c r="D161" s="13">
+        <v>14.5</v>
       </c>
       <c r="E161" t="s">
         <v>7</v>
@@ -7473,19 +7542,20 @@
       <c r="G161">
         <v>2.2000000000000002</v>
       </c>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J161" s="12"/>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>2</v>
       </c>
-      <c r="B162" t="s">
+      <c r="B162" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="C162" t="s">
+      <c r="C162" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D162">
-        <v>16</v>
+      <c r="D162" s="13">
+        <v>8</v>
       </c>
       <c r="E162" t="s">
         <v>7</v>
@@ -7496,19 +7566,20 @@
       <c r="G162">
         <v>2.2000000000000002</v>
       </c>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J162" s="12"/>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>2</v>
       </c>
-      <c r="B163" t="s">
+      <c r="B163" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="C163" t="s">
+      <c r="C163" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="D163">
-        <v>4</v>
+      <c r="D163" s="13">
+        <v>2</v>
       </c>
       <c r="E163" t="s">
         <v>7</v>
@@ -7519,19 +7590,20 @@
       <c r="G163">
         <v>1.8</v>
       </c>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J163" s="12"/>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>2</v>
       </c>
-      <c r="B164" t="s">
+      <c r="B164" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="C164" t="s">
+      <c r="C164" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="D164">
-        <v>3</v>
+      <c r="D164" s="13">
+        <v>1.5</v>
       </c>
       <c r="E164" t="s">
         <v>7</v>
@@ -7542,19 +7614,20 @@
       <c r="G164">
         <v>1.8</v>
       </c>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J164" s="12"/>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>2</v>
       </c>
-      <c r="B165" t="s">
+      <c r="B165" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="C165" t="s">
+      <c r="C165" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="D165">
-        <v>6</v>
+      <c r="D165" s="13">
+        <v>3</v>
       </c>
       <c r="E165" t="s">
         <v>7</v>
@@ -7565,19 +7638,20 @@
       <c r="G165">
         <v>1.8</v>
       </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J165" s="12"/>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>2</v>
       </c>
-      <c r="B166" t="s">
+      <c r="B166" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="C166" t="s">
+      <c r="C166" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="D166">
-        <v>13</v>
+      <c r="D166" s="13">
+        <v>6.5</v>
       </c>
       <c r="E166" t="s">
         <v>7</v>
@@ -7588,19 +7662,20 @@
       <c r="G166">
         <v>1.8</v>
       </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J166" s="12"/>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>2</v>
       </c>
-      <c r="B167" t="s">
+      <c r="B167" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="C167" t="s">
+      <c r="C167" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="D167">
-        <v>19</v>
+      <c r="D167" s="13">
+        <v>9.5</v>
       </c>
       <c r="E167" t="s">
         <v>7</v>
@@ -7611,19 +7686,20 @@
       <c r="G167">
         <v>2.8</v>
       </c>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J167" s="12"/>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>2</v>
       </c>
-      <c r="B168" t="s">
+      <c r="B168" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="C168" t="s">
+      <c r="C168" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="D168">
-        <v>21</v>
+      <c r="D168" s="13">
+        <v>10.5</v>
       </c>
       <c r="E168" t="s">
         <v>7</v>
@@ -7634,19 +7710,20 @@
       <c r="G168">
         <v>2.8</v>
       </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J168" s="12"/>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>2</v>
       </c>
-      <c r="B169" t="s">
+      <c r="B169" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="C169" t="s">
+      <c r="C169" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="D169">
-        <v>13</v>
+      <c r="D169" s="13">
+        <v>6.5</v>
       </c>
       <c r="E169" t="s">
         <v>7</v>
@@ -7657,19 +7734,20 @@
       <c r="G169">
         <v>2.8</v>
       </c>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J169" s="12"/>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>2</v>
       </c>
-      <c r="B170" t="s">
+      <c r="B170" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="C170" t="s">
+      <c r="C170" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="D170">
-        <v>6</v>
+      <c r="D170" s="13">
+        <v>3</v>
       </c>
       <c r="E170" t="s">
         <v>7</v>
@@ -7680,18 +7758,19 @@
       <c r="G170">
         <v>2.8</v>
       </c>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J170" s="12"/>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>2</v>
       </c>
-      <c r="B171" t="s">
+      <c r="B171" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="C171" t="s">
+      <c r="C171" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="D171">
+      <c r="D171" s="13">
         <v>0</v>
       </c>
       <c r="E171" t="s">
@@ -7703,19 +7782,20 @@
       <c r="G171">
         <v>2</v>
       </c>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J171" s="12"/>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>2</v>
       </c>
-      <c r="B172" t="s">
+      <c r="B172" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="C172" t="s">
+      <c r="C172" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="D172">
-        <v>6</v>
+      <c r="D172" s="13">
+        <v>3</v>
       </c>
       <c r="E172" t="s">
         <v>8</v>
@@ -7726,19 +7806,20 @@
       <c r="G172">
         <v>1.3</v>
       </c>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J172" s="12"/>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>2</v>
       </c>
-      <c r="B173" t="s">
+      <c r="B173" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="C173" t="s">
+      <c r="C173" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="D173">
-        <v>14</v>
+      <c r="D173" s="13">
+        <v>7</v>
       </c>
       <c r="E173" t="s">
         <v>8</v>
@@ -7749,19 +7830,20 @@
       <c r="G173">
         <v>1.3</v>
       </c>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J173" s="12"/>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>2</v>
       </c>
-      <c r="B174" t="s">
+      <c r="B174" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="C174" t="s">
+      <c r="C174" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D174">
-        <v>16</v>
+      <c r="D174" s="13">
+        <v>8</v>
       </c>
       <c r="E174" t="s">
         <v>8</v>
@@ -7772,19 +7854,20 @@
       <c r="G174">
         <v>1.3</v>
       </c>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J174" s="12"/>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>2</v>
       </c>
-      <c r="B175" t="s">
+      <c r="B175" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="C175" t="s">
+      <c r="C175" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="D175">
-        <v>9</v>
+      <c r="D175" s="13">
+        <v>4.5</v>
       </c>
       <c r="E175" t="s">
         <v>8</v>
@@ -7795,19 +7878,20 @@
       <c r="G175">
         <v>1.3</v>
       </c>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J175" s="12"/>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>2</v>
       </c>
-      <c r="B176" t="s">
+      <c r="B176" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="C176" t="s">
+      <c r="C176" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="D176">
-        <v>7</v>
+      <c r="D176" s="13">
+        <v>3.5</v>
       </c>
       <c r="E176" t="s">
         <v>8</v>
@@ -7818,19 +7902,20 @@
       <c r="G176">
         <v>2.2000000000000002</v>
       </c>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J176" s="12"/>
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A177">
         <v>2</v>
       </c>
-      <c r="B177" t="s">
+      <c r="B177" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="C177" t="s">
+      <c r="C177" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="D177">
-        <v>20</v>
+      <c r="D177" s="13">
+        <v>10</v>
       </c>
       <c r="E177" t="s">
         <v>8</v>
@@ -7841,19 +7926,20 @@
       <c r="G177">
         <v>2.2000000000000002</v>
       </c>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J177" s="12"/>
+    </row>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>2</v>
       </c>
-      <c r="B178" t="s">
+      <c r="B178" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="C178" t="s">
+      <c r="C178" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="D178">
-        <v>30</v>
+      <c r="D178" s="13">
+        <v>15</v>
       </c>
       <c r="E178" t="s">
         <v>8</v>
@@ -7864,19 +7950,20 @@
       <c r="G178">
         <v>2.2000000000000002</v>
       </c>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J178" s="12"/>
+    </row>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A179">
         <v>2</v>
       </c>
-      <c r="B179" t="s">
+      <c r="B179" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="C179" t="s">
+      <c r="C179" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="D179">
-        <v>17</v>
+      <c r="D179" s="13">
+        <v>8.5</v>
       </c>
       <c r="E179" t="s">
         <v>8</v>
@@ -7887,19 +7974,20 @@
       <c r="G179">
         <v>2.2000000000000002</v>
       </c>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J179" s="12"/>
+    </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A180">
         <v>2</v>
       </c>
-      <c r="B180" t="s">
+      <c r="B180" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="C180" t="s">
+      <c r="C180" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="D180">
-        <v>5</v>
+      <c r="D180" s="13">
+        <v>2.5</v>
       </c>
       <c r="E180" t="s">
         <v>8</v>
@@ -7910,19 +7998,20 @@
       <c r="G180">
         <v>1.8</v>
       </c>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J180" s="12"/>
+    </row>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A181">
         <v>2</v>
       </c>
-      <c r="B181" t="s">
+      <c r="B181" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="C181" t="s">
+      <c r="C181" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="D181">
-        <v>4</v>
+      <c r="D181" s="13">
+        <v>2</v>
       </c>
       <c r="E181" t="s">
         <v>8</v>
@@ -7933,19 +8022,20 @@
       <c r="G181">
         <v>1.8</v>
       </c>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J181" s="12"/>
+    </row>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A182">
         <v>2</v>
       </c>
-      <c r="B182" t="s">
+      <c r="B182" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="C182" t="s">
+      <c r="C182" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="D182">
-        <v>7</v>
+      <c r="D182" s="13">
+        <v>3.5</v>
       </c>
       <c r="E182" t="s">
         <v>8</v>
@@ -7956,19 +8046,20 @@
       <c r="G182">
         <v>1.8</v>
       </c>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J182" s="12"/>
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A183">
         <v>2</v>
       </c>
-      <c r="B183" t="s">
+      <c r="B183" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="C183" t="s">
+      <c r="C183" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="D183">
-        <v>15</v>
+      <c r="D183" s="13">
+        <v>7.5</v>
       </c>
       <c r="E183" t="s">
         <v>8</v>
@@ -7979,19 +8070,20 @@
       <c r="G183">
         <v>1.8</v>
       </c>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J183" s="12"/>
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>2</v>
       </c>
-      <c r="B184" t="s">
+      <c r="B184" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="C184" t="s">
+      <c r="C184" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="D184">
-        <v>20</v>
+      <c r="D184" s="13">
+        <v>10</v>
       </c>
       <c r="E184" t="s">
         <v>8</v>
@@ -8002,19 +8094,20 @@
       <c r="G184">
         <v>2.8</v>
       </c>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J184" s="12"/>
+    </row>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>2</v>
       </c>
-      <c r="B185" t="s">
+      <c r="B185" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="C185" t="s">
+      <c r="C185" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="D185">
-        <v>22</v>
+      <c r="D185" s="13">
+        <v>11</v>
       </c>
       <c r="E185" t="s">
         <v>8</v>
@@ -8025,19 +8118,20 @@
       <c r="G185">
         <v>2.8</v>
       </c>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J185" s="12"/>
+    </row>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A186">
         <v>2</v>
       </c>
-      <c r="B186" t="s">
+      <c r="B186" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="C186" t="s">
+      <c r="C186" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="D186">
-        <v>15</v>
+      <c r="D186" s="13">
+        <v>7.5</v>
       </c>
       <c r="E186" t="s">
         <v>8</v>
@@ -8048,19 +8142,20 @@
       <c r="G186">
         <v>2.8</v>
       </c>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J186" s="12"/>
+    </row>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A187">
         <v>2</v>
       </c>
-      <c r="B187" t="s">
+      <c r="B187" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="C187" t="s">
+      <c r="C187" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D187">
-        <v>7</v>
+      <c r="D187" s="13">
+        <v>3.5</v>
       </c>
       <c r="E187" t="s">
         <v>8</v>
@@ -8071,18 +8166,19 @@
       <c r="G187">
         <v>2.8</v>
       </c>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J187" s="12"/>
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A188">
         <v>2</v>
       </c>
-      <c r="B188" t="s">
+      <c r="B188" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="C188" t="s">
+      <c r="C188" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="D188">
+      <c r="D188" s="13">
         <v>0</v>
       </c>
       <c r="E188" t="s">
@@ -8094,19 +8190,20 @@
       <c r="G188">
         <v>2</v>
       </c>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J188" s="12"/>
+    </row>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A189">
         <v>2</v>
       </c>
-      <c r="B189" t="s">
+      <c r="B189" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="C189" t="s">
+      <c r="C189" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="D189">
-        <v>6</v>
+      <c r="D189" s="13">
+        <v>3</v>
       </c>
       <c r="E189" t="s">
         <v>9</v>
@@ -8117,19 +8214,20 @@
       <c r="G189">
         <v>1.3</v>
       </c>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J189" s="12"/>
+    </row>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A190">
         <v>2</v>
       </c>
-      <c r="B190" t="s">
+      <c r="B190" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="C190" t="s">
+      <c r="C190" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="D190">
-        <v>15</v>
+      <c r="D190" s="13">
+        <v>7.5</v>
       </c>
       <c r="E190" t="s">
         <v>9</v>
@@ -8140,19 +8238,20 @@
       <c r="G190">
         <v>1.3</v>
       </c>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J190" s="12"/>
+    </row>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A191">
         <v>2</v>
       </c>
-      <c r="B191" t="s">
+      <c r="B191" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="C191" t="s">
+      <c r="C191" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="D191">
-        <v>17</v>
+      <c r="D191" s="13">
+        <v>8.5</v>
       </c>
       <c r="E191" t="s">
         <v>9</v>
@@ -8163,19 +8262,20 @@
       <c r="G191">
         <v>1.3</v>
       </c>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J191" s="12"/>
+    </row>
+    <row r="192" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A192">
         <v>2</v>
       </c>
-      <c r="B192" t="s">
+      <c r="B192" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="C192" t="s">
+      <c r="C192" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="D192">
-        <v>10</v>
+      <c r="D192" s="13">
+        <v>5</v>
       </c>
       <c r="E192" t="s">
         <v>9</v>
@@ -8186,19 +8286,20 @@
       <c r="G192">
         <v>1.3</v>
       </c>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J192" s="12"/>
+    </row>
+    <row r="193" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A193">
         <v>2</v>
       </c>
-      <c r="B193" t="s">
+      <c r="B193" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="C193" t="s">
+      <c r="C193" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="D193">
-        <v>9</v>
+      <c r="D193" s="13">
+        <v>4.5</v>
       </c>
       <c r="E193" t="s">
         <v>9</v>
@@ -8209,19 +8310,20 @@
       <c r="G193">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J193" s="12"/>
+    </row>
+    <row r="194" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A194">
         <v>2</v>
       </c>
-      <c r="B194" t="s">
+      <c r="B194" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="C194" t="s">
+      <c r="C194" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="D194">
-        <v>22</v>
+      <c r="D194" s="13">
+        <v>11</v>
       </c>
       <c r="E194" t="s">
         <v>9</v>
@@ -8232,19 +8334,20 @@
       <c r="G194">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J194" s="12"/>
+    </row>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A195">
         <v>2</v>
       </c>
-      <c r="B195" t="s">
+      <c r="B195" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="C195" t="s">
+      <c r="C195" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="D195">
-        <v>32</v>
+      <c r="D195" s="13">
+        <v>16</v>
       </c>
       <c r="E195" t="s">
         <v>9</v>
@@ -8255,19 +8358,20 @@
       <c r="G195">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J195" s="12"/>
+    </row>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A196">
         <v>2</v>
       </c>
-      <c r="B196" t="s">
+      <c r="B196" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="C196" t="s">
+      <c r="C196" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="D196">
-        <v>20</v>
+      <c r="D196" s="13">
+        <v>10</v>
       </c>
       <c r="E196" t="s">
         <v>9</v>
@@ -8278,19 +8382,20 @@
       <c r="G196">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J196" s="12"/>
+    </row>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A197">
         <v>2</v>
       </c>
-      <c r="B197" t="s">
+      <c r="B197" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="C197" t="s">
+      <c r="C197" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="D197">
-        <v>6</v>
+      <c r="D197" s="13">
+        <v>3</v>
       </c>
       <c r="E197" t="s">
         <v>9</v>
@@ -8301,19 +8406,20 @@
       <c r="G197">
         <v>2</v>
       </c>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J197" s="12"/>
+    </row>
+    <row r="198" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A198">
         <v>2</v>
       </c>
-      <c r="B198" t="s">
+      <c r="B198" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="C198" t="s">
+      <c r="C198" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="D198">
-        <v>7</v>
+      <c r="D198" s="13">
+        <v>3.5</v>
       </c>
       <c r="E198" t="s">
         <v>9</v>
@@ -8324,19 +8430,20 @@
       <c r="G198">
         <v>2</v>
       </c>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J198" s="12"/>
+    </row>
+    <row r="199" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A199">
         <v>2</v>
       </c>
-      <c r="B199" t="s">
+      <c r="B199" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="C199" t="s">
+      <c r="C199" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="D199">
-        <v>12</v>
+      <c r="D199" s="13">
+        <v>6</v>
       </c>
       <c r="E199" t="s">
         <v>9</v>
@@ -8347,19 +8454,20 @@
       <c r="G199">
         <v>2</v>
       </c>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J199" s="12"/>
+    </row>
+    <row r="200" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A200">
         <v>2</v>
       </c>
-      <c r="B200" t="s">
+      <c r="B200" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="C200" t="s">
+      <c r="C200" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="D200">
-        <v>18</v>
+      <c r="D200" s="13">
+        <v>9</v>
       </c>
       <c r="E200" t="s">
         <v>9</v>
@@ -8370,19 +8478,20 @@
       <c r="G200">
         <v>2</v>
       </c>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J200" s="12"/>
+    </row>
+    <row r="201" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A201">
         <v>2</v>
       </c>
-      <c r="B201" t="s">
+      <c r="B201" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="C201" t="s">
+      <c r="C201" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="D201">
-        <v>26</v>
+      <c r="D201" s="13">
+        <v>13</v>
       </c>
       <c r="E201" t="s">
         <v>9</v>
@@ -8393,19 +8502,20 @@
       <c r="G201">
         <v>3.8</v>
       </c>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J201" s="12"/>
+    </row>
+    <row r="202" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A202">
         <v>2</v>
       </c>
-      <c r="B202" t="s">
+      <c r="B202" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="C202" t="s">
+      <c r="C202" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="D202">
-        <v>28</v>
+      <c r="D202" s="13">
+        <v>14</v>
       </c>
       <c r="E202" t="s">
         <v>9</v>
@@ -8416,19 +8526,20 @@
       <c r="G202">
         <v>3.8</v>
       </c>
-    </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J202" s="12"/>
+    </row>
+    <row r="203" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A203">
         <v>2</v>
       </c>
-      <c r="B203" t="s">
+      <c r="B203" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="C203" t="s">
+      <c r="C203" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="D203">
-        <v>22</v>
+      <c r="D203" s="13">
+        <v>11</v>
       </c>
       <c r="E203" t="s">
         <v>9</v>
@@ -8439,19 +8550,20 @@
       <c r="G203">
         <v>3.8</v>
       </c>
-    </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J203" s="12"/>
+    </row>
+    <row r="204" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A204">
         <v>2</v>
       </c>
-      <c r="B204" t="s">
+      <c r="B204" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="C204" t="s">
+      <c r="C204" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="D204">
-        <v>12</v>
+      <c r="D204" s="13">
+        <v>6</v>
       </c>
       <c r="E204" t="s">
         <v>9</v>
@@ -8462,18 +8574,19 @@
       <c r="G204">
         <v>3.8</v>
       </c>
-    </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J204" s="12"/>
+    </row>
+    <row r="205" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A205">
         <v>2</v>
       </c>
-      <c r="B205" t="s">
+      <c r="B205" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="C205" t="s">
+      <c r="C205" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="D205">
+      <c r="D205" s="13">
         <v>0</v>
       </c>
       <c r="E205" t="s">
@@ -8485,19 +8598,20 @@
       <c r="G205">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J205" s="12"/>
+    </row>
+    <row r="206" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A206">
         <v>2</v>
       </c>
-      <c r="B206" t="s">
+      <c r="B206" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="C206" t="s">
+      <c r="C206" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="D206">
-        <v>3</v>
+      <c r="D206" s="13">
+        <v>1.5</v>
       </c>
       <c r="E206" t="s">
         <v>10</v>
@@ -8508,19 +8622,20 @@
       <c r="G206">
         <v>2</v>
       </c>
-    </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J206" s="12"/>
+    </row>
+    <row r="207" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A207">
         <v>2</v>
       </c>
-      <c r="B207" t="s">
+      <c r="B207" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="C207" t="s">
+      <c r="C207" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="D207">
-        <v>6</v>
+      <c r="D207" s="13">
+        <v>3</v>
       </c>
       <c r="E207" t="s">
         <v>10</v>
@@ -8531,19 +8646,20 @@
       <c r="G207">
         <v>2</v>
       </c>
-    </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J207" s="12"/>
+    </row>
+    <row r="208" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A208">
         <v>2</v>
       </c>
-      <c r="B208" t="s">
+      <c r="B208" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="C208" t="s">
+      <c r="C208" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="D208">
-        <v>16</v>
+      <c r="D208" s="13">
+        <v>8</v>
       </c>
       <c r="E208" t="s">
         <v>10</v>
@@ -8554,19 +8670,20 @@
       <c r="G208">
         <v>2</v>
       </c>
-    </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J208" s="12"/>
+    </row>
+    <row r="209" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A209">
         <v>2</v>
       </c>
-      <c r="B209" t="s">
+      <c r="B209" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="C209" t="s">
+      <c r="C209" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="D209">
-        <v>24</v>
+      <c r="D209" s="13">
+        <v>12</v>
       </c>
       <c r="E209" t="s">
         <v>10</v>
@@ -8577,19 +8694,20 @@
       <c r="G209">
         <v>2</v>
       </c>
-    </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J209" s="12"/>
+    </row>
+    <row r="210" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A210">
         <v>2</v>
       </c>
-      <c r="B210" t="s">
+      <c r="B210" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="C210" t="s">
+      <c r="C210" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D210">
-        <v>26</v>
+      <c r="D210" s="13">
+        <v>13</v>
       </c>
       <c r="E210" t="s">
         <v>10</v>
@@ -8600,19 +8718,20 @@
       <c r="G210">
         <v>3.5</v>
       </c>
-    </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J210" s="12"/>
+    </row>
+    <row r="211" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A211">
         <v>2</v>
       </c>
-      <c r="B211" t="s">
+      <c r="B211" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="C211" t="s">
+      <c r="C211" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="D211">
-        <v>24</v>
+      <c r="D211" s="13">
+        <v>12</v>
       </c>
       <c r="E211" t="s">
         <v>10</v>
@@ -8623,19 +8742,20 @@
       <c r="G211">
         <v>3.5</v>
       </c>
-    </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J211" s="12"/>
+    </row>
+    <row r="212" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A212">
         <v>2</v>
       </c>
-      <c r="B212" t="s">
+      <c r="B212" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="C212" t="s">
+      <c r="C212" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="D212">
-        <v>28</v>
+      <c r="D212" s="13">
+        <v>14</v>
       </c>
       <c r="E212" t="s">
         <v>10</v>
@@ -8646,19 +8766,20 @@
       <c r="G212">
         <v>3.5</v>
       </c>
-    </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J212" s="12"/>
+    </row>
+    <row r="213" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A213">
         <v>2</v>
       </c>
-      <c r="B213" t="s">
+      <c r="B213" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="C213" t="s">
+      <c r="C213" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="D213">
-        <v>24</v>
+      <c r="D213" s="13">
+        <v>12</v>
       </c>
       <c r="E213" t="s">
         <v>10</v>
@@ -8669,19 +8790,20 @@
       <c r="G213">
         <v>3.5</v>
       </c>
-    </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J213" s="12"/>
+    </row>
+    <row r="214" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A214">
         <v>2</v>
       </c>
-      <c r="B214" t="s">
+      <c r="B214" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C214" t="s">
+      <c r="C214" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="D214">
-        <v>12</v>
+      <c r="D214" s="13">
+        <v>6</v>
       </c>
       <c r="E214" t="s">
         <v>10</v>
@@ -8692,19 +8814,20 @@
       <c r="G214">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J214" s="12"/>
+    </row>
+    <row r="215" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A215">
         <v>2</v>
       </c>
-      <c r="B215" t="s">
+      <c r="B215" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="C215" t="s">
+      <c r="C215" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="D215">
-        <v>10</v>
+      <c r="D215" s="13">
+        <v>5</v>
       </c>
       <c r="E215" t="s">
         <v>10</v>
@@ -8715,19 +8838,20 @@
       <c r="G215">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J215" s="12"/>
+    </row>
+    <row r="216" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A216">
         <v>2</v>
       </c>
-      <c r="B216" t="s">
+      <c r="B216" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C216" t="s">
+      <c r="C216" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="D216">
-        <v>14</v>
+      <c r="D216" s="13">
+        <v>7</v>
       </c>
       <c r="E216" t="s">
         <v>10</v>
@@ -8738,19 +8862,20 @@
       <c r="G216">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J216" s="12"/>
+    </row>
+    <row r="217" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A217">
         <v>2</v>
       </c>
-      <c r="B217" t="s">
+      <c r="B217" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="C217" t="s">
+      <c r="C217" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="D217">
-        <v>22</v>
+      <c r="D217" s="13">
+        <v>11</v>
       </c>
       <c r="E217" t="s">
         <v>10</v>
@@ -8761,19 +8886,20 @@
       <c r="G217">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J217" s="12"/>
+    </row>
+    <row r="218" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A218">
         <v>2</v>
       </c>
-      <c r="B218" t="s">
+      <c r="B218" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="C218" t="s">
+      <c r="C218" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="D218">
-        <v>30</v>
+      <c r="D218" s="13">
+        <v>15</v>
       </c>
       <c r="E218" t="s">
         <v>10</v>
@@ -8784,19 +8910,20 @@
       <c r="G218">
         <v>4.2</v>
       </c>
-    </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J218" s="12"/>
+    </row>
+    <row r="219" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A219">
         <v>2</v>
       </c>
-      <c r="B219" t="s">
+      <c r="B219" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="C219" t="s">
+      <c r="C219" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="D219">
-        <v>32</v>
+      <c r="D219" s="13">
+        <v>16</v>
       </c>
       <c r="E219" t="s">
         <v>10</v>
@@ -8807,19 +8934,20 @@
       <c r="G219">
         <v>4.2</v>
       </c>
-    </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J219" s="12"/>
+    </row>
+    <row r="220" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A220">
         <v>2</v>
       </c>
-      <c r="B220" t="s">
+      <c r="B220" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="C220" t="s">
+      <c r="C220" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="D220">
-        <v>26</v>
+      <c r="D220" s="13">
+        <v>13</v>
       </c>
       <c r="E220" t="s">
         <v>10</v>
@@ -8830,19 +8958,20 @@
       <c r="G220">
         <v>4.2</v>
       </c>
-    </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J220" s="12"/>
+    </row>
+    <row r="221" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A221">
         <v>2</v>
       </c>
-      <c r="B221" t="s">
+      <c r="B221" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="C221" t="s">
+      <c r="C221" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="D221">
-        <v>16</v>
+      <c r="D221" s="13">
+        <v>8</v>
       </c>
       <c r="E221" t="s">
         <v>10</v>
@@ -8853,18 +8982,19 @@
       <c r="G221">
         <v>4.2</v>
       </c>
-    </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J221" s="12"/>
+    </row>
+    <row r="222" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A222">
         <v>2</v>
       </c>
-      <c r="B222" t="s">
+      <c r="B222" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="C222" t="s">
+      <c r="C222" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="D222">
+      <c r="D222" s="13">
         <v>0</v>
       </c>
       <c r="E222" t="s">
@@ -8876,19 +9006,20 @@
       <c r="G222">
         <v>3</v>
       </c>
-    </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J222" s="12"/>
+    </row>
+    <row r="223" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A223">
         <v>2</v>
       </c>
-      <c r="B223" t="s">
+      <c r="B223" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="C223" t="s">
+      <c r="C223" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="D223">
-        <v>3</v>
+      <c r="D223" s="13">
+        <v>1.5</v>
       </c>
       <c r="E223" t="s">
         <v>11</v>
@@ -8899,19 +9030,20 @@
       <c r="G223">
         <v>2</v>
       </c>
-    </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J223" s="12"/>
+    </row>
+    <row r="224" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A224">
         <v>2</v>
       </c>
-      <c r="B224" t="s">
+      <c r="B224" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="C224" t="s">
+      <c r="C224" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="D224">
-        <v>5</v>
+      <c r="D224" s="13">
+        <v>2.5</v>
       </c>
       <c r="E224" t="s">
         <v>11</v>
@@ -8922,19 +9054,20 @@
       <c r="G224">
         <v>2</v>
       </c>
-    </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J224" s="12"/>
+    </row>
+    <row r="225" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A225">
         <v>2</v>
       </c>
-      <c r="B225" t="s">
+      <c r="B225" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="C225" t="s">
+      <c r="C225" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="D225">
-        <v>14</v>
+      <c r="D225" s="13">
+        <v>7</v>
       </c>
       <c r="E225" t="s">
         <v>11</v>
@@ -8945,19 +9078,20 @@
       <c r="G225">
         <v>2</v>
       </c>
-    </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J225" s="12"/>
+    </row>
+    <row r="226" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A226">
         <v>2</v>
       </c>
-      <c r="B226" t="s">
+      <c r="B226" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="C226" t="s">
+      <c r="C226" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="D226">
-        <v>20</v>
+      <c r="D226" s="13">
+        <v>10</v>
       </c>
       <c r="E226" t="s">
         <v>11</v>
@@ -8968,19 +9102,20 @@
       <c r="G226">
         <v>2</v>
       </c>
-    </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J226" s="12"/>
+    </row>
+    <row r="227" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A227">
         <v>2</v>
       </c>
-      <c r="B227" t="s">
+      <c r="B227" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="C227" t="s">
+      <c r="C227" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="D227">
-        <v>22</v>
+      <c r="D227" s="13">
+        <v>11</v>
       </c>
       <c r="E227" t="s">
         <v>11</v>
@@ -8991,19 +9126,20 @@
       <c r="G227">
         <v>3.5</v>
       </c>
-    </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J227" s="12"/>
+    </row>
+    <row r="228" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A228">
         <v>2</v>
       </c>
-      <c r="B228" t="s">
+      <c r="B228" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="C228" t="s">
+      <c r="C228" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="D228">
-        <v>26</v>
+      <c r="D228" s="13">
+        <v>13</v>
       </c>
       <c r="E228" t="s">
         <v>11</v>
@@ -9014,19 +9150,20 @@
       <c r="G228">
         <v>3.5</v>
       </c>
-    </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J228" s="12"/>
+    </row>
+    <row r="229" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A229">
         <v>2</v>
       </c>
-      <c r="B229" t="s">
+      <c r="B229" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="C229" t="s">
+      <c r="C229" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="D229">
-        <v>28</v>
+      <c r="D229" s="13">
+        <v>14</v>
       </c>
       <c r="E229" t="s">
         <v>11</v>
@@ -9037,19 +9174,20 @@
       <c r="G229">
         <v>3.5</v>
       </c>
-    </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J229" s="12"/>
+    </row>
+    <row r="230" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A230">
         <v>2</v>
       </c>
-      <c r="B230" t="s">
+      <c r="B230" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="C230" t="s">
+      <c r="C230" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="D230">
-        <v>24</v>
+      <c r="D230" s="13">
+        <v>12</v>
       </c>
       <c r="E230" t="s">
         <v>11</v>
@@ -9060,19 +9198,20 @@
       <c r="G230">
         <v>3.5</v>
       </c>
-    </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J230" s="12"/>
+    </row>
+    <row r="231" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A231">
         <v>2</v>
       </c>
-      <c r="B231" t="s">
+      <c r="B231" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="C231" t="s">
+      <c r="C231" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="D231">
-        <v>14</v>
+      <c r="D231" s="13">
+        <v>7</v>
       </c>
       <c r="E231" t="s">
         <v>11</v>
@@ -9083,19 +9222,20 @@
       <c r="G231">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J231" s="12"/>
+    </row>
+    <row r="232" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A232">
         <v>2</v>
       </c>
-      <c r="B232" t="s">
+      <c r="B232" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="C232" t="s">
+      <c r="C232" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="D232">
-        <v>10</v>
+      <c r="D232" s="13">
+        <v>5</v>
       </c>
       <c r="E232" t="s">
         <v>11</v>
@@ -9106,19 +9246,20 @@
       <c r="G232">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J232" s="12"/>
+    </row>
+    <row r="233" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A233">
         <v>2</v>
       </c>
-      <c r="B233" t="s">
+      <c r="B233" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="C233" t="s">
+      <c r="C233" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="D233">
-        <v>10</v>
+      <c r="D233" s="13">
+        <v>5</v>
       </c>
       <c r="E233" t="s">
         <v>11</v>
@@ -9129,19 +9270,20 @@
       <c r="G233">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J233" s="12"/>
+    </row>
+    <row r="234" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A234">
         <v>2</v>
       </c>
-      <c r="B234" t="s">
+      <c r="B234" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="C234" t="s">
+      <c r="C234" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="D234">
-        <v>18</v>
+      <c r="D234" s="13">
+        <v>9</v>
       </c>
       <c r="E234" t="s">
         <v>11</v>
@@ -9152,19 +9294,20 @@
       <c r="G234">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J234" s="12"/>
+    </row>
+    <row r="235" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A235">
         <v>2</v>
       </c>
-      <c r="B235" t="s">
+      <c r="B235" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="C235" t="s">
+      <c r="C235" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="D235">
-        <v>22</v>
+      <c r="D235" s="13">
+        <v>11</v>
       </c>
       <c r="E235" t="s">
         <v>11</v>
@@ -9175,19 +9318,20 @@
       <c r="G235">
         <v>4.2</v>
       </c>
-    </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J235" s="12"/>
+    </row>
+    <row r="236" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A236">
         <v>2</v>
       </c>
-      <c r="B236" t="s">
+      <c r="B236" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="C236" t="s">
+      <c r="C236" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="D236">
-        <v>24</v>
+      <c r="D236" s="13">
+        <v>12</v>
       </c>
       <c r="E236" t="s">
         <v>11</v>
@@ -9198,19 +9342,20 @@
       <c r="G236">
         <v>4.2</v>
       </c>
-    </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J236" s="12"/>
+    </row>
+    <row r="237" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A237">
         <v>2</v>
       </c>
-      <c r="B237" t="s">
+      <c r="B237" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="C237" t="s">
+      <c r="C237" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="D237">
-        <v>18</v>
+      <c r="D237" s="13">
+        <v>9</v>
       </c>
       <c r="E237" t="s">
         <v>11</v>
@@ -9221,19 +9366,20 @@
       <c r="G237">
         <v>4.2</v>
       </c>
-    </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J237" s="12"/>
+    </row>
+    <row r="238" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A238">
         <v>2</v>
       </c>
-      <c r="B238" t="s">
+      <c r="B238" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="C238" t="s">
+      <c r="C238" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="D238">
-        <v>10</v>
+      <c r="D238" s="13">
+        <v>5</v>
       </c>
       <c r="E238" t="s">
         <v>11</v>
@@ -9244,18 +9390,19 @@
       <c r="G238">
         <v>4.2</v>
       </c>
-    </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J238" s="12"/>
+    </row>
+    <row r="239" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A239">
         <v>2</v>
       </c>
-      <c r="B239" t="s">
+      <c r="B239" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="C239" t="s">
+      <c r="C239" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="D239">
+      <c r="D239" s="13">
         <v>0</v>
       </c>
       <c r="E239" t="s">
@@ -9267,6 +9414,7 @@
       <c r="G239">
         <v>0</v>
       </c>
+      <c r="J239" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/scripts/restaurant_variables.xlsx
+++ b/scripts/restaurant_variables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\loren\Desktop\Simulation\Progetto\Restaurant_2025\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69032B05-EF17-43C2-AFC7-8DDD5062390A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6389F4E-875A-48A8-9645-FAEAFE40CB7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="19420" tabRatio="851" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -648,7 +648,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -720,22 +720,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -748,7 +737,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
@@ -756,15 +744,6 @@
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="23">
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="none">
@@ -955,6 +934,15 @@
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1011,10 +999,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{7D1585E5-EB18-4555-BFB4-AB049789BB50}" name="tables_selection" displayName="tables_selection" ref="A1:J11" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:J11" xr:uid="{7D1585E5-EB18-4555-BFB4-AB049789BB50}"/>
   <tableColumns count="10">
-    <tableColumn id="10" xr3:uid="{1ADF8E6C-C756-4DB0-AF29-730090E9A389}" uniqueName="10" name="scenario" queryTableFieldId="10" dataDxfId="22"/>
-    <tableColumn id="1" xr3:uid="{9DF6AF6D-4327-4E8B-A17C-4CE32200A2CC}" uniqueName="1" name="start_timestamp" queryTableFieldId="1" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{DB186560-5030-4DB1-A6BD-A74C44B2F90A}" uniqueName="2" name="end_timestamp" queryTableFieldId="2" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{6CE09762-A225-468B-8C15-326E109C4C41}" uniqueName="3" name="period" queryTableFieldId="3" dataDxfId="19"/>
+    <tableColumn id="10" xr3:uid="{1ADF8E6C-C756-4DB0-AF29-730090E9A389}" uniqueName="10" name="scenario" queryTableFieldId="10" dataDxfId="19"/>
+    <tableColumn id="1" xr3:uid="{9DF6AF6D-4327-4E8B-A17C-4CE32200A2CC}" uniqueName="1" name="start_timestamp" queryTableFieldId="1" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{DB186560-5030-4DB1-A6BD-A74C44B2F90A}" uniqueName="2" name="end_timestamp" queryTableFieldId="2" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{6CE09762-A225-468B-8C15-326E109C4C41}" uniqueName="3" name="period" queryTableFieldId="3" dataDxfId="16"/>
     <tableColumn id="4" xr3:uid="{90771DE1-93AE-42DD-88DE-8292168CC27F}" uniqueName="4" name="bar_on" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{2D6F5E1B-E207-46D0-A78B-EA6977317860}" uniqueName="5" name="inside_on" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{5AFB94CB-8BB6-4AE5-B6B3-D1BD6C86A1FB}" uniqueName="6" name="outside_on" queryTableFieldId="6"/>
@@ -1030,12 +1018,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{54D2211C-274A-47E4-BDD0-4C0951D8DD68}" name="employees_schedule" displayName="employees_schedule" ref="A1:H71" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:H71" xr:uid="{54D2211C-274A-47E4-BDD0-4C0951D8DD68}"/>
   <tableColumns count="8">
-    <tableColumn id="15" xr3:uid="{C7ED7AB4-5A31-4D81-834A-B6E64F7023C8}" uniqueName="15" name="scenario" queryTableFieldId="9" dataDxfId="18"/>
-    <tableColumn id="1" xr3:uid="{1826F0BC-F6D0-44C5-8A93-C7D99BD8CB8B}" uniqueName="1" name="start_timestamp" queryTableFieldId="1" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{75D23335-1496-4011-81D1-D6034B72FF11}" uniqueName="2" name="end_timestamp" queryTableFieldId="2" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{92C90E84-B1B0-4866-9DDC-2A2B72F890FA}" uniqueName="4" name="weekday" queryTableFieldId="4" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{954429F6-A3DE-46A7-885B-49BC6CAF5664}" uniqueName="5" name="hour" queryTableFieldId="5" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{D0D42E6A-14B4-4741-A3F6-DD9143A88038}" uniqueName="6" name="period" queryTableFieldId="6" dataDxfId="13"/>
+    <tableColumn id="15" xr3:uid="{C7ED7AB4-5A31-4D81-834A-B6E64F7023C8}" uniqueName="15" name="scenario" queryTableFieldId="9" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{1826F0BC-F6D0-44C5-8A93-C7D99BD8CB8B}" uniqueName="1" name="start_timestamp" queryTableFieldId="1" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{75D23335-1496-4011-81D1-D6034B72FF11}" uniqueName="2" name="end_timestamp" queryTableFieldId="2" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{92C90E84-B1B0-4866-9DDC-2A2B72F890FA}" uniqueName="4" name="weekday" queryTableFieldId="4" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{954429F6-A3DE-46A7-885B-49BC6CAF5664}" uniqueName="5" name="hour" queryTableFieldId="5" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{D0D42E6A-14B4-4741-A3F6-DD9143A88038}" uniqueName="6" name="period" queryTableFieldId="6" dataDxfId="10"/>
     <tableColumn id="7" xr3:uid="{DC0D317B-9907-4E39-BD04-56F982B6DFC4}" uniqueName="7" name="waiters" queryTableFieldId="7"/>
     <tableColumn id="8" xr3:uid="{5822B03F-BA67-4CAF-8288-1B9FA740A60F}" uniqueName="8" name="cooks" queryTableFieldId="8"/>
   </tableColumns>
@@ -1044,14 +1032,14 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D544813D-DF99-41C8-AE8A-38BE1FAF9E94}" name="Tabella3" displayName="Tabella3" ref="A1:E11" totalsRowShown="0" headerRowDxfId="12" dataDxfId="10" headerRowBorderDxfId="11" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D544813D-DF99-41C8-AE8A-38BE1FAF9E94}" name="Tabella3" displayName="Tabella3" ref="A1:E11" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5">
   <autoFilter ref="A1:E11" xr:uid="{D544813D-DF99-41C8-AE8A-38BE1FAF9E94}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{5F6DE45A-D069-49C3-A965-E57C526C9F10}" name="scenario" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{4D8F0B29-A4FF-499D-9A3B-DCD79E56771F}" name="start_timestamp" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{73FD92A6-7E32-4F59-A6D2-E391CC1529B2}" name="end_timestamp" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{E9B6B43D-80B9-448F-8CE5-DB0428CE9192}" name="period" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{FA561D75-B96F-4DC4-B290-98BCE5AF9EBB}" name="time_avg" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{5F6DE45A-D069-49C3-A965-E57C526C9F10}" name="scenario" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{4D8F0B29-A4FF-499D-9A3B-DCD79E56771F}" name="start_timestamp" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{73FD92A6-7E32-4F59-A6D2-E391CC1529B2}" name="end_timestamp" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{E9B6B43D-80B9-448F-8CE5-DB0428CE9192}" name="period" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{FA561D75-B96F-4DC4-B290-98BCE5AF9EBB}" name="time_avg" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1062,9 +1050,9 @@
   <autoFilter ref="A1:G239" xr:uid="{E79869A8-51C0-465F-A154-CE9C9BB79619}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{C0C152CA-AC82-4A38-9515-01F93B55CD35}" name="scenario"/>
-    <tableColumn id="2" xr3:uid="{A9274257-0F1F-4EC5-AEAD-2D02ED20F27D}" name="start_timestamp" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{8EBF5A3E-33DA-4E63-85B2-6A750FD2B59E}" name="end_timestamp" dataDxfId="0"/>
-    <tableColumn id="4" xr3:uid="{1B570803-0CC6-4039-83E4-466D06E97DE8}" name="arrival_rate" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{A9274257-0F1F-4EC5-AEAD-2D02ED20F27D}" name="start_timestamp" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{8EBF5A3E-33DA-4E63-85B2-6A750FD2B59E}" name="end_timestamp" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{1B570803-0CC6-4039-83E4-466D06E97DE8}" name="arrival_rate" dataDxfId="20"/>
     <tableColumn id="5" xr3:uid="{2330BE18-97F9-494B-A0D2-BC6CD4BE5D26}" name="weekday"/>
     <tableColumn id="6" xr3:uid="{511C9B76-5714-4C6E-B45F-24A76465D0A2}" name="hour"/>
     <tableColumn id="7" xr3:uid="{DDB83C9A-5515-4339-958C-0504A36D7FBA}" name="avg_group_size"/>
@@ -3437,10 +3425,10 @@
         <v>158</v>
       </c>
       <c r="G66">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H66">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.35">
@@ -3790,12 +3778,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BD3D082-868C-448F-9F19-732771E93A1D}">
-  <dimension ref="A1:J239"/>
+  <dimension ref="A1:G239"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.81640625" style="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.453125" style="13" customWidth="1"/>
+    <col min="1" max="1" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="17.81640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.453125" style="12" customWidth="1"/>
     <col min="5" max="5" width="10.6328125" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="16" bestFit="1" customWidth="1"/>
   </cols>
@@ -3804,13 +3792,13 @@
       <c r="A1" t="s">
         <v>166</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="13" t="s">
+      <c r="C1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="12" t="s">
         <v>2</v>
       </c>
       <c r="E1" t="s">
@@ -3827,14 +3815,14 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="13">
-        <v>5</v>
+      <c r="D2" s="12">
+        <v>1.6666666666666667</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -3850,14 +3838,14 @@
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="13">
-        <v>12</v>
+      <c r="D3" s="12">
+        <v>4</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
@@ -3873,14 +3861,14 @@
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="13">
-        <v>14</v>
+      <c r="D4" s="12">
+        <v>4.666666666666667</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -3896,14 +3884,14 @@
       <c r="A5">
         <v>1</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="13">
-        <v>8</v>
+      <c r="D5" s="12">
+        <v>2.6666666666666665</v>
       </c>
       <c r="E5" t="s">
         <v>5</v>
@@ -3919,14 +3907,14 @@
       <c r="A6">
         <v>1</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="13">
-        <v>6</v>
+      <c r="D6" s="12">
+        <v>2</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -3942,14 +3930,14 @@
       <c r="A7">
         <v>1</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="13">
-        <v>18</v>
+      <c r="D7" s="12">
+        <v>6</v>
       </c>
       <c r="E7" t="s">
         <v>5</v>
@@ -3965,14 +3953,14 @@
       <c r="A8">
         <v>1</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="13">
-        <v>28</v>
+      <c r="D8" s="12">
+        <v>9.3333333333333339</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -3988,14 +3976,14 @@
       <c r="A9">
         <v>1</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="13">
-        <v>16</v>
+      <c r="D9" s="12">
+        <v>5.333333333333333</v>
       </c>
       <c r="E9" t="s">
         <v>5</v>
@@ -4011,14 +3999,14 @@
       <c r="A10">
         <v>1</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="13">
-        <v>4</v>
+      <c r="D10" s="12">
+        <v>1.3333333333333333</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
@@ -4034,14 +4022,14 @@
       <c r="A11">
         <v>1</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="13">
-        <v>3</v>
+      <c r="D11" s="12">
+        <v>1</v>
       </c>
       <c r="E11" t="s">
         <v>5</v>
@@ -4057,14 +4045,14 @@
       <c r="A12">
         <v>1</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="13">
-        <v>5</v>
+      <c r="D12" s="12">
+        <v>1.6666666666666667</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
@@ -4080,14 +4068,14 @@
       <c r="A13">
         <v>1</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="13">
-        <v>12</v>
+      <c r="D13" s="12">
+        <v>4</v>
       </c>
       <c r="E13" t="s">
         <v>5</v>
@@ -4103,14 +4091,14 @@
       <c r="A14">
         <v>1</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="13">
-        <v>18</v>
+      <c r="D14" s="12">
+        <v>6</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
@@ -4126,14 +4114,14 @@
       <c r="A15">
         <v>1</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="13">
-        <v>20</v>
+      <c r="D15" s="12">
+        <v>6.666666666666667</v>
       </c>
       <c r="E15" t="s">
         <v>5</v>
@@ -4149,14 +4137,14 @@
       <c r="A16">
         <v>1</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="13">
-        <v>12</v>
+      <c r="D16" s="12">
+        <v>4</v>
       </c>
       <c r="E16" t="s">
         <v>5</v>
@@ -4172,14 +4160,14 @@
       <c r="A17">
         <v>1</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D17" s="13">
-        <v>5</v>
+      <c r="D17" s="12">
+        <v>1.6666666666666667</v>
       </c>
       <c r="E17" t="s">
         <v>5</v>
@@ -4195,13 +4183,13 @@
       <c r="A18">
         <v>1</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="13">
+      <c r="D18" s="12">
         <v>0</v>
       </c>
       <c r="E18" t="s">
@@ -4218,14 +4206,14 @@
       <c r="A19">
         <v>1</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C19" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="D19" s="13">
-        <v>5</v>
+      <c r="D19" s="12">
+        <v>1.6666666666666667</v>
       </c>
       <c r="E19" t="s">
         <v>6</v>
@@ -4241,14 +4229,14 @@
       <c r="A20">
         <v>1</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D20" s="13">
-        <v>14</v>
+      <c r="D20" s="12">
+        <v>4.666666666666667</v>
       </c>
       <c r="E20" t="s">
         <v>6</v>
@@ -4264,14 +4252,14 @@
       <c r="A21">
         <v>1</v>
       </c>
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C21" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="D21" s="13">
-        <v>15</v>
+      <c r="D21" s="12">
+        <v>5</v>
       </c>
       <c r="E21" t="s">
         <v>6</v>
@@ -4287,14 +4275,14 @@
       <c r="A22">
         <v>1</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="C22" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="13">
-        <v>8</v>
+      <c r="D22" s="12">
+        <v>2.6666666666666665</v>
       </c>
       <c r="E22" t="s">
         <v>6</v>
@@ -4310,14 +4298,14 @@
       <c r="A23">
         <v>1</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="C23" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D23" s="13">
-        <v>6</v>
+      <c r="D23" s="12">
+        <v>2</v>
       </c>
       <c r="E23" t="s">
         <v>6</v>
@@ -4333,14 +4321,14 @@
       <c r="A24">
         <v>1</v>
       </c>
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="C24" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="D24" s="13">
-        <v>19</v>
+      <c r="D24" s="12">
+        <v>6.333333333333333</v>
       </c>
       <c r="E24" t="s">
         <v>6</v>
@@ -4356,14 +4344,14 @@
       <c r="A25">
         <v>1</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="B25" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="C25" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="D25" s="13">
-        <v>29</v>
+      <c r="D25" s="12">
+        <v>9.6666666666666661</v>
       </c>
       <c r="E25" t="s">
         <v>6</v>
@@ -4379,14 +4367,14 @@
       <c r="A26">
         <v>1</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C26" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D26" s="13">
-        <v>16</v>
+      <c r="D26" s="12">
+        <v>5.333333333333333</v>
       </c>
       <c r="E26" t="s">
         <v>6</v>
@@ -4402,14 +4390,14 @@
       <c r="A27">
         <v>1</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="B27" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="C27" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="D27" s="13">
-        <v>4</v>
+      <c r="D27" s="12">
+        <v>1.3333333333333333</v>
       </c>
       <c r="E27" t="s">
         <v>6</v>
@@ -4425,14 +4413,14 @@
       <c r="A28">
         <v>1</v>
       </c>
-      <c r="B28" s="14" t="s">
+      <c r="B28" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="C28" s="14" t="s">
+      <c r="C28" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="D28" s="13">
-        <v>3</v>
+      <c r="D28" s="12">
+        <v>1</v>
       </c>
       <c r="E28" t="s">
         <v>6</v>
@@ -4448,14 +4436,14 @@
       <c r="A29">
         <v>1</v>
       </c>
-      <c r="B29" s="14" t="s">
+      <c r="B29" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="C29" s="14" t="s">
+      <c r="C29" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="D29" s="13">
-        <v>6</v>
+      <c r="D29" s="12">
+        <v>2</v>
       </c>
       <c r="E29" t="s">
         <v>6</v>
@@ -4471,14 +4459,14 @@
       <c r="A30">
         <v>1</v>
       </c>
-      <c r="B30" s="14" t="s">
+      <c r="B30" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="C30" s="14" t="s">
+      <c r="C30" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="D30" s="13">
-        <v>12</v>
+      <c r="D30" s="12">
+        <v>4</v>
       </c>
       <c r="E30" t="s">
         <v>6</v>
@@ -4494,14 +4482,14 @@
       <c r="A31">
         <v>1</v>
       </c>
-      <c r="B31" s="14" t="s">
+      <c r="B31" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="C31" s="14" t="s">
+      <c r="C31" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="D31" s="13">
-        <v>19</v>
+      <c r="D31" s="12">
+        <v>6.333333333333333</v>
       </c>
       <c r="E31" t="s">
         <v>6</v>
@@ -4517,14 +4505,14 @@
       <c r="A32">
         <v>1</v>
       </c>
-      <c r="B32" s="14" t="s">
+      <c r="B32" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="C32" s="14" t="s">
+      <c r="C32" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="D32" s="13">
-        <v>25</v>
+      <c r="D32" s="12">
+        <v>8.3333333333333339</v>
       </c>
       <c r="E32" t="s">
         <v>6</v>
@@ -4540,14 +4528,14 @@
       <c r="A33">
         <v>1</v>
       </c>
-      <c r="B33" s="14" t="s">
+      <c r="B33" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C33" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D33" s="13">
-        <v>12</v>
+      <c r="D33" s="12">
+        <v>4</v>
       </c>
       <c r="E33" t="s">
         <v>6</v>
@@ -4563,14 +4551,14 @@
       <c r="A34">
         <v>1</v>
       </c>
-      <c r="B34" s="14" t="s">
+      <c r="B34" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="C34" s="14" t="s">
+      <c r="C34" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="D34" s="13">
-        <v>5</v>
+      <c r="D34" s="12">
+        <v>1.6666666666666667</v>
       </c>
       <c r="E34" t="s">
         <v>6</v>
@@ -4586,13 +4574,13 @@
       <c r="A35">
         <v>1</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="C35" s="14" t="s">
+      <c r="C35" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="D35" s="13">
+      <c r="D35" s="12">
         <v>0</v>
       </c>
       <c r="E35" t="s">
@@ -4609,14 +4597,14 @@
       <c r="A36">
         <v>1</v>
       </c>
-      <c r="B36" s="14" t="s">
+      <c r="B36" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C36" s="14" t="s">
+      <c r="C36" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="D36" s="13">
-        <v>5</v>
+      <c r="D36" s="12">
+        <v>1.6666666666666667</v>
       </c>
       <c r="E36" t="s">
         <v>7</v>
@@ -4632,14 +4620,14 @@
       <c r="A37">
         <v>1</v>
       </c>
-      <c r="B37" s="14" t="s">
+      <c r="B37" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="C37" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="D37" s="13">
-        <v>13</v>
+      <c r="D37" s="12">
+        <v>4.333333333333333</v>
       </c>
       <c r="E37" t="s">
         <v>7</v>
@@ -4655,14 +4643,14 @@
       <c r="A38">
         <v>1</v>
       </c>
-      <c r="B38" s="14" t="s">
+      <c r="B38" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="C38" s="14" t="s">
+      <c r="C38" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="D38" s="13">
-        <v>15</v>
+      <c r="D38" s="12">
+        <v>5</v>
       </c>
       <c r="E38" t="s">
         <v>7</v>
@@ -4678,14 +4666,14 @@
       <c r="A39">
         <v>1</v>
       </c>
-      <c r="B39" s="14" t="s">
+      <c r="B39" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C39" s="14" t="s">
+      <c r="C39" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="D39" s="13">
-        <v>8</v>
+      <c r="D39" s="12">
+        <v>2.6666666666666665</v>
       </c>
       <c r="E39" t="s">
         <v>7</v>
@@ -4701,14 +4689,14 @@
       <c r="A40">
         <v>1</v>
       </c>
-      <c r="B40" s="14" t="s">
+      <c r="B40" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C40" s="14" t="s">
+      <c r="C40" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="D40" s="13">
-        <v>6</v>
+      <c r="D40" s="12">
+        <v>2</v>
       </c>
       <c r="E40" t="s">
         <v>7</v>
@@ -4724,14 +4712,14 @@
       <c r="A41">
         <v>1</v>
       </c>
-      <c r="B41" s="14" t="s">
+      <c r="B41" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C41" s="14" t="s">
+      <c r="C41" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="D41" s="13">
-        <v>20</v>
+      <c r="D41" s="12">
+        <v>6.666666666666667</v>
       </c>
       <c r="E41" t="s">
         <v>7</v>
@@ -4747,14 +4735,14 @@
       <c r="A42">
         <v>1</v>
       </c>
-      <c r="B42" s="14" t="s">
+      <c r="B42" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C42" s="14" t="s">
+      <c r="C42" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="D42" s="13">
-        <v>29</v>
+      <c r="D42" s="12">
+        <v>9.6666666666666661</v>
       </c>
       <c r="E42" t="s">
         <v>7</v>
@@ -4770,14 +4758,14 @@
       <c r="A43">
         <v>1</v>
       </c>
-      <c r="B43" s="14" t="s">
+      <c r="B43" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C43" s="14" t="s">
+      <c r="C43" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D43" s="13">
-        <v>16</v>
+      <c r="D43" s="12">
+        <v>5.333333333333333</v>
       </c>
       <c r="E43" t="s">
         <v>7</v>
@@ -4793,14 +4781,14 @@
       <c r="A44">
         <v>1</v>
       </c>
-      <c r="B44" s="14" t="s">
+      <c r="B44" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="C44" s="14" t="s">
+      <c r="C44" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="D44" s="13">
-        <v>4</v>
+      <c r="D44" s="12">
+        <v>1.3333333333333333</v>
       </c>
       <c r="E44" t="s">
         <v>7</v>
@@ -4816,14 +4804,14 @@
       <c r="A45">
         <v>1</v>
       </c>
-      <c r="B45" s="14" t="s">
+      <c r="B45" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="C45" s="14" t="s">
+      <c r="C45" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="D45" s="13">
-        <v>3</v>
+      <c r="D45" s="12">
+        <v>1</v>
       </c>
       <c r="E45" t="s">
         <v>7</v>
@@ -4839,14 +4827,14 @@
       <c r="A46">
         <v>1</v>
       </c>
-      <c r="B46" s="14" t="s">
+      <c r="B46" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="C46" s="14" t="s">
+      <c r="C46" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="D46" s="13">
-        <v>6</v>
+      <c r="D46" s="12">
+        <v>2</v>
       </c>
       <c r="E46" t="s">
         <v>7</v>
@@ -4862,14 +4850,14 @@
       <c r="A47">
         <v>1</v>
       </c>
-      <c r="B47" s="14" t="s">
+      <c r="B47" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="C47" s="14" t="s">
+      <c r="C47" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="D47" s="13">
-        <v>13</v>
+      <c r="D47" s="12">
+        <v>4.333333333333333</v>
       </c>
       <c r="E47" t="s">
         <v>7</v>
@@ -4885,14 +4873,14 @@
       <c r="A48">
         <v>1</v>
       </c>
-      <c r="B48" s="14" t="s">
+      <c r="B48" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="C48" s="14" t="s">
+      <c r="C48" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="D48" s="13">
-        <v>19</v>
+      <c r="D48" s="12">
+        <v>6.333333333333333</v>
       </c>
       <c r="E48" t="s">
         <v>7</v>
@@ -4908,14 +4896,14 @@
       <c r="A49">
         <v>1</v>
       </c>
-      <c r="B49" s="14" t="s">
+      <c r="B49" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C49" s="14" t="s">
+      <c r="C49" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="D49" s="13">
-        <v>21</v>
+      <c r="D49" s="12">
+        <v>7</v>
       </c>
       <c r="E49" t="s">
         <v>7</v>
@@ -4931,14 +4919,14 @@
       <c r="A50">
         <v>1</v>
       </c>
-      <c r="B50" s="14" t="s">
+      <c r="B50" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C50" s="14" t="s">
+      <c r="C50" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="D50" s="13">
-        <v>13</v>
+      <c r="D50" s="12">
+        <v>4.333333333333333</v>
       </c>
       <c r="E50" t="s">
         <v>7</v>
@@ -4954,14 +4942,14 @@
       <c r="A51">
         <v>1</v>
       </c>
-      <c r="B51" s="14" t="s">
+      <c r="B51" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="C51" s="14" t="s">
+      <c r="C51" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="D51" s="13">
-        <v>6</v>
+      <c r="D51" s="12">
+        <v>2</v>
       </c>
       <c r="E51" t="s">
         <v>7</v>
@@ -4977,13 +4965,13 @@
       <c r="A52">
         <v>1</v>
       </c>
-      <c r="B52" s="14" t="s">
+      <c r="B52" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="C52" s="14" t="s">
+      <c r="C52" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="D52" s="13">
+      <c r="D52" s="12">
         <v>0</v>
       </c>
       <c r="E52" t="s">
@@ -5000,14 +4988,14 @@
       <c r="A53">
         <v>1</v>
       </c>
-      <c r="B53" s="14" t="s">
+      <c r="B53" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="C53" s="14" t="s">
+      <c r="C53" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="D53" s="13">
-        <v>6</v>
+      <c r="D53" s="12">
+        <v>2</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
@@ -5023,14 +5011,14 @@
       <c r="A54">
         <v>1</v>
       </c>
-      <c r="B54" s="14" t="s">
+      <c r="B54" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="C54" s="14" t="s">
+      <c r="C54" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="D54" s="13">
-        <v>14</v>
+      <c r="D54" s="12">
+        <v>4.666666666666667</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
@@ -5046,14 +5034,14 @@
       <c r="A55">
         <v>1</v>
       </c>
-      <c r="B55" s="14" t="s">
+      <c r="B55" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="C55" s="14" t="s">
+      <c r="C55" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="D55" s="13">
-        <v>16</v>
+      <c r="D55" s="12">
+        <v>5.333333333333333</v>
       </c>
       <c r="E55" t="s">
         <v>8</v>
@@ -5069,14 +5057,14 @@
       <c r="A56">
         <v>1</v>
       </c>
-      <c r="B56" s="14" t="s">
+      <c r="B56" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C56" s="14" t="s">
+      <c r="C56" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="D56" s="13">
-        <v>9</v>
+      <c r="D56" s="12">
+        <v>3</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
@@ -5092,14 +5080,14 @@
       <c r="A57">
         <v>1</v>
       </c>
-      <c r="B57" s="14" t="s">
+      <c r="B57" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="C57" s="14" t="s">
+      <c r="C57" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="D57" s="13">
-        <v>7</v>
+      <c r="D57" s="12">
+        <v>2.3333333333333335</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
@@ -5115,14 +5103,14 @@
       <c r="A58">
         <v>1</v>
       </c>
-      <c r="B58" s="14" t="s">
+      <c r="B58" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="C58" s="14" t="s">
+      <c r="C58" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="D58" s="13">
-        <v>20</v>
+      <c r="D58" s="12">
+        <v>6.666666666666667</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
@@ -5138,14 +5126,14 @@
       <c r="A59">
         <v>1</v>
       </c>
-      <c r="B59" s="14" t="s">
+      <c r="B59" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C59" s="14" t="s">
+      <c r="C59" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="D59" s="13">
-        <v>30</v>
+      <c r="D59" s="12">
+        <v>10</v>
       </c>
       <c r="E59" t="s">
         <v>8</v>
@@ -5161,14 +5149,14 @@
       <c r="A60">
         <v>1</v>
       </c>
-      <c r="B60" s="14" t="s">
+      <c r="B60" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="C60" s="14" t="s">
+      <c r="C60" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D60" s="13">
-        <v>17</v>
+      <c r="D60" s="12">
+        <v>5.666666666666667</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
@@ -5184,14 +5172,14 @@
       <c r="A61">
         <v>1</v>
       </c>
-      <c r="B61" s="14" t="s">
+      <c r="B61" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="C61" s="14" t="s">
+      <c r="C61" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="D61" s="13">
-        <v>5</v>
+      <c r="D61" s="12">
+        <v>1.6666666666666667</v>
       </c>
       <c r="E61" t="s">
         <v>8</v>
@@ -5207,14 +5195,14 @@
       <c r="A62">
         <v>1</v>
       </c>
-      <c r="B62" s="14" t="s">
+      <c r="B62" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="C62" s="14" t="s">
+      <c r="C62" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="D62" s="13">
-        <v>4</v>
+      <c r="D62" s="12">
+        <v>1.3333333333333333</v>
       </c>
       <c r="E62" t="s">
         <v>8</v>
@@ -5230,14 +5218,14 @@
       <c r="A63">
         <v>1</v>
       </c>
-      <c r="B63" s="14" t="s">
+      <c r="B63" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="C63" s="14" t="s">
+      <c r="C63" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="D63" s="13">
-        <v>7</v>
+      <c r="D63" s="12">
+        <v>2.3333333333333335</v>
       </c>
       <c r="E63" t="s">
         <v>8</v>
@@ -5253,14 +5241,14 @@
       <c r="A64">
         <v>1</v>
       </c>
-      <c r="B64" s="14" t="s">
+      <c r="B64" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="C64" s="14" t="s">
+      <c r="C64" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="D64" s="13">
-        <v>15</v>
+      <c r="D64" s="12">
+        <v>5</v>
       </c>
       <c r="E64" t="s">
         <v>8</v>
@@ -5276,14 +5264,14 @@
       <c r="A65">
         <v>1</v>
       </c>
-      <c r="B65" s="14" t="s">
+      <c r="B65" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="C65" s="14" t="s">
+      <c r="C65" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="D65" s="13">
-        <v>20</v>
+      <c r="D65" s="12">
+        <v>6.666666666666667</v>
       </c>
       <c r="E65" t="s">
         <v>8</v>
@@ -5299,14 +5287,14 @@
       <c r="A66">
         <v>1</v>
       </c>
-      <c r="B66" s="14" t="s">
+      <c r="B66" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="C66" s="14" t="s">
+      <c r="C66" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="D66" s="13">
-        <v>22</v>
+      <c r="D66" s="12">
+        <v>7.333333333333333</v>
       </c>
       <c r="E66" t="s">
         <v>8</v>
@@ -5322,14 +5310,14 @@
       <c r="A67">
         <v>1</v>
       </c>
-      <c r="B67" s="14" t="s">
+      <c r="B67" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="C67" s="14" t="s">
+      <c r="C67" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="D67" s="13">
-        <v>15</v>
+      <c r="D67" s="12">
+        <v>5</v>
       </c>
       <c r="E67" t="s">
         <v>8</v>
@@ -5345,14 +5333,14 @@
       <c r="A68">
         <v>1</v>
       </c>
-      <c r="B68" s="14" t="s">
+      <c r="B68" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C68" s="14" t="s">
+      <c r="C68" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="D68" s="13">
-        <v>7</v>
+      <c r="D68" s="12">
+        <v>2.3333333333333335</v>
       </c>
       <c r="E68" t="s">
         <v>8</v>
@@ -5368,13 +5356,13 @@
       <c r="A69">
         <v>1</v>
       </c>
-      <c r="B69" s="14" t="s">
+      <c r="B69" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="C69" s="14" t="s">
+      <c r="C69" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="D69" s="13">
+      <c r="D69" s="12">
         <v>0</v>
       </c>
       <c r="E69" t="s">
@@ -5391,14 +5379,14 @@
       <c r="A70">
         <v>1</v>
       </c>
-      <c r="B70" s="14" t="s">
+      <c r="B70" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="C70" s="14" t="s">
+      <c r="C70" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="D70" s="13">
-        <v>6</v>
+      <c r="D70" s="12">
+        <v>2</v>
       </c>
       <c r="E70" t="s">
         <v>9</v>
@@ -5414,14 +5402,14 @@
       <c r="A71">
         <v>1</v>
       </c>
-      <c r="B71" s="14" t="s">
+      <c r="B71" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="C71" s="14" t="s">
+      <c r="C71" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="D71" s="13">
-        <v>15</v>
+      <c r="D71" s="12">
+        <v>5</v>
       </c>
       <c r="E71" t="s">
         <v>9</v>
@@ -5437,14 +5425,14 @@
       <c r="A72">
         <v>1</v>
       </c>
-      <c r="B72" s="14" t="s">
+      <c r="B72" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="C72" s="14" t="s">
+      <c r="C72" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="D72" s="13">
-        <v>17</v>
+      <c r="D72" s="12">
+        <v>5.666666666666667</v>
       </c>
       <c r="E72" t="s">
         <v>9</v>
@@ -5460,14 +5448,14 @@
       <c r="A73">
         <v>1</v>
       </c>
-      <c r="B73" s="14" t="s">
+      <c r="B73" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="C73" s="14" t="s">
+      <c r="C73" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="D73" s="13">
-        <v>10</v>
+      <c r="D73" s="12">
+        <v>3.3333333333333335</v>
       </c>
       <c r="E73" t="s">
         <v>9</v>
@@ -5483,14 +5471,14 @@
       <c r="A74">
         <v>1</v>
       </c>
-      <c r="B74" s="14" t="s">
+      <c r="B74" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="C74" s="14" t="s">
+      <c r="C74" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="D74" s="13">
-        <v>9</v>
+      <c r="D74" s="12">
+        <v>3</v>
       </c>
       <c r="E74" t="s">
         <v>9</v>
@@ -5506,14 +5494,14 @@
       <c r="A75">
         <v>1</v>
       </c>
-      <c r="B75" s="14" t="s">
+      <c r="B75" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="C75" s="14" t="s">
+      <c r="C75" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="D75" s="13">
-        <v>22</v>
+      <c r="D75" s="12">
+        <v>7.333333333333333</v>
       </c>
       <c r="E75" t="s">
         <v>9</v>
@@ -5529,14 +5517,14 @@
       <c r="A76">
         <v>1</v>
       </c>
-      <c r="B76" s="14" t="s">
+      <c r="B76" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="C76" s="14" t="s">
+      <c r="C76" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="D76" s="13">
-        <v>32</v>
+      <c r="D76" s="12">
+        <v>10.666666666666666</v>
       </c>
       <c r="E76" t="s">
         <v>9</v>
@@ -5552,14 +5540,14 @@
       <c r="A77">
         <v>1</v>
       </c>
-      <c r="B77" s="14" t="s">
+      <c r="B77" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="C77" s="14" t="s">
+      <c r="C77" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="D77" s="13">
-        <v>20</v>
+      <c r="D77" s="12">
+        <v>6.666666666666667</v>
       </c>
       <c r="E77" t="s">
         <v>9</v>
@@ -5575,14 +5563,14 @@
       <c r="A78">
         <v>1</v>
       </c>
-      <c r="B78" s="14" t="s">
+      <c r="B78" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="C78" s="14" t="s">
+      <c r="C78" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="D78" s="13">
-        <v>6</v>
+      <c r="D78" s="12">
+        <v>2</v>
       </c>
       <c r="E78" t="s">
         <v>9</v>
@@ -5598,14 +5586,14 @@
       <c r="A79">
         <v>1</v>
       </c>
-      <c r="B79" s="14" t="s">
+      <c r="B79" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="C79" s="14" t="s">
+      <c r="C79" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="D79" s="13">
-        <v>7</v>
+      <c r="D79" s="12">
+        <v>2.3333333333333335</v>
       </c>
       <c r="E79" t="s">
         <v>9</v>
@@ -5621,14 +5609,14 @@
       <c r="A80">
         <v>1</v>
       </c>
-      <c r="B80" s="14" t="s">
+      <c r="B80" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="C80" s="14" t="s">
+      <c r="C80" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="D80" s="13">
-        <v>12</v>
+      <c r="D80" s="12">
+        <v>4</v>
       </c>
       <c r="E80" t="s">
         <v>9</v>
@@ -5644,14 +5632,14 @@
       <c r="A81">
         <v>1</v>
       </c>
-      <c r="B81" s="14" t="s">
+      <c r="B81" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="C81" s="14" t="s">
+      <c r="C81" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="D81" s="13">
-        <v>18</v>
+      <c r="D81" s="12">
+        <v>6</v>
       </c>
       <c r="E81" t="s">
         <v>9</v>
@@ -5667,14 +5655,14 @@
       <c r="A82">
         <v>1</v>
       </c>
-      <c r="B82" s="14" t="s">
+      <c r="B82" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="C82" s="14" t="s">
+      <c r="C82" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="D82" s="13">
-        <v>26</v>
+      <c r="D82" s="12">
+        <v>8.6666666666666661</v>
       </c>
       <c r="E82" t="s">
         <v>9</v>
@@ -5690,14 +5678,14 @@
       <c r="A83">
         <v>1</v>
       </c>
-      <c r="B83" s="14" t="s">
+      <c r="B83" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="C83" s="14" t="s">
+      <c r="C83" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="D83" s="13">
-        <v>28</v>
+      <c r="D83" s="12">
+        <v>9.3333333333333339</v>
       </c>
       <c r="E83" t="s">
         <v>9</v>
@@ -5713,14 +5701,14 @@
       <c r="A84">
         <v>1</v>
       </c>
-      <c r="B84" s="14" t="s">
+      <c r="B84" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="C84" s="14" t="s">
+      <c r="C84" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="D84" s="13">
-        <v>22</v>
+      <c r="D84" s="12">
+        <v>7.333333333333333</v>
       </c>
       <c r="E84" t="s">
         <v>9</v>
@@ -5736,14 +5724,14 @@
       <c r="A85">
         <v>1</v>
       </c>
-      <c r="B85" s="14" t="s">
+      <c r="B85" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="C85" s="14" t="s">
+      <c r="C85" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="D85" s="13">
-        <v>12</v>
+      <c r="D85" s="12">
+        <v>4</v>
       </c>
       <c r="E85" t="s">
         <v>9</v>
@@ -5759,13 +5747,13 @@
       <c r="A86">
         <v>1</v>
       </c>
-      <c r="B86" s="14" t="s">
+      <c r="B86" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="C86" s="14" t="s">
+      <c r="C86" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="D86" s="13">
+      <c r="D86" s="12">
         <v>0</v>
       </c>
       <c r="E86" t="s">
@@ -5782,14 +5770,14 @@
       <c r="A87">
         <v>1</v>
       </c>
-      <c r="B87" s="14" t="s">
+      <c r="B87" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="C87" s="14" t="s">
+      <c r="C87" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="D87" s="13">
-        <v>3</v>
+      <c r="D87" s="12">
+        <v>1</v>
       </c>
       <c r="E87" t="s">
         <v>10</v>
@@ -5805,14 +5793,14 @@
       <c r="A88">
         <v>1</v>
       </c>
-      <c r="B88" s="14" t="s">
+      <c r="B88" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="C88" s="14" t="s">
+      <c r="C88" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="D88" s="13">
-        <v>6</v>
+      <c r="D88" s="12">
+        <v>2</v>
       </c>
       <c r="E88" t="s">
         <v>10</v>
@@ -5828,14 +5816,14 @@
       <c r="A89">
         <v>1</v>
       </c>
-      <c r="B89" s="14" t="s">
+      <c r="B89" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="C89" s="14" t="s">
+      <c r="C89" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="D89" s="13">
-        <v>16</v>
+      <c r="D89" s="12">
+        <v>5.333333333333333</v>
       </c>
       <c r="E89" t="s">
         <v>10</v>
@@ -5851,14 +5839,14 @@
       <c r="A90">
         <v>1</v>
       </c>
-      <c r="B90" s="14" t="s">
+      <c r="B90" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="C90" s="14" t="s">
+      <c r="C90" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="D90" s="13">
-        <v>24</v>
+      <c r="D90" s="12">
+        <v>8</v>
       </c>
       <c r="E90" t="s">
         <v>10</v>
@@ -5874,14 +5862,14 @@
       <c r="A91">
         <v>1</v>
       </c>
-      <c r="B91" s="14" t="s">
+      <c r="B91" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C91" s="14" t="s">
+      <c r="C91" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D91" s="13">
-        <v>26</v>
+      <c r="D91" s="12">
+        <v>8.6666666666666661</v>
       </c>
       <c r="E91" t="s">
         <v>10</v>
@@ -5897,14 +5885,14 @@
       <c r="A92">
         <v>1</v>
       </c>
-      <c r="B92" s="14" t="s">
+      <c r="B92" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="C92" s="14" t="s">
+      <c r="C92" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="D92" s="13">
-        <v>24</v>
+      <c r="D92" s="12">
+        <v>8</v>
       </c>
       <c r="E92" t="s">
         <v>10</v>
@@ -5920,14 +5908,14 @@
       <c r="A93">
         <v>1</v>
       </c>
-      <c r="B93" s="14" t="s">
+      <c r="B93" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="C93" s="14" t="s">
+      <c r="C93" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="D93" s="13">
-        <v>28</v>
+      <c r="D93" s="12">
+        <v>9.3333333333333339</v>
       </c>
       <c r="E93" t="s">
         <v>10</v>
@@ -5943,14 +5931,14 @@
       <c r="A94">
         <v>1</v>
       </c>
-      <c r="B94" s="14" t="s">
+      <c r="B94" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="C94" s="14" t="s">
+      <c r="C94" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="D94" s="13">
-        <v>24</v>
+      <c r="D94" s="12">
+        <v>8</v>
       </c>
       <c r="E94" t="s">
         <v>10</v>
@@ -5966,14 +5954,14 @@
       <c r="A95">
         <v>1</v>
       </c>
-      <c r="B95" s="14" t="s">
+      <c r="B95" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="C95" s="14" t="s">
+      <c r="C95" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="D95" s="13">
-        <v>12</v>
+      <c r="D95" s="12">
+        <v>4</v>
       </c>
       <c r="E95" t="s">
         <v>10</v>
@@ -5989,14 +5977,14 @@
       <c r="A96">
         <v>1</v>
       </c>
-      <c r="B96" s="14" t="s">
+      <c r="B96" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="C96" s="14" t="s">
+      <c r="C96" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="D96" s="13">
-        <v>10</v>
+      <c r="D96" s="12">
+        <v>3.3333333333333335</v>
       </c>
       <c r="E96" t="s">
         <v>10</v>
@@ -6012,14 +6000,14 @@
       <c r="A97">
         <v>1</v>
       </c>
-      <c r="B97" s="14" t="s">
+      <c r="B97" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="C97" s="14" t="s">
+      <c r="C97" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D97" s="13">
-        <v>14</v>
+      <c r="D97" s="12">
+        <v>4.666666666666667</v>
       </c>
       <c r="E97" t="s">
         <v>10</v>
@@ -6035,14 +6023,14 @@
       <c r="A98">
         <v>1</v>
       </c>
-      <c r="B98" s="14" t="s">
+      <c r="B98" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="C98" s="14" t="s">
+      <c r="C98" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="D98" s="13">
-        <v>22</v>
+      <c r="D98" s="12">
+        <v>7.333333333333333</v>
       </c>
       <c r="E98" t="s">
         <v>10</v>
@@ -6058,14 +6046,14 @@
       <c r="A99">
         <v>1</v>
       </c>
-      <c r="B99" s="14" t="s">
+      <c r="B99" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="C99" s="14" t="s">
+      <c r="C99" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="D99" s="13">
-        <v>30</v>
+      <c r="D99" s="12">
+        <v>10</v>
       </c>
       <c r="E99" t="s">
         <v>10</v>
@@ -6081,14 +6069,14 @@
       <c r="A100">
         <v>1</v>
       </c>
-      <c r="B100" s="14" t="s">
+      <c r="B100" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="C100" s="14" t="s">
+      <c r="C100" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="D100" s="13">
-        <v>32</v>
+      <c r="D100" s="12">
+        <v>10.666666666666666</v>
       </c>
       <c r="E100" t="s">
         <v>10</v>
@@ -6104,14 +6092,14 @@
       <c r="A101">
         <v>1</v>
       </c>
-      <c r="B101" s="14" t="s">
+      <c r="B101" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="C101" s="14" t="s">
+      <c r="C101" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="D101" s="13">
-        <v>26</v>
+      <c r="D101" s="12">
+        <v>8.6666666666666661</v>
       </c>
       <c r="E101" t="s">
         <v>10</v>
@@ -6127,14 +6115,14 @@
       <c r="A102">
         <v>1</v>
       </c>
-      <c r="B102" s="14" t="s">
+      <c r="B102" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="C102" s="14" t="s">
+      <c r="C102" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="D102" s="13">
-        <v>16</v>
+      <c r="D102" s="12">
+        <v>5.333333333333333</v>
       </c>
       <c r="E102" t="s">
         <v>10</v>
@@ -6150,13 +6138,13 @@
       <c r="A103">
         <v>1</v>
       </c>
-      <c r="B103" s="14" t="s">
+      <c r="B103" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="C103" s="14" t="s">
+      <c r="C103" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="D103" s="13">
+      <c r="D103" s="12">
         <v>0</v>
       </c>
       <c r="E103" t="s">
@@ -6173,14 +6161,14 @@
       <c r="A104">
         <v>1</v>
       </c>
-      <c r="B104" s="14" t="s">
+      <c r="B104" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="C104" s="14" t="s">
+      <c r="C104" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="D104" s="13">
-        <v>3</v>
+      <c r="D104" s="12">
+        <v>1</v>
       </c>
       <c r="E104" t="s">
         <v>11</v>
@@ -6196,14 +6184,14 @@
       <c r="A105">
         <v>1</v>
       </c>
-      <c r="B105" s="14" t="s">
+      <c r="B105" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="C105" s="14" t="s">
+      <c r="C105" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="D105" s="13">
-        <v>5</v>
+      <c r="D105" s="12">
+        <v>1.6666666666666667</v>
       </c>
       <c r="E105" t="s">
         <v>11</v>
@@ -6219,14 +6207,14 @@
       <c r="A106">
         <v>1</v>
       </c>
-      <c r="B106" s="14" t="s">
+      <c r="B106" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="C106" s="14" t="s">
+      <c r="C106" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="D106" s="13">
-        <v>14</v>
+      <c r="D106" s="12">
+        <v>4.666666666666667</v>
       </c>
       <c r="E106" t="s">
         <v>11</v>
@@ -6242,14 +6230,14 @@
       <c r="A107">
         <v>1</v>
       </c>
-      <c r="B107" s="14" t="s">
+      <c r="B107" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="C107" s="14" t="s">
+      <c r="C107" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="D107" s="13">
-        <v>20</v>
+      <c r="D107" s="12">
+        <v>6.666666666666667</v>
       </c>
       <c r="E107" t="s">
         <v>11</v>
@@ -6265,14 +6253,14 @@
       <c r="A108">
         <v>1</v>
       </c>
-      <c r="B108" s="14" t="s">
+      <c r="B108" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="C108" s="14" t="s">
+      <c r="C108" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="D108" s="13">
-        <v>22</v>
+      <c r="D108" s="12">
+        <v>7.333333333333333</v>
       </c>
       <c r="E108" t="s">
         <v>11</v>
@@ -6288,14 +6276,14 @@
       <c r="A109">
         <v>1</v>
       </c>
-      <c r="B109" s="14" t="s">
+      <c r="B109" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="C109" s="14" t="s">
+      <c r="C109" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="D109" s="13">
-        <v>26</v>
+      <c r="D109" s="12">
+        <v>8.6666666666666661</v>
       </c>
       <c r="E109" t="s">
         <v>11</v>
@@ -6311,14 +6299,14 @@
       <c r="A110">
         <v>1</v>
       </c>
-      <c r="B110" s="14" t="s">
+      <c r="B110" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="C110" s="14" t="s">
+      <c r="C110" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="D110" s="13">
-        <v>28</v>
+      <c r="D110" s="12">
+        <v>9.3333333333333339</v>
       </c>
       <c r="E110" t="s">
         <v>11</v>
@@ -6334,14 +6322,14 @@
       <c r="A111">
         <v>1</v>
       </c>
-      <c r="B111" s="14" t="s">
+      <c r="B111" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="C111" s="14" t="s">
+      <c r="C111" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="D111" s="13">
-        <v>24</v>
+      <c r="D111" s="12">
+        <v>8</v>
       </c>
       <c r="E111" t="s">
         <v>11</v>
@@ -6357,14 +6345,14 @@
       <c r="A112">
         <v>1</v>
       </c>
-      <c r="B112" s="14" t="s">
+      <c r="B112" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="C112" s="14" t="s">
+      <c r="C112" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="D112" s="13">
-        <v>14</v>
+      <c r="D112" s="12">
+        <v>4.666666666666667</v>
       </c>
       <c r="E112" t="s">
         <v>11</v>
@@ -6376,18 +6364,18 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>1</v>
       </c>
-      <c r="B113" s="14" t="s">
+      <c r="B113" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="C113" s="14" t="s">
+      <c r="C113" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="D113" s="13">
-        <v>10</v>
+      <c r="D113" s="12">
+        <v>3.3333333333333335</v>
       </c>
       <c r="E113" t="s">
         <v>11</v>
@@ -6399,18 +6387,18 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>1</v>
       </c>
-      <c r="B114" s="14" t="s">
+      <c r="B114" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="C114" s="14" t="s">
+      <c r="C114" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="D114" s="13">
-        <v>10</v>
+      <c r="D114" s="12">
+        <v>3.3333333333333335</v>
       </c>
       <c r="E114" t="s">
         <v>11</v>
@@ -6422,18 +6410,18 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>1</v>
       </c>
-      <c r="B115" s="14" t="s">
+      <c r="B115" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="C115" s="14" t="s">
+      <c r="C115" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="D115" s="13">
-        <v>18</v>
+      <c r="D115" s="12">
+        <v>6</v>
       </c>
       <c r="E115" t="s">
         <v>11</v>
@@ -6445,18 +6433,18 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>1</v>
       </c>
-      <c r="B116" s="14" t="s">
+      <c r="B116" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="C116" s="14" t="s">
+      <c r="C116" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="D116" s="13">
-        <v>22</v>
+      <c r="D116" s="12">
+        <v>7.333333333333333</v>
       </c>
       <c r="E116" t="s">
         <v>11</v>
@@ -6468,18 +6456,18 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>1</v>
       </c>
-      <c r="B117" s="14" t="s">
+      <c r="B117" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="C117" s="14" t="s">
+      <c r="C117" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="D117" s="13">
-        <v>24</v>
+      <c r="D117" s="12">
+        <v>8</v>
       </c>
       <c r="E117" t="s">
         <v>11</v>
@@ -6491,18 +6479,18 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>1</v>
       </c>
-      <c r="B118" s="14" t="s">
+      <c r="B118" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="C118" s="14" t="s">
+      <c r="C118" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="D118" s="13">
-        <v>18</v>
+      <c r="D118" s="12">
+        <v>6</v>
       </c>
       <c r="E118" t="s">
         <v>11</v>
@@ -6514,18 +6502,18 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>1</v>
       </c>
-      <c r="B119" s="14" t="s">
+      <c r="B119" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="C119" s="14" t="s">
+      <c r="C119" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="D119" s="13">
-        <v>10</v>
+      <c r="D119" s="12">
+        <v>3.3333333333333335</v>
       </c>
       <c r="E119" t="s">
         <v>11</v>
@@ -6537,17 +6525,17 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>1</v>
       </c>
-      <c r="B120" s="14" t="s">
+      <c r="B120" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="C120" s="14" t="s">
+      <c r="C120" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="D120" s="13">
+      <c r="D120" s="12">
         <v>0</v>
       </c>
       <c r="E120" t="s">
@@ -6560,17 +6548,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>2</v>
       </c>
-      <c r="B121" s="14" t="s">
+      <c r="B121" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C121" s="14" t="s">
+      <c r="C121" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D121" s="13">
+      <c r="D121" s="12">
         <v>2.5</v>
       </c>
       <c r="E121" t="s">
@@ -6582,19 +6570,18 @@
       <c r="G121">
         <v>1.3</v>
       </c>
-      <c r="J121" s="12"/>
-    </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>2</v>
       </c>
-      <c r="B122" s="14" t="s">
+      <c r="B122" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C122" s="14" t="s">
+      <c r="C122" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D122" s="13">
+      <c r="D122" s="12">
         <v>6</v>
       </c>
       <c r="E122" t="s">
@@ -6606,19 +6593,18 @@
       <c r="G122">
         <v>1.3</v>
       </c>
-      <c r="J122" s="12"/>
-    </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>2</v>
       </c>
-      <c r="B123" s="14" t="s">
+      <c r="B123" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C123" s="14" t="s">
+      <c r="C123" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D123" s="13">
+      <c r="D123" s="12">
         <v>7</v>
       </c>
       <c r="E123" t="s">
@@ -6630,19 +6616,18 @@
       <c r="G123">
         <v>1.3</v>
       </c>
-      <c r="J123" s="12"/>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>2</v>
       </c>
-      <c r="B124" s="14" t="s">
+      <c r="B124" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C124" s="14" t="s">
+      <c r="C124" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D124" s="13">
+      <c r="D124" s="12">
         <v>4</v>
       </c>
       <c r="E124" t="s">
@@ -6654,19 +6639,18 @@
       <c r="G124">
         <v>1.3</v>
       </c>
-      <c r="J124" s="12"/>
-    </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>2</v>
       </c>
-      <c r="B125" s="14" t="s">
+      <c r="B125" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C125" s="14" t="s">
+      <c r="C125" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D125" s="13">
+      <c r="D125" s="12">
         <v>3</v>
       </c>
       <c r="E125" t="s">
@@ -6678,19 +6662,18 @@
       <c r="G125">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J125" s="12"/>
-    </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>2</v>
       </c>
-      <c r="B126" s="14" t="s">
+      <c r="B126" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C126" s="14" t="s">
+      <c r="C126" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D126" s="13">
+      <c r="D126" s="12">
         <v>9</v>
       </c>
       <c r="E126" t="s">
@@ -6702,19 +6685,18 @@
       <c r="G126">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J126" s="12"/>
-    </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>2</v>
       </c>
-      <c r="B127" s="14" t="s">
+      <c r="B127" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C127" s="14" t="s">
+      <c r="C127" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D127" s="13">
+      <c r="D127" s="12">
         <v>14</v>
       </c>
       <c r="E127" t="s">
@@ -6726,19 +6708,18 @@
       <c r="G127">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J127" s="12"/>
-    </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>2</v>
       </c>
-      <c r="B128" s="14" t="s">
+      <c r="B128" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C128" s="14" t="s">
+      <c r="C128" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D128" s="13">
+      <c r="D128" s="12">
         <v>8</v>
       </c>
       <c r="E128" t="s">
@@ -6750,19 +6731,18 @@
       <c r="G128">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J128" s="12"/>
-    </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>2</v>
       </c>
-      <c r="B129" s="14" t="s">
+      <c r="B129" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C129" s="14" t="s">
+      <c r="C129" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D129" s="13">
+      <c r="D129" s="12">
         <v>2</v>
       </c>
       <c r="E129" t="s">
@@ -6774,19 +6754,18 @@
       <c r="G129">
         <v>1.8</v>
       </c>
-      <c r="J129" s="12"/>
-    </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>2</v>
       </c>
-      <c r="B130" s="14" t="s">
+      <c r="B130" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C130" s="14" t="s">
+      <c r="C130" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D130" s="13">
+      <c r="D130" s="12">
         <v>1.5</v>
       </c>
       <c r="E130" t="s">
@@ -6798,19 +6777,18 @@
       <c r="G130">
         <v>1.8</v>
       </c>
-      <c r="J130" s="12"/>
-    </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>2</v>
       </c>
-      <c r="B131" s="14" t="s">
+      <c r="B131" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C131" s="14" t="s">
+      <c r="C131" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D131" s="13">
+      <c r="D131" s="12">
         <v>2.5</v>
       </c>
       <c r="E131" t="s">
@@ -6822,19 +6800,18 @@
       <c r="G131">
         <v>1.8</v>
       </c>
-      <c r="J131" s="12"/>
-    </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>2</v>
       </c>
-      <c r="B132" s="14" t="s">
+      <c r="B132" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C132" s="14" t="s">
+      <c r="C132" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D132" s="13">
+      <c r="D132" s="12">
         <v>6</v>
       </c>
       <c r="E132" t="s">
@@ -6846,19 +6823,18 @@
       <c r="G132">
         <v>1.8</v>
       </c>
-      <c r="J132" s="12"/>
-    </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>2</v>
       </c>
-      <c r="B133" s="14" t="s">
+      <c r="B133" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C133" s="14" t="s">
+      <c r="C133" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D133" s="13">
+      <c r="D133" s="12">
         <v>9</v>
       </c>
       <c r="E133" t="s">
@@ -6870,19 +6846,18 @@
       <c r="G133">
         <v>2.8</v>
       </c>
-      <c r="J133" s="12"/>
-    </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>2</v>
       </c>
-      <c r="B134" s="14" t="s">
+      <c r="B134" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C134" s="14" t="s">
+      <c r="C134" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D134" s="13">
+      <c r="D134" s="12">
         <v>10</v>
       </c>
       <c r="E134" t="s">
@@ -6894,19 +6869,18 @@
       <c r="G134">
         <v>2.8</v>
       </c>
-      <c r="J134" s="12"/>
-    </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>2</v>
       </c>
-      <c r="B135" s="14" t="s">
+      <c r="B135" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C135" s="14" t="s">
+      <c r="C135" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="D135" s="13">
+      <c r="D135" s="12">
         <v>6</v>
       </c>
       <c r="E135" t="s">
@@ -6918,19 +6892,18 @@
       <c r="G135">
         <v>2.8</v>
       </c>
-      <c r="J135" s="12"/>
-    </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>2</v>
       </c>
-      <c r="B136" s="14" t="s">
+      <c r="B136" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C136" s="14" t="s">
+      <c r="C136" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D136" s="13">
+      <c r="D136" s="12">
         <v>2.5</v>
       </c>
       <c r="E136" t="s">
@@ -6942,19 +6915,18 @@
       <c r="G136">
         <v>2.8</v>
       </c>
-      <c r="J136" s="12"/>
-    </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>2</v>
       </c>
-      <c r="B137" s="14" t="s">
+      <c r="B137" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="C137" s="14" t="s">
+      <c r="C137" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D137" s="13">
+      <c r="D137" s="12">
         <v>0</v>
       </c>
       <c r="E137" t="s">
@@ -6966,19 +6938,18 @@
       <c r="G137">
         <v>2</v>
       </c>
-      <c r="J137" s="12"/>
-    </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>2</v>
       </c>
-      <c r="B138" s="14" t="s">
+      <c r="B138" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C138" s="14" t="s">
+      <c r="C138" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="D138" s="13">
+      <c r="D138" s="12">
         <v>2.5</v>
       </c>
       <c r="E138" t="s">
@@ -6990,19 +6961,18 @@
       <c r="G138">
         <v>1.3</v>
       </c>
-      <c r="J138" s="12"/>
-    </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>2</v>
       </c>
-      <c r="B139" s="14" t="s">
+      <c r="B139" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C139" s="14" t="s">
+      <c r="C139" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D139" s="13">
+      <c r="D139" s="12">
         <v>7</v>
       </c>
       <c r="E139" t="s">
@@ -7014,19 +6984,18 @@
       <c r="G139">
         <v>1.3</v>
       </c>
-      <c r="J139" s="12"/>
-    </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>2</v>
       </c>
-      <c r="B140" s="14" t="s">
+      <c r="B140" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C140" s="14" t="s">
+      <c r="C140" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="D140" s="13">
+      <c r="D140" s="12">
         <v>7.5</v>
       </c>
       <c r="E140" t="s">
@@ -7038,19 +7007,18 @@
       <c r="G140">
         <v>1.3</v>
       </c>
-      <c r="J140" s="12"/>
-    </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>2</v>
       </c>
-      <c r="B141" s="14" t="s">
+      <c r="B141" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C141" s="14" t="s">
+      <c r="C141" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="D141" s="13">
+      <c r="D141" s="12">
         <v>4</v>
       </c>
       <c r="E141" t="s">
@@ -7062,19 +7030,18 @@
       <c r="G141">
         <v>1.3</v>
       </c>
-      <c r="J141" s="12"/>
-    </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>2</v>
       </c>
-      <c r="B142" s="14" t="s">
+      <c r="B142" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C142" s="14" t="s">
+      <c r="C142" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D142" s="13">
+      <c r="D142" s="12">
         <v>3</v>
       </c>
       <c r="E142" t="s">
@@ -7086,19 +7053,18 @@
       <c r="G142">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J142" s="12"/>
-    </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>2</v>
       </c>
-      <c r="B143" s="14" t="s">
+      <c r="B143" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C143" s="14" t="s">
+      <c r="C143" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="D143" s="13">
+      <c r="D143" s="12">
         <v>9.5</v>
       </c>
       <c r="E143" t="s">
@@ -7110,19 +7076,18 @@
       <c r="G143">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J143" s="12"/>
-    </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>2</v>
       </c>
-      <c r="B144" s="14" t="s">
+      <c r="B144" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="C144" s="14" t="s">
+      <c r="C144" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="D144" s="13">
+      <c r="D144" s="12">
         <v>14.5</v>
       </c>
       <c r="E144" t="s">
@@ -7134,19 +7099,18 @@
       <c r="G144">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J144" s="12"/>
-    </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>2</v>
       </c>
-      <c r="B145" s="14" t="s">
+      <c r="B145" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="C145" s="14" t="s">
+      <c r="C145" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D145" s="13">
+      <c r="D145" s="12">
         <v>8</v>
       </c>
       <c r="E145" t="s">
@@ -7158,19 +7122,18 @@
       <c r="G145">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J145" s="12"/>
-    </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>2</v>
       </c>
-      <c r="B146" s="14" t="s">
+      <c r="B146" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="C146" s="14" t="s">
+      <c r="C146" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="D146" s="13">
+      <c r="D146" s="12">
         <v>2</v>
       </c>
       <c r="E146" t="s">
@@ -7182,19 +7145,18 @@
       <c r="G146">
         <v>1.8</v>
       </c>
-      <c r="J146" s="12"/>
-    </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>2</v>
       </c>
-      <c r="B147" s="14" t="s">
+      <c r="B147" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="C147" s="14" t="s">
+      <c r="C147" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="D147" s="13">
+      <c r="D147" s="12">
         <v>1.5</v>
       </c>
       <c r="E147" t="s">
@@ -7206,19 +7168,18 @@
       <c r="G147">
         <v>1.8</v>
       </c>
-      <c r="J147" s="12"/>
-    </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>2</v>
       </c>
-      <c r="B148" s="14" t="s">
+      <c r="B148" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="C148" s="14" t="s">
+      <c r="C148" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="D148" s="13">
+      <c r="D148" s="12">
         <v>3</v>
       </c>
       <c r="E148" t="s">
@@ -7230,19 +7191,18 @@
       <c r="G148">
         <v>1.8</v>
       </c>
-      <c r="J148" s="12"/>
-    </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>2</v>
       </c>
-      <c r="B149" s="14" t="s">
+      <c r="B149" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="C149" s="14" t="s">
+      <c r="C149" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="D149" s="13">
+      <c r="D149" s="12">
         <v>6</v>
       </c>
       <c r="E149" t="s">
@@ -7254,19 +7214,18 @@
       <c r="G149">
         <v>1.8</v>
       </c>
-      <c r="J149" s="12"/>
-    </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>2</v>
       </c>
-      <c r="B150" s="14" t="s">
+      <c r="B150" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="C150" s="14" t="s">
+      <c r="C150" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="D150" s="13">
+      <c r="D150" s="12">
         <v>9.5</v>
       </c>
       <c r="E150" t="s">
@@ -7278,19 +7237,18 @@
       <c r="G150">
         <v>2.8</v>
       </c>
-      <c r="J150" s="12"/>
-    </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>2</v>
       </c>
-      <c r="B151" s="14" t="s">
+      <c r="B151" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="C151" s="14" t="s">
+      <c r="C151" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="D151" s="13">
+      <c r="D151" s="12">
         <v>12.5</v>
       </c>
       <c r="E151" t="s">
@@ -7302,19 +7260,18 @@
       <c r="G151">
         <v>2.8</v>
       </c>
-      <c r="J151" s="12"/>
-    </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>2</v>
       </c>
-      <c r="B152" s="14" t="s">
+      <c r="B152" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C152" s="14" t="s">
+      <c r="C152" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D152" s="13">
+      <c r="D152" s="12">
         <v>6</v>
       </c>
       <c r="E152" t="s">
@@ -7326,19 +7283,18 @@
       <c r="G152">
         <v>2.8</v>
       </c>
-      <c r="J152" s="12"/>
-    </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>2</v>
       </c>
-      <c r="B153" s="14" t="s">
+      <c r="B153" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="C153" s="14" t="s">
+      <c r="C153" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="D153" s="13">
+      <c r="D153" s="12">
         <v>2.5</v>
       </c>
       <c r="E153" t="s">
@@ -7350,19 +7306,18 @@
       <c r="G153">
         <v>2.8</v>
       </c>
-      <c r="J153" s="12"/>
-    </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>2</v>
       </c>
-      <c r="B154" s="14" t="s">
+      <c r="B154" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="C154" s="14" t="s">
+      <c r="C154" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="D154" s="13">
+      <c r="D154" s="12">
         <v>0</v>
       </c>
       <c r="E154" t="s">
@@ -7374,19 +7329,18 @@
       <c r="G154">
         <v>2</v>
       </c>
-      <c r="J154" s="12"/>
-    </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>2</v>
       </c>
-      <c r="B155" s="14" t="s">
+      <c r="B155" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C155" s="14" t="s">
+      <c r="C155" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="D155" s="13">
+      <c r="D155" s="12">
         <v>2.5</v>
       </c>
       <c r="E155" t="s">
@@ -7398,19 +7352,18 @@
       <c r="G155">
         <v>1.3</v>
       </c>
-      <c r="J155" s="12"/>
-    </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>2</v>
       </c>
-      <c r="B156" s="14" t="s">
+      <c r="B156" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C156" s="14" t="s">
+      <c r="C156" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="D156" s="13">
+      <c r="D156" s="12">
         <v>6.5</v>
       </c>
       <c r="E156" t="s">
@@ -7422,19 +7375,18 @@
       <c r="G156">
         <v>1.3</v>
       </c>
-      <c r="J156" s="12"/>
-    </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>2</v>
       </c>
-      <c r="B157" s="14" t="s">
+      <c r="B157" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="C157" s="14" t="s">
+      <c r="C157" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="D157" s="13">
+      <c r="D157" s="12">
         <v>7.5</v>
       </c>
       <c r="E157" t="s">
@@ -7446,19 +7398,18 @@
       <c r="G157">
         <v>1.3</v>
       </c>
-      <c r="J157" s="12"/>
-    </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>2</v>
       </c>
-      <c r="B158" s="14" t="s">
+      <c r="B158" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C158" s="14" t="s">
+      <c r="C158" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="D158" s="13">
+      <c r="D158" s="12">
         <v>4</v>
       </c>
       <c r="E158" t="s">
@@ -7470,19 +7421,18 @@
       <c r="G158">
         <v>1.3</v>
       </c>
-      <c r="J158" s="12"/>
-    </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>2</v>
       </c>
-      <c r="B159" s="14" t="s">
+      <c r="B159" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C159" s="14" t="s">
+      <c r="C159" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="D159" s="13">
+      <c r="D159" s="12">
         <v>3</v>
       </c>
       <c r="E159" t="s">
@@ -7494,19 +7444,18 @@
       <c r="G159">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J159" s="12"/>
-    </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>2</v>
       </c>
-      <c r="B160" s="14" t="s">
+      <c r="B160" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C160" s="14" t="s">
+      <c r="C160" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="D160" s="13">
+      <c r="D160" s="12">
         <v>10</v>
       </c>
       <c r="E160" t="s">
@@ -7518,19 +7467,18 @@
       <c r="G160">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J160" s="12"/>
-    </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>2</v>
       </c>
-      <c r="B161" s="14" t="s">
+      <c r="B161" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C161" s="14" t="s">
+      <c r="C161" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="D161" s="13">
+      <c r="D161" s="12">
         <v>14.5</v>
       </c>
       <c r="E161" t="s">
@@ -7542,19 +7490,18 @@
       <c r="G161">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J161" s="12"/>
-    </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>2</v>
       </c>
-      <c r="B162" s="14" t="s">
+      <c r="B162" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C162" s="14" t="s">
+      <c r="C162" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D162" s="13">
+      <c r="D162" s="12">
         <v>8</v>
       </c>
       <c r="E162" t="s">
@@ -7566,19 +7513,18 @@
       <c r="G162">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J162" s="12"/>
-    </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>2</v>
       </c>
-      <c r="B163" s="14" t="s">
+      <c r="B163" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="C163" s="14" t="s">
+      <c r="C163" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="D163" s="13">
+      <c r="D163" s="12">
         <v>2</v>
       </c>
       <c r="E163" t="s">
@@ -7590,19 +7536,18 @@
       <c r="G163">
         <v>1.8</v>
       </c>
-      <c r="J163" s="12"/>
-    </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>2</v>
       </c>
-      <c r="B164" s="14" t="s">
+      <c r="B164" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="C164" s="14" t="s">
+      <c r="C164" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="D164" s="13">
+      <c r="D164" s="12">
         <v>1.5</v>
       </c>
       <c r="E164" t="s">
@@ -7614,19 +7559,18 @@
       <c r="G164">
         <v>1.8</v>
       </c>
-      <c r="J164" s="12"/>
-    </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>2</v>
       </c>
-      <c r="B165" s="14" t="s">
+      <c r="B165" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="C165" s="14" t="s">
+      <c r="C165" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="D165" s="13">
+      <c r="D165" s="12">
         <v>3</v>
       </c>
       <c r="E165" t="s">
@@ -7638,19 +7582,18 @@
       <c r="G165">
         <v>1.8</v>
       </c>
-      <c r="J165" s="12"/>
-    </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>2</v>
       </c>
-      <c r="B166" s="14" t="s">
+      <c r="B166" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="C166" s="14" t="s">
+      <c r="C166" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="D166" s="13">
+      <c r="D166" s="12">
         <v>6.5</v>
       </c>
       <c r="E166" t="s">
@@ -7662,19 +7605,18 @@
       <c r="G166">
         <v>1.8</v>
       </c>
-      <c r="J166" s="12"/>
-    </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>2</v>
       </c>
-      <c r="B167" s="14" t="s">
+      <c r="B167" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="C167" s="14" t="s">
+      <c r="C167" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="D167" s="13">
+      <c r="D167" s="12">
         <v>9.5</v>
       </c>
       <c r="E167" t="s">
@@ -7686,19 +7628,18 @@
       <c r="G167">
         <v>2.8</v>
       </c>
-      <c r="J167" s="12"/>
-    </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>2</v>
       </c>
-      <c r="B168" s="14" t="s">
+      <c r="B168" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C168" s="14" t="s">
+      <c r="C168" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="D168" s="13">
+      <c r="D168" s="12">
         <v>10.5</v>
       </c>
       <c r="E168" t="s">
@@ -7710,19 +7651,18 @@
       <c r="G168">
         <v>2.8</v>
       </c>
-      <c r="J168" s="12"/>
-    </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>2</v>
       </c>
-      <c r="B169" s="14" t="s">
+      <c r="B169" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C169" s="14" t="s">
+      <c r="C169" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="D169" s="13">
+      <c r="D169" s="12">
         <v>6.5</v>
       </c>
       <c r="E169" t="s">
@@ -7734,19 +7674,18 @@
       <c r="G169">
         <v>2.8</v>
       </c>
-      <c r="J169" s="12"/>
-    </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>2</v>
       </c>
-      <c r="B170" s="14" t="s">
+      <c r="B170" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="C170" s="14" t="s">
+      <c r="C170" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="D170" s="13">
+      <c r="D170" s="12">
         <v>3</v>
       </c>
       <c r="E170" t="s">
@@ -7758,19 +7697,18 @@
       <c r="G170">
         <v>2.8</v>
       </c>
-      <c r="J170" s="12"/>
-    </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>2</v>
       </c>
-      <c r="B171" s="14" t="s">
+      <c r="B171" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="C171" s="14" t="s">
+      <c r="C171" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="D171" s="13">
+      <c r="D171" s="12">
         <v>0</v>
       </c>
       <c r="E171" t="s">
@@ -7782,19 +7720,18 @@
       <c r="G171">
         <v>2</v>
       </c>
-      <c r="J171" s="12"/>
-    </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>2</v>
       </c>
-      <c r="B172" s="14" t="s">
+      <c r="B172" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="C172" s="14" t="s">
+      <c r="C172" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="D172" s="13">
+      <c r="D172" s="12">
         <v>3</v>
       </c>
       <c r="E172" t="s">
@@ -7806,19 +7743,18 @@
       <c r="G172">
         <v>1.3</v>
       </c>
-      <c r="J172" s="12"/>
-    </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>2</v>
       </c>
-      <c r="B173" s="14" t="s">
+      <c r="B173" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="C173" s="14" t="s">
+      <c r="C173" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="D173" s="13">
+      <c r="D173" s="12">
         <v>7</v>
       </c>
       <c r="E173" t="s">
@@ -7830,19 +7766,18 @@
       <c r="G173">
         <v>1.3</v>
       </c>
-      <c r="J173" s="12"/>
-    </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>2</v>
       </c>
-      <c r="B174" s="14" t="s">
+      <c r="B174" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="C174" s="14" t="s">
+      <c r="C174" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="D174" s="13">
+      <c r="D174" s="12">
         <v>8</v>
       </c>
       <c r="E174" t="s">
@@ -7854,19 +7789,18 @@
       <c r="G174">
         <v>1.3</v>
       </c>
-      <c r="J174" s="12"/>
-    </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>2</v>
       </c>
-      <c r="B175" s="14" t="s">
+      <c r="B175" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C175" s="14" t="s">
+      <c r="C175" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="D175" s="13">
+      <c r="D175" s="12">
         <v>4.5</v>
       </c>
       <c r="E175" t="s">
@@ -7878,19 +7812,18 @@
       <c r="G175">
         <v>1.3</v>
       </c>
-      <c r="J175" s="12"/>
-    </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>2</v>
       </c>
-      <c r="B176" s="14" t="s">
+      <c r="B176" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="C176" s="14" t="s">
+      <c r="C176" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="D176" s="13">
+      <c r="D176" s="12">
         <v>3.5</v>
       </c>
       <c r="E176" t="s">
@@ -7902,19 +7835,18 @@
       <c r="G176">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J176" s="12"/>
-    </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177">
         <v>2</v>
       </c>
-      <c r="B177" s="14" t="s">
+      <c r="B177" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="C177" s="14" t="s">
+      <c r="C177" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="D177" s="13">
+      <c r="D177" s="12">
         <v>10</v>
       </c>
       <c r="E177" t="s">
@@ -7926,19 +7858,18 @@
       <c r="G177">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J177" s="12"/>
-    </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>2</v>
       </c>
-      <c r="B178" s="14" t="s">
+      <c r="B178" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C178" s="14" t="s">
+      <c r="C178" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="D178" s="13">
+      <c r="D178" s="12">
         <v>15</v>
       </c>
       <c r="E178" t="s">
@@ -7950,19 +7881,18 @@
       <c r="G178">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J178" s="12"/>
-    </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179">
         <v>2</v>
       </c>
-      <c r="B179" s="14" t="s">
+      <c r="B179" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="C179" s="14" t="s">
+      <c r="C179" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D179" s="13">
+      <c r="D179" s="12">
         <v>8.5</v>
       </c>
       <c r="E179" t="s">
@@ -7974,19 +7904,18 @@
       <c r="G179">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J179" s="12"/>
-    </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180">
         <v>2</v>
       </c>
-      <c r="B180" s="14" t="s">
+      <c r="B180" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="C180" s="14" t="s">
+      <c r="C180" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="D180" s="13">
+      <c r="D180" s="12">
         <v>2.5</v>
       </c>
       <c r="E180" t="s">
@@ -7998,19 +7927,18 @@
       <c r="G180">
         <v>1.8</v>
       </c>
-      <c r="J180" s="12"/>
-    </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181">
         <v>2</v>
       </c>
-      <c r="B181" s="14" t="s">
+      <c r="B181" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="C181" s="14" t="s">
+      <c r="C181" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="D181" s="13">
+      <c r="D181" s="12">
         <v>2</v>
       </c>
       <c r="E181" t="s">
@@ -8022,19 +7950,18 @@
       <c r="G181">
         <v>1.8</v>
       </c>
-      <c r="J181" s="12"/>
-    </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182">
         <v>2</v>
       </c>
-      <c r="B182" s="14" t="s">
+      <c r="B182" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="C182" s="14" t="s">
+      <c r="C182" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="D182" s="13">
+      <c r="D182" s="12">
         <v>3.5</v>
       </c>
       <c r="E182" t="s">
@@ -8046,19 +7973,18 @@
       <c r="G182">
         <v>1.8</v>
       </c>
-      <c r="J182" s="12"/>
-    </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183">
         <v>2</v>
       </c>
-      <c r="B183" s="14" t="s">
+      <c r="B183" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="C183" s="14" t="s">
+      <c r="C183" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="D183" s="13">
+      <c r="D183" s="12">
         <v>7.5</v>
       </c>
       <c r="E183" t="s">
@@ -8070,19 +7996,18 @@
       <c r="G183">
         <v>1.8</v>
       </c>
-      <c r="J183" s="12"/>
-    </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>2</v>
       </c>
-      <c r="B184" s="14" t="s">
+      <c r="B184" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="C184" s="14" t="s">
+      <c r="C184" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="D184" s="13">
+      <c r="D184" s="12">
         <v>10</v>
       </c>
       <c r="E184" t="s">
@@ -8094,19 +8019,18 @@
       <c r="G184">
         <v>2.8</v>
       </c>
-      <c r="J184" s="12"/>
-    </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>2</v>
       </c>
-      <c r="B185" s="14" t="s">
+      <c r="B185" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="C185" s="14" t="s">
+      <c r="C185" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="D185" s="13">
+      <c r="D185" s="12">
         <v>11</v>
       </c>
       <c r="E185" t="s">
@@ -8118,19 +8042,18 @@
       <c r="G185">
         <v>2.8</v>
       </c>
-      <c r="J185" s="12"/>
-    </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186">
         <v>2</v>
       </c>
-      <c r="B186" s="14" t="s">
+      <c r="B186" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="C186" s="14" t="s">
+      <c r="C186" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="D186" s="13">
+      <c r="D186" s="12">
         <v>7.5</v>
       </c>
       <c r="E186" t="s">
@@ -8142,19 +8065,18 @@
       <c r="G186">
         <v>2.8</v>
       </c>
-      <c r="J186" s="12"/>
-    </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187">
         <v>2</v>
       </c>
-      <c r="B187" s="14" t="s">
+      <c r="B187" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C187" s="14" t="s">
+      <c r="C187" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="D187" s="13">
+      <c r="D187" s="12">
         <v>3.5</v>
       </c>
       <c r="E187" t="s">
@@ -8166,19 +8088,18 @@
       <c r="G187">
         <v>2.8</v>
       </c>
-      <c r="J187" s="12"/>
-    </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188">
         <v>2</v>
       </c>
-      <c r="B188" s="14" t="s">
+      <c r="B188" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="C188" s="14" t="s">
+      <c r="C188" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="D188" s="13">
+      <c r="D188" s="12">
         <v>0</v>
       </c>
       <c r="E188" t="s">
@@ -8190,19 +8111,18 @@
       <c r="G188">
         <v>2</v>
       </c>
-      <c r="J188" s="12"/>
-    </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189">
         <v>2</v>
       </c>
-      <c r="B189" s="14" t="s">
+      <c r="B189" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="C189" s="14" t="s">
+      <c r="C189" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="D189" s="13">
+      <c r="D189" s="12">
         <v>3</v>
       </c>
       <c r="E189" t="s">
@@ -8214,19 +8134,18 @@
       <c r="G189">
         <v>1.3</v>
       </c>
-      <c r="J189" s="12"/>
-    </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190">
         <v>2</v>
       </c>
-      <c r="B190" s="14" t="s">
+      <c r="B190" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="C190" s="14" t="s">
+      <c r="C190" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="D190" s="13">
+      <c r="D190" s="12">
         <v>7.5</v>
       </c>
       <c r="E190" t="s">
@@ -8238,19 +8157,18 @@
       <c r="G190">
         <v>1.3</v>
       </c>
-      <c r="J190" s="12"/>
-    </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191">
         <v>2</v>
       </c>
-      <c r="B191" s="14" t="s">
+      <c r="B191" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="C191" s="14" t="s">
+      <c r="C191" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="D191" s="13">
+      <c r="D191" s="12">
         <v>8.5</v>
       </c>
       <c r="E191" t="s">
@@ -8262,19 +8180,18 @@
       <c r="G191">
         <v>1.3</v>
       </c>
-      <c r="J191" s="12"/>
-    </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192">
         <v>2</v>
       </c>
-      <c r="B192" s="14" t="s">
+      <c r="B192" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="C192" s="14" t="s">
+      <c r="C192" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="D192" s="13">
+      <c r="D192" s="12">
         <v>5</v>
       </c>
       <c r="E192" t="s">
@@ -8286,19 +8203,18 @@
       <c r="G192">
         <v>1.3</v>
       </c>
-      <c r="J192" s="12"/>
-    </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193">
         <v>2</v>
       </c>
-      <c r="B193" s="14" t="s">
+      <c r="B193" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="C193" s="14" t="s">
+      <c r="C193" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="D193" s="13">
+      <c r="D193" s="12">
         <v>4.5</v>
       </c>
       <c r="E193" t="s">
@@ -8310,19 +8226,18 @@
       <c r="G193">
         <v>2.5</v>
       </c>
-      <c r="J193" s="12"/>
-    </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194">
         <v>2</v>
       </c>
-      <c r="B194" s="14" t="s">
+      <c r="B194" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="C194" s="14" t="s">
+      <c r="C194" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="D194" s="13">
+      <c r="D194" s="12">
         <v>11</v>
       </c>
       <c r="E194" t="s">
@@ -8334,19 +8249,18 @@
       <c r="G194">
         <v>2.5</v>
       </c>
-      <c r="J194" s="12"/>
-    </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195">
         <v>2</v>
       </c>
-      <c r="B195" s="14" t="s">
+      <c r="B195" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="C195" s="14" t="s">
+      <c r="C195" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="D195" s="13">
+      <c r="D195" s="12">
         <v>16</v>
       </c>
       <c r="E195" t="s">
@@ -8358,19 +8272,18 @@
       <c r="G195">
         <v>2.5</v>
       </c>
-      <c r="J195" s="12"/>
-    </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196">
         <v>2</v>
       </c>
-      <c r="B196" s="14" t="s">
+      <c r="B196" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="C196" s="14" t="s">
+      <c r="C196" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="D196" s="13">
+      <c r="D196" s="12">
         <v>10</v>
       </c>
       <c r="E196" t="s">
@@ -8382,19 +8295,18 @@
       <c r="G196">
         <v>2.5</v>
       </c>
-      <c r="J196" s="12"/>
-    </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197">
         <v>2</v>
       </c>
-      <c r="B197" s="14" t="s">
+      <c r="B197" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="C197" s="14" t="s">
+      <c r="C197" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="D197" s="13">
+      <c r="D197" s="12">
         <v>3</v>
       </c>
       <c r="E197" t="s">
@@ -8406,19 +8318,18 @@
       <c r="G197">
         <v>2</v>
       </c>
-      <c r="J197" s="12"/>
-    </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198">
         <v>2</v>
       </c>
-      <c r="B198" s="14" t="s">
+      <c r="B198" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="C198" s="14" t="s">
+      <c r="C198" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="D198" s="13">
+      <c r="D198" s="12">
         <v>3.5</v>
       </c>
       <c r="E198" t="s">
@@ -8430,19 +8341,18 @@
       <c r="G198">
         <v>2</v>
       </c>
-      <c r="J198" s="12"/>
-    </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199">
         <v>2</v>
       </c>
-      <c r="B199" s="14" t="s">
+      <c r="B199" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="C199" s="14" t="s">
+      <c r="C199" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="D199" s="13">
+      <c r="D199" s="12">
         <v>6</v>
       </c>
       <c r="E199" t="s">
@@ -8454,19 +8364,18 @@
       <c r="G199">
         <v>2</v>
       </c>
-      <c r="J199" s="12"/>
-    </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200">
         <v>2</v>
       </c>
-      <c r="B200" s="14" t="s">
+      <c r="B200" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="C200" s="14" t="s">
+      <c r="C200" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="D200" s="13">
+      <c r="D200" s="12">
         <v>9</v>
       </c>
       <c r="E200" t="s">
@@ -8478,19 +8387,18 @@
       <c r="G200">
         <v>2</v>
       </c>
-      <c r="J200" s="12"/>
-    </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201">
         <v>2</v>
       </c>
-      <c r="B201" s="14" t="s">
+      <c r="B201" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="C201" s="14" t="s">
+      <c r="C201" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="D201" s="13">
+      <c r="D201" s="12">
         <v>13</v>
       </c>
       <c r="E201" t="s">
@@ -8502,19 +8410,18 @@
       <c r="G201">
         <v>3.8</v>
       </c>
-      <c r="J201" s="12"/>
-    </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202">
         <v>2</v>
       </c>
-      <c r="B202" s="14" t="s">
+      <c r="B202" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="C202" s="14" t="s">
+      <c r="C202" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="D202" s="13">
+      <c r="D202" s="12">
         <v>14</v>
       </c>
       <c r="E202" t="s">
@@ -8526,19 +8433,18 @@
       <c r="G202">
         <v>3.8</v>
       </c>
-      <c r="J202" s="12"/>
-    </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203">
         <v>2</v>
       </c>
-      <c r="B203" s="14" t="s">
+      <c r="B203" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="C203" s="14" t="s">
+      <c r="C203" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="D203" s="13">
+      <c r="D203" s="12">
         <v>11</v>
       </c>
       <c r="E203" t="s">
@@ -8550,19 +8456,18 @@
       <c r="G203">
         <v>3.8</v>
       </c>
-      <c r="J203" s="12"/>
-    </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204">
         <v>2</v>
       </c>
-      <c r="B204" s="14" t="s">
+      <c r="B204" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="C204" s="14" t="s">
+      <c r="C204" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="D204" s="13">
+      <c r="D204" s="12">
         <v>6</v>
       </c>
       <c r="E204" t="s">
@@ -8574,19 +8479,18 @@
       <c r="G204">
         <v>3.8</v>
       </c>
-      <c r="J204" s="12"/>
-    </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205">
         <v>2</v>
       </c>
-      <c r="B205" s="14" t="s">
+      <c r="B205" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="C205" s="14" t="s">
+      <c r="C205" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="D205" s="13">
+      <c r="D205" s="12">
         <v>0</v>
       </c>
       <c r="E205" t="s">
@@ -8598,19 +8502,18 @@
       <c r="G205">
         <v>2.5</v>
       </c>
-      <c r="J205" s="12"/>
-    </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206">
         <v>2</v>
       </c>
-      <c r="B206" s="14" t="s">
+      <c r="B206" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="C206" s="14" t="s">
+      <c r="C206" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="D206" s="13">
+      <c r="D206" s="12">
         <v>1.5</v>
       </c>
       <c r="E206" t="s">
@@ -8622,19 +8525,18 @@
       <c r="G206">
         <v>2</v>
       </c>
-      <c r="J206" s="12"/>
-    </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207">
         <v>2</v>
       </c>
-      <c r="B207" s="14" t="s">
+      <c r="B207" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="C207" s="14" t="s">
+      <c r="C207" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="D207" s="13">
+      <c r="D207" s="12">
         <v>3</v>
       </c>
       <c r="E207" t="s">
@@ -8646,19 +8548,18 @@
       <c r="G207">
         <v>2</v>
       </c>
-      <c r="J207" s="12"/>
-    </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208">
         <v>2</v>
       </c>
-      <c r="B208" s="14" t="s">
+      <c r="B208" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="C208" s="14" t="s">
+      <c r="C208" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="D208" s="13">
+      <c r="D208" s="12">
         <v>8</v>
       </c>
       <c r="E208" t="s">
@@ -8670,19 +8571,18 @@
       <c r="G208">
         <v>2</v>
       </c>
-      <c r="J208" s="12"/>
-    </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209">
         <v>2</v>
       </c>
-      <c r="B209" s="14" t="s">
+      <c r="B209" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="C209" s="14" t="s">
+      <c r="C209" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="D209" s="13">
+      <c r="D209" s="12">
         <v>12</v>
       </c>
       <c r="E209" t="s">
@@ -8694,19 +8594,18 @@
       <c r="G209">
         <v>2</v>
       </c>
-      <c r="J209" s="12"/>
-    </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210">
         <v>2</v>
       </c>
-      <c r="B210" s="14" t="s">
+      <c r="B210" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C210" s="14" t="s">
+      <c r="C210" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D210" s="13">
+      <c r="D210" s="12">
         <v>13</v>
       </c>
       <c r="E210" t="s">
@@ -8718,19 +8617,18 @@
       <c r="G210">
         <v>3.5</v>
       </c>
-      <c r="J210" s="12"/>
-    </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211">
         <v>2</v>
       </c>
-      <c r="B211" s="14" t="s">
+      <c r="B211" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="C211" s="14" t="s">
+      <c r="C211" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="D211" s="13">
+      <c r="D211" s="12">
         <v>12</v>
       </c>
       <c r="E211" t="s">
@@ -8742,19 +8640,18 @@
       <c r="G211">
         <v>3.5</v>
       </c>
-      <c r="J211" s="12"/>
-    </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212">
         <v>2</v>
       </c>
-      <c r="B212" s="14" t="s">
+      <c r="B212" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="C212" s="14" t="s">
+      <c r="C212" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="D212" s="13">
+      <c r="D212" s="12">
         <v>14</v>
       </c>
       <c r="E212" t="s">
@@ -8766,19 +8663,18 @@
       <c r="G212">
         <v>3.5</v>
       </c>
-      <c r="J212" s="12"/>
-    </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A213">
         <v>2</v>
       </c>
-      <c r="B213" s="14" t="s">
+      <c r="B213" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="C213" s="14" t="s">
+      <c r="C213" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="D213" s="13">
+      <c r="D213" s="12">
         <v>12</v>
       </c>
       <c r="E213" t="s">
@@ -8790,19 +8686,18 @@
       <c r="G213">
         <v>3.5</v>
       </c>
-      <c r="J213" s="12"/>
-    </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214">
         <v>2</v>
       </c>
-      <c r="B214" s="14" t="s">
+      <c r="B214" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="C214" s="14" t="s">
+      <c r="C214" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="D214" s="13">
+      <c r="D214" s="12">
         <v>6</v>
       </c>
       <c r="E214" t="s">
@@ -8814,19 +8709,18 @@
       <c r="G214">
         <v>2.5</v>
       </c>
-      <c r="J214" s="12"/>
-    </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215">
         <v>2</v>
       </c>
-      <c r="B215" s="14" t="s">
+      <c r="B215" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="C215" s="14" t="s">
+      <c r="C215" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="D215" s="13">
+      <c r="D215" s="12">
         <v>5</v>
       </c>
       <c r="E215" t="s">
@@ -8838,19 +8732,18 @@
       <c r="G215">
         <v>2.5</v>
       </c>
-      <c r="J215" s="12"/>
-    </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A216">
         <v>2</v>
       </c>
-      <c r="B216" s="14" t="s">
+      <c r="B216" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="C216" s="14" t="s">
+      <c r="C216" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D216" s="13">
+      <c r="D216" s="12">
         <v>7</v>
       </c>
       <c r="E216" t="s">
@@ -8862,19 +8755,18 @@
       <c r="G216">
         <v>2.5</v>
       </c>
-      <c r="J216" s="12"/>
-    </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A217">
         <v>2</v>
       </c>
-      <c r="B217" s="14" t="s">
+      <c r="B217" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="C217" s="14" t="s">
+      <c r="C217" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="D217" s="13">
+      <c r="D217" s="12">
         <v>11</v>
       </c>
       <c r="E217" t="s">
@@ -8886,19 +8778,18 @@
       <c r="G217">
         <v>2.5</v>
       </c>
-      <c r="J217" s="12"/>
-    </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218">
         <v>2</v>
       </c>
-      <c r="B218" s="14" t="s">
+      <c r="B218" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="C218" s="14" t="s">
+      <c r="C218" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="D218" s="13">
+      <c r="D218" s="12">
         <v>15</v>
       </c>
       <c r="E218" t="s">
@@ -8910,19 +8801,18 @@
       <c r="G218">
         <v>4.2</v>
       </c>
-      <c r="J218" s="12"/>
-    </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A219">
         <v>2</v>
       </c>
-      <c r="B219" s="14" t="s">
+      <c r="B219" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="C219" s="14" t="s">
+      <c r="C219" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="D219" s="13">
+      <c r="D219" s="12">
         <v>16</v>
       </c>
       <c r="E219" t="s">
@@ -8934,19 +8824,18 @@
       <c r="G219">
         <v>4.2</v>
       </c>
-      <c r="J219" s="12"/>
-    </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220">
         <v>2</v>
       </c>
-      <c r="B220" s="14" t="s">
+      <c r="B220" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="C220" s="14" t="s">
+      <c r="C220" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="D220" s="13">
+      <c r="D220" s="12">
         <v>13</v>
       </c>
       <c r="E220" t="s">
@@ -8958,19 +8847,18 @@
       <c r="G220">
         <v>4.2</v>
       </c>
-      <c r="J220" s="12"/>
-    </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221">
         <v>2</v>
       </c>
-      <c r="B221" s="14" t="s">
+      <c r="B221" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="C221" s="14" t="s">
+      <c r="C221" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="D221" s="13">
+      <c r="D221" s="12">
         <v>8</v>
       </c>
       <c r="E221" t="s">
@@ -8982,19 +8870,18 @@
       <c r="G221">
         <v>4.2</v>
       </c>
-      <c r="J221" s="12"/>
-    </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A222">
         <v>2</v>
       </c>
-      <c r="B222" s="14" t="s">
+      <c r="B222" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="C222" s="14" t="s">
+      <c r="C222" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="D222" s="13">
+      <c r="D222" s="12">
         <v>0</v>
       </c>
       <c r="E222" t="s">
@@ -9006,19 +8893,18 @@
       <c r="G222">
         <v>3</v>
       </c>
-      <c r="J222" s="12"/>
-    </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223">
         <v>2</v>
       </c>
-      <c r="B223" s="14" t="s">
+      <c r="B223" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="C223" s="14" t="s">
+      <c r="C223" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="D223" s="13">
+      <c r="D223" s="12">
         <v>1.5</v>
       </c>
       <c r="E223" t="s">
@@ -9030,19 +8916,18 @@
       <c r="G223">
         <v>2</v>
       </c>
-      <c r="J223" s="12"/>
-    </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224">
         <v>2</v>
       </c>
-      <c r="B224" s="14" t="s">
+      <c r="B224" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="C224" s="14" t="s">
+      <c r="C224" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="D224" s="13">
+      <c r="D224" s="12">
         <v>2.5</v>
       </c>
       <c r="E224" t="s">
@@ -9054,19 +8939,18 @@
       <c r="G224">
         <v>2</v>
       </c>
-      <c r="J224" s="12"/>
-    </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A225">
         <v>2</v>
       </c>
-      <c r="B225" s="14" t="s">
+      <c r="B225" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="C225" s="14" t="s">
+      <c r="C225" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="D225" s="13">
+      <c r="D225" s="12">
         <v>7</v>
       </c>
       <c r="E225" t="s">
@@ -9078,19 +8962,18 @@
       <c r="G225">
         <v>2</v>
       </c>
-      <c r="J225" s="12"/>
-    </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A226">
         <v>2</v>
       </c>
-      <c r="B226" s="14" t="s">
+      <c r="B226" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="C226" s="14" t="s">
+      <c r="C226" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="D226" s="13">
+      <c r="D226" s="12">
         <v>10</v>
       </c>
       <c r="E226" t="s">
@@ -9102,19 +8985,18 @@
       <c r="G226">
         <v>2</v>
       </c>
-      <c r="J226" s="12"/>
-    </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227">
         <v>2</v>
       </c>
-      <c r="B227" s="14" t="s">
+      <c r="B227" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="C227" s="14" t="s">
+      <c r="C227" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="D227" s="13">
+      <c r="D227" s="12">
         <v>11</v>
       </c>
       <c r="E227" t="s">
@@ -9126,19 +9008,18 @@
       <c r="G227">
         <v>3.5</v>
       </c>
-      <c r="J227" s="12"/>
-    </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A228">
         <v>2</v>
       </c>
-      <c r="B228" s="14" t="s">
+      <c r="B228" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="C228" s="14" t="s">
+      <c r="C228" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="D228" s="13">
+      <c r="D228" s="12">
         <v>13</v>
       </c>
       <c r="E228" t="s">
@@ -9150,19 +9031,18 @@
       <c r="G228">
         <v>3.5</v>
       </c>
-      <c r="J228" s="12"/>
-    </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A229">
         <v>2</v>
       </c>
-      <c r="B229" s="14" t="s">
+      <c r="B229" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="C229" s="14" t="s">
+      <c r="C229" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="D229" s="13">
+      <c r="D229" s="12">
         <v>14</v>
       </c>
       <c r="E229" t="s">
@@ -9174,19 +9054,18 @@
       <c r="G229">
         <v>3.5</v>
       </c>
-      <c r="J229" s="12"/>
-    </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230">
         <v>2</v>
       </c>
-      <c r="B230" s="14" t="s">
+      <c r="B230" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="C230" s="14" t="s">
+      <c r="C230" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="D230" s="13">
+      <c r="D230" s="12">
         <v>12</v>
       </c>
       <c r="E230" t="s">
@@ -9198,19 +9077,18 @@
       <c r="G230">
         <v>3.5</v>
       </c>
-      <c r="J230" s="12"/>
-    </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A231">
         <v>2</v>
       </c>
-      <c r="B231" s="14" t="s">
+      <c r="B231" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="C231" s="14" t="s">
+      <c r="C231" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="D231" s="13">
+      <c r="D231" s="12">
         <v>7</v>
       </c>
       <c r="E231" t="s">
@@ -9222,19 +9100,18 @@
       <c r="G231">
         <v>2.5</v>
       </c>
-      <c r="J231" s="12"/>
-    </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A232">
         <v>2</v>
       </c>
-      <c r="B232" s="14" t="s">
+      <c r="B232" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="C232" s="14" t="s">
+      <c r="C232" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="D232" s="13">
+      <c r="D232" s="12">
         <v>5</v>
       </c>
       <c r="E232" t="s">
@@ -9246,19 +9123,18 @@
       <c r="G232">
         <v>2.5</v>
       </c>
-      <c r="J232" s="12"/>
-    </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A233">
         <v>2</v>
       </c>
-      <c r="B233" s="14" t="s">
+      <c r="B233" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="C233" s="14" t="s">
+      <c r="C233" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="D233" s="13">
+      <c r="D233" s="12">
         <v>5</v>
       </c>
       <c r="E233" t="s">
@@ -9270,19 +9146,18 @@
       <c r="G233">
         <v>2.5</v>
       </c>
-      <c r="J233" s="12"/>
-    </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A234">
         <v>2</v>
       </c>
-      <c r="B234" s="14" t="s">
+      <c r="B234" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="C234" s="14" t="s">
+      <c r="C234" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="D234" s="13">
+      <c r="D234" s="12">
         <v>9</v>
       </c>
       <c r="E234" t="s">
@@ -9294,19 +9169,18 @@
       <c r="G234">
         <v>2.5</v>
       </c>
-      <c r="J234" s="12"/>
-    </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A235">
         <v>2</v>
       </c>
-      <c r="B235" s="14" t="s">
+      <c r="B235" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="C235" s="14" t="s">
+      <c r="C235" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="D235" s="13">
+      <c r="D235" s="12">
         <v>11</v>
       </c>
       <c r="E235" t="s">
@@ -9318,19 +9192,18 @@
       <c r="G235">
         <v>4.2</v>
       </c>
-      <c r="J235" s="12"/>
-    </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A236">
         <v>2</v>
       </c>
-      <c r="B236" s="14" t="s">
+      <c r="B236" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="C236" s="14" t="s">
+      <c r="C236" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="D236" s="13">
+      <c r="D236" s="12">
         <v>12</v>
       </c>
       <c r="E236" t="s">
@@ -9342,19 +9215,18 @@
       <c r="G236">
         <v>4.2</v>
       </c>
-      <c r="J236" s="12"/>
-    </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A237">
         <v>2</v>
       </c>
-      <c r="B237" s="14" t="s">
+      <c r="B237" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="C237" s="14" t="s">
+      <c r="C237" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="D237" s="13">
+      <c r="D237" s="12">
         <v>9</v>
       </c>
       <c r="E237" t="s">
@@ -9366,19 +9238,18 @@
       <c r="G237">
         <v>4.2</v>
       </c>
-      <c r="J237" s="12"/>
-    </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A238">
         <v>2</v>
       </c>
-      <c r="B238" s="14" t="s">
+      <c r="B238" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="C238" s="14" t="s">
+      <c r="C238" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="D238" s="13">
+      <c r="D238" s="12">
         <v>5</v>
       </c>
       <c r="E238" t="s">
@@ -9390,19 +9261,18 @@
       <c r="G238">
         <v>4.2</v>
       </c>
-      <c r="J238" s="12"/>
-    </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A239">
         <v>2</v>
       </c>
-      <c r="B239" s="14" t="s">
+      <c r="B239" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="C239" s="14" t="s">
+      <c r="C239" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="D239" s="13">
+      <c r="D239" s="12">
         <v>0</v>
       </c>
       <c r="E239" t="s">
@@ -9414,7 +9284,6 @@
       <c r="G239">
         <v>0</v>
       </c>
-      <c r="J239" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/scripts/restaurant_variables.xlsx
+++ b/scripts/restaurant_variables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\loren\Desktop\Simulation\Progetto\Restaurant_2025\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6389F4E-875A-48A8-9645-FAEAFE40CB7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FF148C4-FB29-4439-BB2F-CFB750259F8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="19420" tabRatio="851" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -744,6 +744,15 @@
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="23">
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="none">
@@ -908,6 +917,18 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
     </dxf>
     <dxf>
@@ -921,27 +942,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -999,10 +999,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{7D1585E5-EB18-4555-BFB4-AB049789BB50}" name="tables_selection" displayName="tables_selection" ref="A1:J11" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:J11" xr:uid="{7D1585E5-EB18-4555-BFB4-AB049789BB50}"/>
   <tableColumns count="10">
-    <tableColumn id="10" xr3:uid="{1ADF8E6C-C756-4DB0-AF29-730090E9A389}" uniqueName="10" name="scenario" queryTableFieldId="10" dataDxfId="19"/>
-    <tableColumn id="1" xr3:uid="{9DF6AF6D-4327-4E8B-A17C-4CE32200A2CC}" uniqueName="1" name="start_timestamp" queryTableFieldId="1" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{DB186560-5030-4DB1-A6BD-A74C44B2F90A}" uniqueName="2" name="end_timestamp" queryTableFieldId="2" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{6CE09762-A225-468B-8C15-326E109C4C41}" uniqueName="3" name="period" queryTableFieldId="3" dataDxfId="16"/>
+    <tableColumn id="10" xr3:uid="{1ADF8E6C-C756-4DB0-AF29-730090E9A389}" uniqueName="10" name="scenario" queryTableFieldId="10" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{9DF6AF6D-4327-4E8B-A17C-4CE32200A2CC}" uniqueName="1" name="start_timestamp" queryTableFieldId="1" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{DB186560-5030-4DB1-A6BD-A74C44B2F90A}" uniqueName="2" name="end_timestamp" queryTableFieldId="2" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{6CE09762-A225-468B-8C15-326E109C4C41}" uniqueName="3" name="period" queryTableFieldId="3" dataDxfId="13"/>
     <tableColumn id="4" xr3:uid="{90771DE1-93AE-42DD-88DE-8292168CC27F}" uniqueName="4" name="bar_on" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{2D6F5E1B-E207-46D0-A78B-EA6977317860}" uniqueName="5" name="inside_on" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{5AFB94CB-8BB6-4AE5-B6B3-D1BD6C86A1FB}" uniqueName="6" name="outside_on" queryTableFieldId="6"/>
@@ -1018,12 +1018,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{54D2211C-274A-47E4-BDD0-4C0951D8DD68}" name="employees_schedule" displayName="employees_schedule" ref="A1:H71" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:H71" xr:uid="{54D2211C-274A-47E4-BDD0-4C0951D8DD68}"/>
   <tableColumns count="8">
-    <tableColumn id="15" xr3:uid="{C7ED7AB4-5A31-4D81-834A-B6E64F7023C8}" uniqueName="15" name="scenario" queryTableFieldId="9" dataDxfId="15"/>
-    <tableColumn id="1" xr3:uid="{1826F0BC-F6D0-44C5-8A93-C7D99BD8CB8B}" uniqueName="1" name="start_timestamp" queryTableFieldId="1" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{75D23335-1496-4011-81D1-D6034B72FF11}" uniqueName="2" name="end_timestamp" queryTableFieldId="2" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{92C90E84-B1B0-4866-9DDC-2A2B72F890FA}" uniqueName="4" name="weekday" queryTableFieldId="4" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{954429F6-A3DE-46A7-885B-49BC6CAF5664}" uniqueName="5" name="hour" queryTableFieldId="5" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{D0D42E6A-14B4-4741-A3F6-DD9143A88038}" uniqueName="6" name="period" queryTableFieldId="6" dataDxfId="10"/>
+    <tableColumn id="15" xr3:uid="{C7ED7AB4-5A31-4D81-834A-B6E64F7023C8}" uniqueName="15" name="scenario" queryTableFieldId="9" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{1826F0BC-F6D0-44C5-8A93-C7D99BD8CB8B}" uniqueName="1" name="start_timestamp" queryTableFieldId="1" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{75D23335-1496-4011-81D1-D6034B72FF11}" uniqueName="2" name="end_timestamp" queryTableFieldId="2" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{92C90E84-B1B0-4866-9DDC-2A2B72F890FA}" uniqueName="4" name="weekday" queryTableFieldId="4" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{954429F6-A3DE-46A7-885B-49BC6CAF5664}" uniqueName="5" name="hour" queryTableFieldId="5" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{D0D42E6A-14B4-4741-A3F6-DD9143A88038}" uniqueName="6" name="period" queryTableFieldId="6" dataDxfId="17"/>
     <tableColumn id="7" xr3:uid="{DC0D317B-9907-4E39-BD04-56F982B6DFC4}" uniqueName="7" name="waiters" queryTableFieldId="7"/>
     <tableColumn id="8" xr3:uid="{5822B03F-BA67-4CAF-8288-1B9FA740A60F}" uniqueName="8" name="cooks" queryTableFieldId="8"/>
   </tableColumns>
@@ -1032,14 +1032,14 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D544813D-DF99-41C8-AE8A-38BE1FAF9E94}" name="Tabella3" displayName="Tabella3" ref="A1:E11" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D544813D-DF99-41C8-AE8A-38BE1FAF9E94}" name="Tabella3" displayName="Tabella3" ref="A1:E11" totalsRowShown="0" headerRowDxfId="12" dataDxfId="10" headerRowBorderDxfId="11" tableBorderDxfId="9" totalsRowBorderDxfId="8">
   <autoFilter ref="A1:E11" xr:uid="{D544813D-DF99-41C8-AE8A-38BE1FAF9E94}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{5F6DE45A-D069-49C3-A965-E57C526C9F10}" name="scenario" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{4D8F0B29-A4FF-499D-9A3B-DCD79E56771F}" name="start_timestamp" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{73FD92A6-7E32-4F59-A6D2-E391CC1529B2}" name="end_timestamp" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{E9B6B43D-80B9-448F-8CE5-DB0428CE9192}" name="period" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{FA561D75-B96F-4DC4-B290-98BCE5AF9EBB}" name="time_avg" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{5F6DE45A-D069-49C3-A965-E57C526C9F10}" name="scenario" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{4D8F0B29-A4FF-499D-9A3B-DCD79E56771F}" name="start_timestamp" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{73FD92A6-7E32-4F59-A6D2-E391CC1529B2}" name="end_timestamp" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{E9B6B43D-80B9-448F-8CE5-DB0428CE9192}" name="period" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{FA561D75-B96F-4DC4-B290-98BCE5AF9EBB}" name="time_avg" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1050,9 +1050,9 @@
   <autoFilter ref="A1:G239" xr:uid="{E79869A8-51C0-465F-A154-CE9C9BB79619}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{C0C152CA-AC82-4A38-9515-01F93B55CD35}" name="scenario"/>
-    <tableColumn id="2" xr3:uid="{A9274257-0F1F-4EC5-AEAD-2D02ED20F27D}" name="start_timestamp" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{8EBF5A3E-33DA-4E63-85B2-6A750FD2B59E}" name="end_timestamp" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{1B570803-0CC6-4039-83E4-466D06E97DE8}" name="arrival_rate" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{A9274257-0F1F-4EC5-AEAD-2D02ED20F27D}" name="start_timestamp" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{8EBF5A3E-33DA-4E63-85B2-6A750FD2B59E}" name="end_timestamp" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{1B570803-0CC6-4039-83E4-466D06E97DE8}" name="arrival_rate" dataDxfId="0"/>
     <tableColumn id="5" xr3:uid="{2330BE18-97F9-494B-A0D2-BC6CD4BE5D26}" name="weekday"/>
     <tableColumn id="6" xr3:uid="{511C9B76-5714-4C6E-B45F-24A76465D0A2}" name="hour"/>
     <tableColumn id="7" xr3:uid="{DDB83C9A-5515-4339-958C-0504A36D7FBA}" name="avg_group_size"/>
@@ -2385,10 +2385,10 @@
         <v>158</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
@@ -2515,10 +2515,10 @@
         <v>158</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
@@ -2645,10 +2645,10 @@
         <v>158</v>
       </c>
       <c r="G36">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H36">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">

--- a/scripts/restaurant_variables.xlsx
+++ b/scripts/restaurant_variables.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">

--- a/scripts/restaurant_variables.xlsx
+++ b/scripts/restaurant_variables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\loren\Desktop\Simulation\Progetto\Restaurant_2025\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FF148C4-FB29-4439-BB2F-CFB750259F8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA4A006E-2F0C-4E53-AA5A-FA26D69BB056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="19420" tabRatio="851" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="arrival_rate_week_groupsize" sheetId="10" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="DatiEsterni_1" localSheetId="1" hidden="1">employees_schedule!$B$1:$H$71</definedName>
+    <definedName name="DatiEsterni_1" localSheetId="1" hidden="1">employees_schedule!$B$1:$H$106</definedName>
     <definedName name="DatiEsterni_2" localSheetId="3" hidden="1">arrival_rate_week_groupsize!$B$1:$G$239</definedName>
     <definedName name="DatiEsterni_3" localSheetId="0" hidden="1">tables_selection!$B$1:$G$11</definedName>
   </definedNames>
@@ -106,7 +106,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="167">
   <si>
     <t>start_timestamp</t>
   </si>
@@ -724,7 +724,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -739,11 +739,30 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="23">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="0.0"/>
     </dxf>
@@ -925,24 +944,6 @@
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -999,10 +1000,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{7D1585E5-EB18-4555-BFB4-AB049789BB50}" name="tables_selection" displayName="tables_selection" ref="A1:J11" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:J11" xr:uid="{7D1585E5-EB18-4555-BFB4-AB049789BB50}"/>
   <tableColumns count="10">
-    <tableColumn id="10" xr3:uid="{1ADF8E6C-C756-4DB0-AF29-730090E9A389}" uniqueName="10" name="scenario" queryTableFieldId="10" dataDxfId="16"/>
-    <tableColumn id="1" xr3:uid="{9DF6AF6D-4327-4E8B-A17C-4CE32200A2CC}" uniqueName="1" name="start_timestamp" queryTableFieldId="1" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{DB186560-5030-4DB1-A6BD-A74C44B2F90A}" uniqueName="2" name="end_timestamp" queryTableFieldId="2" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{6CE09762-A225-468B-8C15-326E109C4C41}" uniqueName="3" name="period" queryTableFieldId="3" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{1ADF8E6C-C756-4DB0-AF29-730090E9A389}" uniqueName="10" name="scenario" queryTableFieldId="10" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{9DF6AF6D-4327-4E8B-A17C-4CE32200A2CC}" uniqueName="1" name="start_timestamp" queryTableFieldId="1" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{DB186560-5030-4DB1-A6BD-A74C44B2F90A}" uniqueName="2" name="end_timestamp" queryTableFieldId="2" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{6CE09762-A225-468B-8C15-326E109C4C41}" uniqueName="3" name="period" queryTableFieldId="3" dataDxfId="19"/>
     <tableColumn id="4" xr3:uid="{90771DE1-93AE-42DD-88DE-8292168CC27F}" uniqueName="4" name="bar_on" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{2D6F5E1B-E207-46D0-A78B-EA6977317860}" uniqueName="5" name="inside_on" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{5AFB94CB-8BB6-4AE5-B6B3-D1BD6C86A1FB}" uniqueName="6" name="outside_on" queryTableFieldId="6"/>
@@ -1015,15 +1016,15 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{54D2211C-274A-47E4-BDD0-4C0951D8DD68}" name="employees_schedule" displayName="employees_schedule" ref="A1:H71" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:H71" xr:uid="{54D2211C-274A-47E4-BDD0-4C0951D8DD68}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{54D2211C-274A-47E4-BDD0-4C0951D8DD68}" name="employees_schedule" displayName="employees_schedule" ref="A1:H106" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:H106" xr:uid="{54D2211C-274A-47E4-BDD0-4C0951D8DD68}"/>
   <tableColumns count="8">
-    <tableColumn id="15" xr3:uid="{C7ED7AB4-5A31-4D81-834A-B6E64F7023C8}" uniqueName="15" name="scenario" queryTableFieldId="9" dataDxfId="22"/>
-    <tableColumn id="1" xr3:uid="{1826F0BC-F6D0-44C5-8A93-C7D99BD8CB8B}" uniqueName="1" name="start_timestamp" queryTableFieldId="1" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{75D23335-1496-4011-81D1-D6034B72FF11}" uniqueName="2" name="end_timestamp" queryTableFieldId="2" dataDxfId="20"/>
-    <tableColumn id="4" xr3:uid="{92C90E84-B1B0-4866-9DDC-2A2B72F890FA}" uniqueName="4" name="weekday" queryTableFieldId="4" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{954429F6-A3DE-46A7-885B-49BC6CAF5664}" uniqueName="5" name="hour" queryTableFieldId="5" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{D0D42E6A-14B4-4741-A3F6-DD9143A88038}" uniqueName="6" name="period" queryTableFieldId="6" dataDxfId="17"/>
+    <tableColumn id="15" xr3:uid="{C7ED7AB4-5A31-4D81-834A-B6E64F7023C8}" uniqueName="15" name="scenario" queryTableFieldId="9" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{1826F0BC-F6D0-44C5-8A93-C7D99BD8CB8B}" uniqueName="1" name="start_timestamp" queryTableFieldId="1" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{75D23335-1496-4011-81D1-D6034B72FF11}" uniqueName="2" name="end_timestamp" queryTableFieldId="2" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{92C90E84-B1B0-4866-9DDC-2A2B72F890FA}" uniqueName="4" name="weekday" queryTableFieldId="4" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{954429F6-A3DE-46A7-885B-49BC6CAF5664}" uniqueName="5" name="hour" queryTableFieldId="5" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{D0D42E6A-14B4-4741-A3F6-DD9143A88038}" uniqueName="6" name="period" queryTableFieldId="6" dataDxfId="0"/>
     <tableColumn id="7" xr3:uid="{DC0D317B-9907-4E39-BD04-56F982B6DFC4}" uniqueName="7" name="waiters" queryTableFieldId="7"/>
     <tableColumn id="8" xr3:uid="{5822B03F-BA67-4CAF-8288-1B9FA740A60F}" uniqueName="8" name="cooks" queryTableFieldId="8"/>
   </tableColumns>
@@ -1032,14 +1033,14 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D544813D-DF99-41C8-AE8A-38BE1FAF9E94}" name="Tabella3" displayName="Tabella3" ref="A1:E11" totalsRowShown="0" headerRowDxfId="12" dataDxfId="10" headerRowBorderDxfId="11" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D544813D-DF99-41C8-AE8A-38BE1FAF9E94}" name="Tabella3" displayName="Tabella3" ref="A1:E11" totalsRowShown="0" headerRowDxfId="18" dataDxfId="16" headerRowBorderDxfId="17" tableBorderDxfId="15" totalsRowBorderDxfId="14">
   <autoFilter ref="A1:E11" xr:uid="{D544813D-DF99-41C8-AE8A-38BE1FAF9E94}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{5F6DE45A-D069-49C3-A965-E57C526C9F10}" name="scenario" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{4D8F0B29-A4FF-499D-9A3B-DCD79E56771F}" name="start_timestamp" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{73FD92A6-7E32-4F59-A6D2-E391CC1529B2}" name="end_timestamp" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{E9B6B43D-80B9-448F-8CE5-DB0428CE9192}" name="period" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{FA561D75-B96F-4DC4-B290-98BCE5AF9EBB}" name="time_avg" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{5F6DE45A-D069-49C3-A965-E57C526C9F10}" name="scenario" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{4D8F0B29-A4FF-499D-9A3B-DCD79E56771F}" name="start_timestamp" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{73FD92A6-7E32-4F59-A6D2-E391CC1529B2}" name="end_timestamp" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{E9B6B43D-80B9-448F-8CE5-DB0428CE9192}" name="period" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{FA561D75-B96F-4DC4-B290-98BCE5AF9EBB}" name="time_avg" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1050,9 +1051,9 @@
   <autoFilter ref="A1:G239" xr:uid="{E79869A8-51C0-465F-A154-CE9C9BB79619}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{C0C152CA-AC82-4A38-9515-01F93B55CD35}" name="scenario"/>
-    <tableColumn id="2" xr3:uid="{A9274257-0F1F-4EC5-AEAD-2D02ED20F27D}" name="start_timestamp" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{8EBF5A3E-33DA-4E63-85B2-6A750FD2B59E}" name="end_timestamp" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{1B570803-0CC6-4039-83E4-466D06E97DE8}" name="arrival_rate" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{A9274257-0F1F-4EC5-AEAD-2D02ED20F27D}" name="start_timestamp" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{8EBF5A3E-33DA-4E63-85B2-6A750FD2B59E}" name="end_timestamp" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{1B570803-0CC6-4039-83E4-466D06E97DE8}" name="arrival_rate" dataDxfId="6"/>
     <tableColumn id="5" xr3:uid="{2330BE18-97F9-494B-A0D2-BC6CD4BE5D26}" name="weekday"/>
     <tableColumn id="6" xr3:uid="{511C9B76-5714-4C6E-B45F-24A76465D0A2}" name="hour"/>
     <tableColumn id="7" xr3:uid="{DDB83C9A-5515-4339-958C-0504A36D7FBA}" name="avg_group_size"/>
@@ -1704,7 +1705,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDE0A4E8-9C6D-48F5-8B37-568D2AC35446}">
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H306"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.26953125" bestFit="1" customWidth="1"/>
@@ -1761,10 +1762,10 @@
         <v>162</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -2671,10 +2672,10 @@
         <v>162</v>
       </c>
       <c r="G37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H37">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
@@ -2723,10 +2724,10 @@
         <v>156</v>
       </c>
       <c r="G39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H39">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
@@ -2801,10 +2802,10 @@
         <v>162</v>
       </c>
       <c r="G42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H42">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
@@ -2853,10 +2854,10 @@
         <v>156</v>
       </c>
       <c r="G44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H44">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
@@ -2931,10 +2932,10 @@
         <v>162</v>
       </c>
       <c r="G47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H47">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
@@ -2983,10 +2984,10 @@
         <v>156</v>
       </c>
       <c r="G49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H49">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
@@ -3061,10 +3062,10 @@
         <v>162</v>
       </c>
       <c r="G52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H52">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
@@ -3113,10 +3114,10 @@
         <v>156</v>
       </c>
       <c r="G54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H54">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.35">
@@ -3191,10 +3192,10 @@
         <v>162</v>
       </c>
       <c r="G57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H57">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.35">
@@ -3243,10 +3244,10 @@
         <v>156</v>
       </c>
       <c r="G59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H59">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.35">
@@ -3321,10 +3322,10 @@
         <v>162</v>
       </c>
       <c r="G62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H62">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.35">
@@ -3425,10 +3426,10 @@
         <v>158</v>
       </c>
       <c r="G66">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H66">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.35">
@@ -3451,10 +3452,10 @@
         <v>162</v>
       </c>
       <c r="G67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H67">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.35">
@@ -3555,11 +3556,2521 @@
         <v>158</v>
       </c>
       <c r="G71">
+        <v>4</v>
+      </c>
+      <c r="H71">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A72">
         <v>3</v>
       </c>
-      <c r="H71">
+      <c r="B72" s="1">
+        <v>25573.291666666668</v>
+      </c>
+      <c r="C72" s="1">
+        <v>25573.458333333332</v>
+      </c>
+      <c r="D72" t="s">
+        <v>5</v>
+      </c>
+      <c r="E72" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="F72" t="s">
+        <v>162</v>
+      </c>
+      <c r="G72">
+        <v>1</v>
+      </c>
+      <c r="H72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A73">
         <v>3</v>
       </c>
+      <c r="B73" s="1">
+        <v>25573.458333333332</v>
+      </c>
+      <c r="C73" s="1">
+        <v>25573.625</v>
+      </c>
+      <c r="D73" t="s">
+        <v>5</v>
+      </c>
+      <c r="E73" s="2">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F73" t="s">
+        <v>155</v>
+      </c>
+      <c r="G73">
+        <v>5</v>
+      </c>
+      <c r="H73">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <v>3</v>
+      </c>
+      <c r="B74" s="1">
+        <v>25573.625</v>
+      </c>
+      <c r="C74" s="1">
+        <v>25573.791666666668</v>
+      </c>
+      <c r="D74" t="s">
+        <v>5</v>
+      </c>
+      <c r="E74" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="F74" t="s">
+        <v>156</v>
+      </c>
+      <c r="G74">
+        <v>2</v>
+      </c>
+      <c r="H74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A75">
+        <v>3</v>
+      </c>
+      <c r="B75" s="1">
+        <v>25573.791666666668</v>
+      </c>
+      <c r="C75" s="1">
+        <v>25573.958333333332</v>
+      </c>
+      <c r="D75" t="s">
+        <v>5</v>
+      </c>
+      <c r="E75" s="2">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F75" t="s">
+        <v>157</v>
+      </c>
+      <c r="G75">
+        <v>6</v>
+      </c>
+      <c r="H75">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A76">
+        <v>3</v>
+      </c>
+      <c r="B76" s="1">
+        <v>25573.958333333332</v>
+      </c>
+      <c r="C76" s="1">
+        <v>25574.291666666668</v>
+      </c>
+      <c r="D76" t="s">
+        <v>5</v>
+      </c>
+      <c r="E76" s="2">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="F76" t="s">
+        <v>158</v>
+      </c>
+      <c r="G76">
+        <v>1</v>
+      </c>
+      <c r="H76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A77">
+        <v>3</v>
+      </c>
+      <c r="B77" s="1">
+        <v>25574.291666666668</v>
+      </c>
+      <c r="C77" s="1">
+        <v>25574.458333333332</v>
+      </c>
+      <c r="D77" t="s">
+        <v>6</v>
+      </c>
+      <c r="E77" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="F77" t="s">
+        <v>162</v>
+      </c>
+      <c r="G77">
+        <v>1</v>
+      </c>
+      <c r="H77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <v>3</v>
+      </c>
+      <c r="B78" s="1">
+        <v>25574.458333333332</v>
+      </c>
+      <c r="C78" s="1">
+        <v>25574.625</v>
+      </c>
+      <c r="D78" t="s">
+        <v>6</v>
+      </c>
+      <c r="E78" s="2">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F78" t="s">
+        <v>155</v>
+      </c>
+      <c r="G78">
+        <v>5</v>
+      </c>
+      <c r="H78">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A79">
+        <v>3</v>
+      </c>
+      <c r="B79" s="1">
+        <v>25574.625</v>
+      </c>
+      <c r="C79" s="1">
+        <v>25574.791666666668</v>
+      </c>
+      <c r="D79" t="s">
+        <v>6</v>
+      </c>
+      <c r="E79" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="F79" t="s">
+        <v>156</v>
+      </c>
+      <c r="G79">
+        <v>2</v>
+      </c>
+      <c r="H79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <v>3</v>
+      </c>
+      <c r="B80" s="1">
+        <v>25574.791666666668</v>
+      </c>
+      <c r="C80" s="1">
+        <v>25574.958333333332</v>
+      </c>
+      <c r="D80" t="s">
+        <v>6</v>
+      </c>
+      <c r="E80" s="2">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F80" t="s">
+        <v>157</v>
+      </c>
+      <c r="G80">
+        <v>6</v>
+      </c>
+      <c r="H80">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A81">
+        <v>3</v>
+      </c>
+      <c r="B81" s="1">
+        <v>25574.958333333332</v>
+      </c>
+      <c r="C81" s="1">
+        <v>25575.291666666668</v>
+      </c>
+      <c r="D81" t="s">
+        <v>6</v>
+      </c>
+      <c r="E81" s="2">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="F81" t="s">
+        <v>158</v>
+      </c>
+      <c r="G81">
+        <v>1</v>
+      </c>
+      <c r="H81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A82">
+        <v>3</v>
+      </c>
+      <c r="B82" s="1">
+        <v>25575.291666666668</v>
+      </c>
+      <c r="C82" s="1">
+        <v>25575.458333333332</v>
+      </c>
+      <c r="D82" t="s">
+        <v>7</v>
+      </c>
+      <c r="E82" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="F82" t="s">
+        <v>162</v>
+      </c>
+      <c r="G82">
+        <v>1</v>
+      </c>
+      <c r="H82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <v>3</v>
+      </c>
+      <c r="B83" s="1">
+        <v>25575.458333333332</v>
+      </c>
+      <c r="C83" s="1">
+        <v>25575.625</v>
+      </c>
+      <c r="D83" t="s">
+        <v>7</v>
+      </c>
+      <c r="E83" s="2">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F83" t="s">
+        <v>155</v>
+      </c>
+      <c r="G83">
+        <v>5</v>
+      </c>
+      <c r="H83">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <v>3</v>
+      </c>
+      <c r="B84" s="1">
+        <v>25575.625</v>
+      </c>
+      <c r="C84" s="1">
+        <v>25575.791666666668</v>
+      </c>
+      <c r="D84" t="s">
+        <v>7</v>
+      </c>
+      <c r="E84" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="F84" t="s">
+        <v>156</v>
+      </c>
+      <c r="G84">
+        <v>2</v>
+      </c>
+      <c r="H84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <v>3</v>
+      </c>
+      <c r="B85" s="1">
+        <v>25575.791666666668</v>
+      </c>
+      <c r="C85" s="1">
+        <v>25575.958333333332</v>
+      </c>
+      <c r="D85" t="s">
+        <v>7</v>
+      </c>
+      <c r="E85" s="2">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F85" t="s">
+        <v>157</v>
+      </c>
+      <c r="G85">
+        <v>6</v>
+      </c>
+      <c r="H85">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A86">
+        <v>3</v>
+      </c>
+      <c r="B86" s="1">
+        <v>25575.958333333332</v>
+      </c>
+      <c r="C86" s="1">
+        <v>25576.291666666668</v>
+      </c>
+      <c r="D86" t="s">
+        <v>7</v>
+      </c>
+      <c r="E86" s="2">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="F86" t="s">
+        <v>158</v>
+      </c>
+      <c r="G86">
+        <v>1</v>
+      </c>
+      <c r="H86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A87">
+        <v>3</v>
+      </c>
+      <c r="B87" s="1">
+        <v>25576.291666666668</v>
+      </c>
+      <c r="C87" s="1">
+        <v>25576.458333333332</v>
+      </c>
+      <c r="D87" t="s">
+        <v>8</v>
+      </c>
+      <c r="E87" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="F87" t="s">
+        <v>162</v>
+      </c>
+      <c r="G87">
+        <v>1</v>
+      </c>
+      <c r="H87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A88">
+        <v>3</v>
+      </c>
+      <c r="B88" s="1">
+        <v>25576.458333333332</v>
+      </c>
+      <c r="C88" s="1">
+        <v>25576.625</v>
+      </c>
+      <c r="D88" t="s">
+        <v>8</v>
+      </c>
+      <c r="E88" s="2">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F88" t="s">
+        <v>155</v>
+      </c>
+      <c r="G88">
+        <v>5</v>
+      </c>
+      <c r="H88">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A89">
+        <v>3</v>
+      </c>
+      <c r="B89" s="1">
+        <v>25576.625</v>
+      </c>
+      <c r="C89" s="1">
+        <v>25576.791666666668</v>
+      </c>
+      <c r="D89" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="F89" t="s">
+        <v>156</v>
+      </c>
+      <c r="G89">
+        <v>2</v>
+      </c>
+      <c r="H89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A90">
+        <v>3</v>
+      </c>
+      <c r="B90" s="1">
+        <v>25576.791666666668</v>
+      </c>
+      <c r="C90" s="1">
+        <v>25576.958333333332</v>
+      </c>
+      <c r="D90" t="s">
+        <v>8</v>
+      </c>
+      <c r="E90" s="2">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F90" t="s">
+        <v>157</v>
+      </c>
+      <c r="G90">
+        <v>6</v>
+      </c>
+      <c r="H90">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A91">
+        <v>3</v>
+      </c>
+      <c r="B91" s="1">
+        <v>25576.958333333332</v>
+      </c>
+      <c r="C91" s="1">
+        <v>25577.291666666668</v>
+      </c>
+      <c r="D91" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="2">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="F91" t="s">
+        <v>158</v>
+      </c>
+      <c r="G91">
+        <v>1</v>
+      </c>
+      <c r="H91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A92">
+        <v>3</v>
+      </c>
+      <c r="B92" s="1">
+        <v>25577.291666666668</v>
+      </c>
+      <c r="C92" s="1">
+        <v>25577.458333333332</v>
+      </c>
+      <c r="D92" t="s">
+        <v>9</v>
+      </c>
+      <c r="E92" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="F92" t="s">
+        <v>162</v>
+      </c>
+      <c r="G92">
+        <v>1</v>
+      </c>
+      <c r="H92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A93">
+        <v>3</v>
+      </c>
+      <c r="B93" s="1">
+        <v>25577.458333333332</v>
+      </c>
+      <c r="C93" s="1">
+        <v>25577.625</v>
+      </c>
+      <c r="D93" t="s">
+        <v>9</v>
+      </c>
+      <c r="E93" s="2">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F93" t="s">
+        <v>155</v>
+      </c>
+      <c r="G93">
+        <v>5</v>
+      </c>
+      <c r="H93">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A94">
+        <v>3</v>
+      </c>
+      <c r="B94" s="1">
+        <v>25577.625</v>
+      </c>
+      <c r="C94" s="1">
+        <v>25577.791666666668</v>
+      </c>
+      <c r="D94" t="s">
+        <v>9</v>
+      </c>
+      <c r="E94" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="F94" t="s">
+        <v>156</v>
+      </c>
+      <c r="G94">
+        <v>2</v>
+      </c>
+      <c r="H94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A95">
+        <v>3</v>
+      </c>
+      <c r="B95" s="1">
+        <v>25577.791666666668</v>
+      </c>
+      <c r="C95" s="1">
+        <v>25577.958333333332</v>
+      </c>
+      <c r="D95" t="s">
+        <v>9</v>
+      </c>
+      <c r="E95" s="2">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F95" t="s">
+        <v>157</v>
+      </c>
+      <c r="G95">
+        <v>6</v>
+      </c>
+      <c r="H95">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A96">
+        <v>3</v>
+      </c>
+      <c r="B96" s="1">
+        <v>25577.958333333332</v>
+      </c>
+      <c r="C96" s="1">
+        <v>25578.291666666668</v>
+      </c>
+      <c r="D96" t="s">
+        <v>9</v>
+      </c>
+      <c r="E96" s="2">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="F96" t="s">
+        <v>158</v>
+      </c>
+      <c r="G96">
+        <v>2</v>
+      </c>
+      <c r="H96">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A97">
+        <v>3</v>
+      </c>
+      <c r="B97" s="1">
+        <v>25578.291666666668</v>
+      </c>
+      <c r="C97" s="1">
+        <v>25578.458333333332</v>
+      </c>
+      <c r="D97" t="s">
+        <v>10</v>
+      </c>
+      <c r="E97" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="F97" t="s">
+        <v>162</v>
+      </c>
+      <c r="G97">
+        <v>1</v>
+      </c>
+      <c r="H97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A98">
+        <v>3</v>
+      </c>
+      <c r="B98" s="1">
+        <v>25578.458333333332</v>
+      </c>
+      <c r="C98" s="1">
+        <v>25578.625</v>
+      </c>
+      <c r="D98" t="s">
+        <v>10</v>
+      </c>
+      <c r="E98" s="2">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F98" t="s">
+        <v>155</v>
+      </c>
+      <c r="G98">
+        <v>5</v>
+      </c>
+      <c r="H98">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A99">
+        <v>3</v>
+      </c>
+      <c r="B99" s="1">
+        <v>25578.625</v>
+      </c>
+      <c r="C99" s="1">
+        <v>25578.791666666668</v>
+      </c>
+      <c r="D99" t="s">
+        <v>10</v>
+      </c>
+      <c r="E99" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="F99" t="s">
+        <v>156</v>
+      </c>
+      <c r="G99">
+        <v>3</v>
+      </c>
+      <c r="H99">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A100">
+        <v>3</v>
+      </c>
+      <c r="B100" s="1">
+        <v>25578.791666666668</v>
+      </c>
+      <c r="C100" s="1">
+        <v>25578.958333333332</v>
+      </c>
+      <c r="D100" t="s">
+        <v>10</v>
+      </c>
+      <c r="E100" s="2">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F100" t="s">
+        <v>157</v>
+      </c>
+      <c r="G100">
+        <v>6</v>
+      </c>
+      <c r="H100">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A101">
+        <v>3</v>
+      </c>
+      <c r="B101" s="1">
+        <v>25578.958333333332</v>
+      </c>
+      <c r="C101" s="1">
+        <v>25579.291666666668</v>
+      </c>
+      <c r="D101" t="s">
+        <v>10</v>
+      </c>
+      <c r="E101" s="2">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="F101" t="s">
+        <v>158</v>
+      </c>
+      <c r="G101">
+        <v>2</v>
+      </c>
+      <c r="H101">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A102">
+        <v>3</v>
+      </c>
+      <c r="B102" s="1">
+        <v>25579.291666666668</v>
+      </c>
+      <c r="C102" s="1">
+        <v>25579.458333333332</v>
+      </c>
+      <c r="D102" t="s">
+        <v>11</v>
+      </c>
+      <c r="E102" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="F102" t="s">
+        <v>162</v>
+      </c>
+      <c r="G102">
+        <v>1</v>
+      </c>
+      <c r="H102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A103">
+        <v>3</v>
+      </c>
+      <c r="B103" s="1">
+        <v>25579.458333333332</v>
+      </c>
+      <c r="C103" s="1">
+        <v>25579.625</v>
+      </c>
+      <c r="D103" t="s">
+        <v>11</v>
+      </c>
+      <c r="E103" s="2">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F103" t="s">
+        <v>155</v>
+      </c>
+      <c r="G103">
+        <v>5</v>
+      </c>
+      <c r="H103">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A104">
+        <v>3</v>
+      </c>
+      <c r="B104" s="1">
+        <v>25579.625</v>
+      </c>
+      <c r="C104" s="1">
+        <v>25579.791666666668</v>
+      </c>
+      <c r="D104" t="s">
+        <v>11</v>
+      </c>
+      <c r="E104" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="F104" t="s">
+        <v>156</v>
+      </c>
+      <c r="G104">
+        <v>2</v>
+      </c>
+      <c r="H104">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A105">
+        <v>3</v>
+      </c>
+      <c r="B105" s="1">
+        <v>25579.791666666668</v>
+      </c>
+      <c r="C105" s="1">
+        <v>25579.958333333332</v>
+      </c>
+      <c r="D105" t="s">
+        <v>11</v>
+      </c>
+      <c r="E105" s="2">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F105" t="s">
+        <v>157</v>
+      </c>
+      <c r="G105">
+        <v>6</v>
+      </c>
+      <c r="H105">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A106">
+        <v>3</v>
+      </c>
+      <c r="B106" s="1">
+        <v>25579.958333333332</v>
+      </c>
+      <c r="C106" s="1">
+        <v>25580.291666666668</v>
+      </c>
+      <c r="D106" t="s">
+        <v>11</v>
+      </c>
+      <c r="E106" s="2">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="F106" t="s">
+        <v>158</v>
+      </c>
+      <c r="G106">
+        <v>2</v>
+      </c>
+      <c r="H106">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A107" s="1"/>
+      <c r="B107" s="1"/>
+      <c r="C107" s="1"/>
+      <c r="D107" s="14"/>
+      <c r="E107" s="2"/>
+      <c r="F107" s="14"/>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A108" s="1"/>
+      <c r="B108" s="1"/>
+      <c r="C108" s="1"/>
+      <c r="D108" s="14"/>
+      <c r="E108" s="2"/>
+      <c r="F108" s="14"/>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A109" s="1"/>
+      <c r="B109" s="1"/>
+      <c r="C109" s="1"/>
+      <c r="D109" s="14"/>
+      <c r="E109" s="2"/>
+      <c r="F109" s="14"/>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A110" s="1"/>
+      <c r="B110" s="1"/>
+      <c r="C110" s="1"/>
+      <c r="D110" s="14"/>
+      <c r="E110" s="2"/>
+      <c r="F110" s="14"/>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A111" s="1"/>
+      <c r="B111" s="1"/>
+      <c r="C111" s="1"/>
+      <c r="D111" s="14"/>
+      <c r="E111" s="2"/>
+      <c r="F111" s="14"/>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A112" s="1"/>
+      <c r="B112" s="1"/>
+      <c r="C112" s="1"/>
+      <c r="D112" s="14"/>
+      <c r="E112" s="2"/>
+      <c r="F112" s="14"/>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A113" s="1"/>
+      <c r="B113" s="1"/>
+      <c r="C113" s="1"/>
+      <c r="D113" s="14"/>
+      <c r="E113" s="2"/>
+      <c r="F113" s="14"/>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A114" s="1"/>
+      <c r="B114" s="1"/>
+      <c r="C114" s="1"/>
+      <c r="D114" s="14"/>
+      <c r="E114" s="2"/>
+      <c r="F114" s="14"/>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A115" s="1"/>
+      <c r="B115" s="1"/>
+      <c r="C115" s="1"/>
+      <c r="D115" s="14"/>
+      <c r="E115" s="2"/>
+      <c r="F115" s="14"/>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A116" s="1"/>
+      <c r="B116" s="1"/>
+      <c r="C116" s="1"/>
+      <c r="D116" s="14"/>
+      <c r="E116" s="2"/>
+      <c r="F116" s="14"/>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A117" s="1"/>
+      <c r="B117" s="1"/>
+      <c r="C117" s="1"/>
+      <c r="D117" s="14"/>
+      <c r="E117" s="2"/>
+      <c r="F117" s="14"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A118" s="1"/>
+      <c r="B118" s="1"/>
+      <c r="C118" s="1"/>
+      <c r="D118" s="14"/>
+      <c r="E118" s="2"/>
+      <c r="F118" s="14"/>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A119" s="1"/>
+      <c r="B119" s="1"/>
+      <c r="C119" s="1"/>
+      <c r="D119" s="14"/>
+      <c r="E119" s="2"/>
+      <c r="F119" s="14"/>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A120" s="1"/>
+      <c r="B120" s="1"/>
+      <c r="C120" s="1"/>
+      <c r="D120" s="14"/>
+      <c r="E120" s="2"/>
+      <c r="F120" s="14"/>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A121" s="1"/>
+      <c r="B121" s="1"/>
+      <c r="C121" s="1"/>
+      <c r="D121" s="14"/>
+      <c r="E121" s="2"/>
+      <c r="F121" s="14"/>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A122" s="1"/>
+      <c r="B122" s="1"/>
+      <c r="C122" s="1"/>
+      <c r="D122" s="14"/>
+      <c r="E122" s="2"/>
+      <c r="F122" s="14"/>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A123" s="1"/>
+      <c r="B123" s="1"/>
+      <c r="C123" s="1"/>
+      <c r="D123" s="14"/>
+      <c r="E123" s="2"/>
+      <c r="F123" s="14"/>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A124" s="1"/>
+      <c r="B124" s="1"/>
+      <c r="C124" s="1"/>
+      <c r="D124" s="14"/>
+      <c r="E124" s="2"/>
+      <c r="F124" s="14"/>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A125" s="1"/>
+      <c r="B125" s="1"/>
+      <c r="C125" s="1"/>
+      <c r="D125" s="14"/>
+      <c r="E125" s="2"/>
+      <c r="F125" s="14"/>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A126" s="1"/>
+      <c r="B126" s="1"/>
+      <c r="C126" s="1"/>
+      <c r="D126" s="14"/>
+      <c r="E126" s="2"/>
+      <c r="F126" s="14"/>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A127" s="1"/>
+      <c r="B127" s="1"/>
+      <c r="C127" s="1"/>
+      <c r="D127" s="14"/>
+      <c r="E127" s="2"/>
+      <c r="F127" s="14"/>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A128" s="1"/>
+      <c r="B128" s="1"/>
+      <c r="C128" s="1"/>
+      <c r="D128" s="14"/>
+      <c r="E128" s="2"/>
+      <c r="F128" s="14"/>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A129" s="1"/>
+      <c r="B129" s="1"/>
+      <c r="C129" s="1"/>
+      <c r="D129" s="14"/>
+      <c r="E129" s="2"/>
+      <c r="F129" s="14"/>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A130" s="1"/>
+      <c r="B130" s="1"/>
+      <c r="C130" s="1"/>
+      <c r="D130" s="14"/>
+      <c r="E130" s="2"/>
+      <c r="F130" s="14"/>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A131" s="1"/>
+      <c r="B131" s="1"/>
+      <c r="C131" s="1"/>
+      <c r="D131" s="14"/>
+      <c r="E131" s="2"/>
+      <c r="F131" s="14"/>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A132" s="1"/>
+      <c r="B132" s="1"/>
+      <c r="C132" s="1"/>
+      <c r="D132" s="14"/>
+      <c r="E132" s="2"/>
+      <c r="F132" s="14"/>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A133" s="1"/>
+      <c r="B133" s="1"/>
+      <c r="C133" s="1"/>
+      <c r="D133" s="14"/>
+      <c r="E133" s="2"/>
+      <c r="F133" s="14"/>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A134" s="1"/>
+      <c r="B134" s="1"/>
+      <c r="C134" s="1"/>
+      <c r="D134" s="14"/>
+      <c r="E134" s="2"/>
+      <c r="F134" s="14"/>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A135" s="1"/>
+      <c r="B135" s="1"/>
+      <c r="C135" s="1"/>
+      <c r="D135" s="14"/>
+      <c r="E135" s="2"/>
+      <c r="F135" s="14"/>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A136" s="1"/>
+      <c r="B136" s="1"/>
+      <c r="C136" s="1"/>
+      <c r="D136" s="14"/>
+      <c r="E136" s="2"/>
+      <c r="F136" s="14"/>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A137" s="1"/>
+      <c r="B137" s="1"/>
+      <c r="C137" s="1"/>
+      <c r="D137" s="14"/>
+      <c r="E137" s="2"/>
+      <c r="F137" s="14"/>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A138" s="1"/>
+      <c r="B138" s="1"/>
+      <c r="C138" s="1"/>
+      <c r="D138" s="14"/>
+      <c r="E138" s="2"/>
+      <c r="F138" s="14"/>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A139" s="1"/>
+      <c r="B139" s="1"/>
+      <c r="C139" s="1"/>
+      <c r="D139" s="14"/>
+      <c r="E139" s="2"/>
+      <c r="F139" s="14"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A140" s="1"/>
+      <c r="B140" s="1"/>
+      <c r="C140" s="1"/>
+      <c r="D140" s="14"/>
+      <c r="E140" s="2"/>
+      <c r="F140" s="14"/>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A141" s="1"/>
+      <c r="B141" s="1"/>
+      <c r="C141" s="1"/>
+      <c r="D141" s="14"/>
+      <c r="E141" s="2"/>
+      <c r="F141" s="14"/>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A142" s="1"/>
+      <c r="B142" s="1"/>
+      <c r="C142" s="1"/>
+      <c r="D142" s="14"/>
+      <c r="E142" s="2"/>
+      <c r="F142" s="14"/>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A143" s="1"/>
+      <c r="B143" s="1"/>
+      <c r="C143" s="1"/>
+      <c r="D143" s="14"/>
+      <c r="E143" s="2"/>
+      <c r="F143" s="14"/>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A144" s="1"/>
+      <c r="B144" s="1"/>
+      <c r="C144" s="1"/>
+      <c r="D144" s="14"/>
+      <c r="E144" s="2"/>
+      <c r="F144" s="14"/>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A145" s="1"/>
+      <c r="B145" s="1"/>
+      <c r="C145" s="1"/>
+      <c r="D145" s="14"/>
+      <c r="E145" s="2"/>
+      <c r="F145" s="14"/>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A146" s="1"/>
+      <c r="B146" s="1"/>
+      <c r="C146" s="1"/>
+      <c r="D146" s="14"/>
+      <c r="E146" s="2"/>
+      <c r="F146" s="14"/>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A147" s="1"/>
+      <c r="B147" s="1"/>
+      <c r="C147" s="1"/>
+      <c r="D147" s="14"/>
+      <c r="E147" s="2"/>
+      <c r="F147" s="14"/>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A148" s="1"/>
+      <c r="B148" s="1"/>
+      <c r="C148" s="1"/>
+      <c r="D148" s="14"/>
+      <c r="E148" s="2"/>
+      <c r="F148" s="14"/>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A149" s="1"/>
+      <c r="B149" s="1"/>
+      <c r="C149" s="1"/>
+      <c r="D149" s="14"/>
+      <c r="E149" s="2"/>
+      <c r="F149" s="14"/>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A150" s="1"/>
+      <c r="B150" s="1"/>
+      <c r="C150" s="1"/>
+      <c r="D150" s="14"/>
+      <c r="E150" s="2"/>
+      <c r="F150" s="14"/>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A151" s="1"/>
+      <c r="B151" s="1"/>
+      <c r="C151" s="1"/>
+      <c r="D151" s="14"/>
+      <c r="E151" s="2"/>
+      <c r="F151" s="14"/>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A152" s="1"/>
+      <c r="B152" s="1"/>
+      <c r="C152" s="1"/>
+      <c r="D152" s="14"/>
+      <c r="E152" s="2"/>
+      <c r="F152" s="14"/>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A153" s="1"/>
+      <c r="B153" s="1"/>
+      <c r="C153" s="1"/>
+      <c r="D153" s="14"/>
+      <c r="E153" s="2"/>
+      <c r="F153" s="14"/>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A154" s="1"/>
+      <c r="B154" s="1"/>
+      <c r="C154" s="1"/>
+      <c r="D154" s="14"/>
+      <c r="E154" s="2"/>
+      <c r="F154" s="14"/>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A155" s="1"/>
+      <c r="B155" s="1"/>
+      <c r="C155" s="1"/>
+      <c r="D155" s="14"/>
+      <c r="E155" s="2"/>
+      <c r="F155" s="14"/>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A156" s="1"/>
+      <c r="B156" s="1"/>
+      <c r="C156" s="1"/>
+      <c r="D156" s="14"/>
+      <c r="E156" s="2"/>
+      <c r="F156" s="14"/>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A157" s="1"/>
+      <c r="B157" s="1"/>
+      <c r="C157" s="1"/>
+      <c r="D157" s="14"/>
+      <c r="E157" s="2"/>
+      <c r="F157" s="14"/>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A158" s="1"/>
+      <c r="B158" s="1"/>
+      <c r="C158" s="1"/>
+      <c r="D158" s="14"/>
+      <c r="E158" s="2"/>
+      <c r="F158" s="14"/>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A159" s="1"/>
+      <c r="B159" s="1"/>
+      <c r="C159" s="1"/>
+      <c r="D159" s="14"/>
+      <c r="E159" s="2"/>
+      <c r="F159" s="14"/>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A160" s="1"/>
+      <c r="B160" s="1"/>
+      <c r="C160" s="1"/>
+      <c r="D160" s="14"/>
+      <c r="E160" s="2"/>
+      <c r="F160" s="14"/>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A161" s="1"/>
+      <c r="B161" s="1"/>
+      <c r="C161" s="1"/>
+      <c r="D161" s="14"/>
+      <c r="E161" s="2"/>
+      <c r="F161" s="14"/>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A162" s="1"/>
+      <c r="B162" s="1"/>
+      <c r="C162" s="1"/>
+      <c r="D162" s="14"/>
+      <c r="E162" s="2"/>
+      <c r="F162" s="14"/>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A163" s="1"/>
+      <c r="B163" s="1"/>
+      <c r="C163" s="1"/>
+      <c r="D163" s="14"/>
+      <c r="E163" s="2"/>
+      <c r="F163" s="14"/>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A164" s="1"/>
+      <c r="B164" s="1"/>
+      <c r="C164" s="1"/>
+      <c r="D164" s="14"/>
+      <c r="E164" s="2"/>
+      <c r="F164" s="14"/>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A165" s="1"/>
+      <c r="B165" s="1"/>
+      <c r="C165" s="1"/>
+      <c r="D165" s="14"/>
+      <c r="E165" s="2"/>
+      <c r="F165" s="14"/>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A166" s="1"/>
+      <c r="B166" s="1"/>
+      <c r="C166" s="1"/>
+      <c r="D166" s="14"/>
+      <c r="E166" s="2"/>
+      <c r="F166" s="14"/>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A167" s="1"/>
+      <c r="B167" s="1"/>
+      <c r="C167" s="1"/>
+      <c r="D167" s="14"/>
+      <c r="E167" s="2"/>
+      <c r="F167" s="14"/>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A168" s="1"/>
+      <c r="B168" s="1"/>
+      <c r="C168" s="1"/>
+      <c r="D168" s="14"/>
+      <c r="E168" s="2"/>
+      <c r="F168" s="14"/>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A169" s="1"/>
+      <c r="B169" s="1"/>
+      <c r="C169" s="1"/>
+      <c r="D169" s="14"/>
+      <c r="E169" s="2"/>
+      <c r="F169" s="14"/>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A170" s="1"/>
+      <c r="B170" s="1"/>
+      <c r="C170" s="1"/>
+      <c r="D170" s="14"/>
+      <c r="E170" s="2"/>
+      <c r="F170" s="14"/>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A171" s="1"/>
+      <c r="B171" s="1"/>
+      <c r="C171" s="1"/>
+      <c r="D171" s="14"/>
+      <c r="E171" s="2"/>
+      <c r="F171" s="14"/>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A172" s="1"/>
+      <c r="B172" s="1"/>
+      <c r="C172" s="1"/>
+      <c r="D172" s="14"/>
+      <c r="E172" s="2"/>
+      <c r="F172" s="14"/>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A173" s="1"/>
+      <c r="B173" s="1"/>
+      <c r="C173" s="1"/>
+      <c r="D173" s="14"/>
+      <c r="E173" s="2"/>
+      <c r="F173" s="14"/>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A174" s="1"/>
+      <c r="B174" s="1"/>
+      <c r="C174" s="1"/>
+      <c r="D174" s="14"/>
+      <c r="E174" s="2"/>
+      <c r="F174" s="14"/>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A175" s="1"/>
+      <c r="B175" s="1"/>
+      <c r="C175" s="1"/>
+      <c r="D175" s="14"/>
+      <c r="E175" s="2"/>
+      <c r="F175" s="14"/>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A176" s="1"/>
+      <c r="B176" s="1"/>
+      <c r="C176" s="1"/>
+      <c r="D176" s="14"/>
+      <c r="E176" s="2"/>
+      <c r="F176" s="14"/>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A177" s="1"/>
+      <c r="B177" s="1"/>
+      <c r="C177" s="1"/>
+      <c r="D177" s="14"/>
+      <c r="E177" s="2"/>
+      <c r="F177" s="14"/>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A178" s="1"/>
+      <c r="B178" s="1"/>
+      <c r="C178" s="1"/>
+      <c r="D178" s="14"/>
+      <c r="E178" s="2"/>
+      <c r="F178" s="14"/>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A179" s="1"/>
+      <c r="B179" s="1"/>
+      <c r="C179" s="1"/>
+      <c r="D179" s="14"/>
+      <c r="E179" s="2"/>
+      <c r="F179" s="14"/>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A180" s="1"/>
+      <c r="B180" s="1"/>
+      <c r="C180" s="1"/>
+      <c r="D180" s="14"/>
+      <c r="E180" s="2"/>
+      <c r="F180" s="14"/>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A181" s="1"/>
+      <c r="B181" s="1"/>
+      <c r="C181" s="1"/>
+      <c r="D181" s="14"/>
+      <c r="E181" s="2"/>
+      <c r="F181" s="14"/>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A182" s="1"/>
+      <c r="B182" s="1"/>
+      <c r="C182" s="1"/>
+      <c r="D182" s="14"/>
+      <c r="E182" s="2"/>
+      <c r="F182" s="14"/>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A183" s="1"/>
+      <c r="B183" s="1"/>
+      <c r="C183" s="1"/>
+      <c r="D183" s="14"/>
+      <c r="E183" s="2"/>
+      <c r="F183" s="14"/>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A184" s="1"/>
+      <c r="B184" s="1"/>
+      <c r="C184" s="1"/>
+      <c r="D184" s="14"/>
+      <c r="E184" s="2"/>
+      <c r="F184" s="14"/>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A185" s="1"/>
+      <c r="B185" s="1"/>
+      <c r="C185" s="1"/>
+      <c r="D185" s="14"/>
+      <c r="E185" s="2"/>
+      <c r="F185" s="14"/>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A186" s="1"/>
+      <c r="B186" s="1"/>
+      <c r="C186" s="1"/>
+      <c r="D186" s="14"/>
+      <c r="E186" s="2"/>
+      <c r="F186" s="14"/>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A187" s="1"/>
+      <c r="B187" s="1"/>
+      <c r="C187" s="1"/>
+      <c r="D187" s="14"/>
+      <c r="E187" s="2"/>
+      <c r="F187" s="14"/>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A188" s="1"/>
+      <c r="B188" s="1"/>
+      <c r="C188" s="1"/>
+      <c r="D188" s="14"/>
+      <c r="E188" s="2"/>
+      <c r="F188" s="14"/>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A189" s="1"/>
+      <c r="B189" s="1"/>
+      <c r="C189" s="1"/>
+      <c r="D189" s="14"/>
+      <c r="E189" s="2"/>
+      <c r="F189" s="14"/>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A190" s="1"/>
+      <c r="B190" s="1"/>
+      <c r="C190" s="1"/>
+      <c r="D190" s="14"/>
+      <c r="E190" s="2"/>
+      <c r="F190" s="14"/>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A191" s="1"/>
+      <c r="B191" s="1"/>
+      <c r="C191" s="1"/>
+      <c r="D191" s="14"/>
+      <c r="E191" s="2"/>
+      <c r="F191" s="14"/>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A192" s="1"/>
+      <c r="B192" s="1"/>
+      <c r="C192" s="1"/>
+      <c r="D192" s="14"/>
+      <c r="E192" s="2"/>
+      <c r="F192" s="14"/>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A193" s="1"/>
+      <c r="B193" s="1"/>
+      <c r="C193" s="1"/>
+      <c r="D193" s="14"/>
+      <c r="E193" s="2"/>
+      <c r="F193" s="14"/>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A194" s="1"/>
+      <c r="B194" s="1"/>
+      <c r="C194" s="1"/>
+      <c r="D194" s="14"/>
+      <c r="E194" s="2"/>
+      <c r="F194" s="14"/>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A195" s="1"/>
+      <c r="B195" s="1"/>
+      <c r="C195" s="1"/>
+      <c r="D195" s="14"/>
+      <c r="E195" s="2"/>
+      <c r="F195" s="14"/>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A196" s="1"/>
+      <c r="B196" s="1"/>
+      <c r="C196" s="1"/>
+      <c r="D196" s="14"/>
+      <c r="E196" s="2"/>
+      <c r="F196" s="14"/>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A197" s="1"/>
+      <c r="B197" s="1"/>
+      <c r="C197" s="1"/>
+      <c r="D197" s="14"/>
+      <c r="E197" s="2"/>
+      <c r="F197" s="14"/>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A198" s="1"/>
+      <c r="B198" s="1"/>
+      <c r="C198" s="1"/>
+      <c r="D198" s="14"/>
+      <c r="E198" s="2"/>
+      <c r="F198" s="14"/>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A199" s="1"/>
+      <c r="B199" s="1"/>
+      <c r="C199" s="1"/>
+      <c r="D199" s="14"/>
+      <c r="E199" s="2"/>
+      <c r="F199" s="14"/>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A200" s="1"/>
+      <c r="B200" s="1"/>
+      <c r="C200" s="1"/>
+      <c r="D200" s="14"/>
+      <c r="E200" s="2"/>
+      <c r="F200" s="14"/>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A201" s="1"/>
+      <c r="B201" s="1"/>
+      <c r="C201" s="1"/>
+      <c r="D201" s="14"/>
+      <c r="E201" s="2"/>
+      <c r="F201" s="14"/>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A202" s="1"/>
+      <c r="B202" s="1"/>
+      <c r="C202" s="1"/>
+      <c r="D202" s="14"/>
+      <c r="E202" s="2"/>
+      <c r="F202" s="14"/>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A203" s="1"/>
+      <c r="B203" s="1"/>
+      <c r="C203" s="1"/>
+      <c r="D203" s="14"/>
+      <c r="E203" s="2"/>
+      <c r="F203" s="14"/>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A204" s="1"/>
+      <c r="B204" s="1"/>
+      <c r="C204" s="1"/>
+      <c r="D204" s="14"/>
+      <c r="E204" s="2"/>
+      <c r="F204" s="14"/>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A205" s="1"/>
+      <c r="B205" s="1"/>
+      <c r="C205" s="1"/>
+      <c r="D205" s="14"/>
+      <c r="E205" s="2"/>
+      <c r="F205" s="14"/>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A206" s="1"/>
+      <c r="B206" s="1"/>
+      <c r="C206" s="1"/>
+      <c r="D206" s="14"/>
+      <c r="E206" s="2"/>
+      <c r="F206" s="14"/>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A207" s="1"/>
+      <c r="B207" s="1"/>
+      <c r="C207" s="1"/>
+      <c r="D207" s="14"/>
+      <c r="E207" s="2"/>
+      <c r="F207" s="14"/>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A208" s="1"/>
+      <c r="B208" s="1"/>
+      <c r="C208" s="1"/>
+      <c r="D208" s="14"/>
+      <c r="E208" s="2"/>
+      <c r="F208" s="14"/>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A209" s="1"/>
+      <c r="B209" s="1"/>
+      <c r="C209" s="1"/>
+      <c r="D209" s="14"/>
+      <c r="E209" s="2"/>
+      <c r="F209" s="14"/>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A210" s="1"/>
+      <c r="B210" s="1"/>
+      <c r="C210" s="1"/>
+      <c r="D210" s="14"/>
+      <c r="E210" s="2"/>
+      <c r="F210" s="14"/>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A211" s="1"/>
+      <c r="B211" s="1"/>
+      <c r="C211" s="1"/>
+      <c r="D211" s="14"/>
+      <c r="E211" s="2"/>
+      <c r="F211" s="14"/>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A212" s="1"/>
+      <c r="B212" s="1"/>
+      <c r="C212" s="1"/>
+      <c r="D212" s="14"/>
+      <c r="E212" s="2"/>
+      <c r="F212" s="14"/>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A213" s="1"/>
+      <c r="B213" s="1"/>
+      <c r="C213" s="1"/>
+      <c r="D213" s="14"/>
+      <c r="E213" s="2"/>
+      <c r="F213" s="14"/>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A214" s="1"/>
+      <c r="B214" s="1"/>
+      <c r="C214" s="1"/>
+      <c r="D214" s="14"/>
+      <c r="E214" s="2"/>
+      <c r="F214" s="14"/>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A215" s="1"/>
+      <c r="B215" s="1"/>
+      <c r="C215" s="1"/>
+      <c r="D215" s="14"/>
+      <c r="E215" s="2"/>
+      <c r="F215" s="14"/>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A216" s="1"/>
+      <c r="B216" s="1"/>
+      <c r="C216" s="1"/>
+      <c r="D216" s="14"/>
+      <c r="E216" s="2"/>
+      <c r="F216" s="14"/>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A217" s="1"/>
+      <c r="B217" s="1"/>
+      <c r="C217" s="1"/>
+      <c r="D217" s="14"/>
+      <c r="E217" s="2"/>
+      <c r="F217" s="14"/>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A218" s="1"/>
+      <c r="B218" s="1"/>
+      <c r="C218" s="1"/>
+      <c r="D218" s="14"/>
+      <c r="E218" s="2"/>
+      <c r="F218" s="14"/>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A219" s="1"/>
+      <c r="B219" s="1"/>
+      <c r="C219" s="1"/>
+      <c r="D219" s="14"/>
+      <c r="E219" s="2"/>
+      <c r="F219" s="14"/>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A220" s="1"/>
+      <c r="B220" s="1"/>
+      <c r="C220" s="1"/>
+      <c r="D220" s="14"/>
+      <c r="E220" s="2"/>
+      <c r="F220" s="14"/>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A221" s="1"/>
+      <c r="B221" s="1"/>
+      <c r="C221" s="1"/>
+      <c r="D221" s="14"/>
+      <c r="E221" s="2"/>
+      <c r="F221" s="14"/>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A222" s="1"/>
+      <c r="B222" s="1"/>
+      <c r="C222" s="1"/>
+      <c r="D222" s="14"/>
+      <c r="E222" s="2"/>
+      <c r="F222" s="14"/>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A223" s="1"/>
+      <c r="B223" s="1"/>
+      <c r="C223" s="1"/>
+      <c r="D223" s="14"/>
+      <c r="E223" s="2"/>
+      <c r="F223" s="14"/>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A224" s="1"/>
+      <c r="B224" s="1"/>
+      <c r="C224" s="1"/>
+      <c r="D224" s="14"/>
+      <c r="E224" s="2"/>
+      <c r="F224" s="14"/>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A225" s="1"/>
+      <c r="B225" s="1"/>
+      <c r="C225" s="1"/>
+      <c r="D225" s="14"/>
+      <c r="E225" s="2"/>
+      <c r="F225" s="14"/>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A226" s="1"/>
+      <c r="B226" s="1"/>
+      <c r="C226" s="1"/>
+      <c r="D226" s="14"/>
+      <c r="E226" s="2"/>
+      <c r="F226" s="14"/>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A227" s="1"/>
+      <c r="B227" s="1"/>
+      <c r="C227" s="1"/>
+      <c r="D227" s="14"/>
+      <c r="E227" s="2"/>
+      <c r="F227" s="14"/>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A228" s="1"/>
+      <c r="B228" s="1"/>
+      <c r="C228" s="1"/>
+      <c r="D228" s="14"/>
+      <c r="E228" s="2"/>
+      <c r="F228" s="14"/>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A229" s="1"/>
+      <c r="B229" s="1"/>
+      <c r="C229" s="1"/>
+      <c r="D229" s="14"/>
+      <c r="E229" s="2"/>
+      <c r="F229" s="14"/>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A230" s="1"/>
+      <c r="B230" s="1"/>
+      <c r="C230" s="1"/>
+      <c r="D230" s="14"/>
+      <c r="E230" s="2"/>
+      <c r="F230" s="14"/>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A231" s="1"/>
+      <c r="B231" s="1"/>
+      <c r="C231" s="1"/>
+      <c r="D231" s="14"/>
+      <c r="E231" s="2"/>
+      <c r="F231" s="14"/>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A232" s="1"/>
+      <c r="B232" s="1"/>
+      <c r="C232" s="1"/>
+      <c r="D232" s="14"/>
+      <c r="E232" s="2"/>
+      <c r="F232" s="14"/>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A233" s="1"/>
+      <c r="B233" s="1"/>
+      <c r="C233" s="1"/>
+      <c r="D233" s="14"/>
+      <c r="E233" s="2"/>
+      <c r="F233" s="14"/>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A234" s="1"/>
+      <c r="B234" s="1"/>
+      <c r="C234" s="1"/>
+      <c r="D234" s="14"/>
+      <c r="E234" s="2"/>
+      <c r="F234" s="14"/>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A235" s="1"/>
+      <c r="B235" s="1"/>
+      <c r="C235" s="1"/>
+      <c r="D235" s="14"/>
+      <c r="E235" s="2"/>
+      <c r="F235" s="14"/>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A236" s="1"/>
+      <c r="B236" s="1"/>
+      <c r="C236" s="1"/>
+      <c r="D236" s="14"/>
+      <c r="E236" s="2"/>
+      <c r="F236" s="14"/>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A237" s="1"/>
+      <c r="B237" s="1"/>
+      <c r="C237" s="1"/>
+      <c r="D237" s="14"/>
+      <c r="E237" s="2"/>
+      <c r="F237" s="14"/>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A238" s="1"/>
+      <c r="B238" s="1"/>
+      <c r="C238" s="1"/>
+      <c r="D238" s="14"/>
+      <c r="E238" s="2"/>
+      <c r="F238" s="14"/>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A239" s="1"/>
+      <c r="B239" s="1"/>
+      <c r="C239" s="1"/>
+      <c r="D239" s="14"/>
+      <c r="E239" s="2"/>
+      <c r="F239" s="14"/>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A240" s="1"/>
+      <c r="B240" s="1"/>
+      <c r="C240" s="1"/>
+      <c r="D240" s="14"/>
+      <c r="E240" s="2"/>
+      <c r="F240" s="14"/>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A241" s="1"/>
+      <c r="B241" s="1"/>
+      <c r="C241" s="1"/>
+      <c r="D241" s="14"/>
+      <c r="E241" s="2"/>
+      <c r="F241" s="14"/>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A242" s="1"/>
+      <c r="B242" s="1"/>
+      <c r="C242" s="1"/>
+      <c r="D242" s="14"/>
+      <c r="E242" s="2"/>
+      <c r="F242" s="14"/>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A243" s="1"/>
+      <c r="B243" s="1"/>
+      <c r="C243" s="1"/>
+      <c r="D243" s="14"/>
+      <c r="E243" s="2"/>
+      <c r="F243" s="14"/>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A244" s="1"/>
+      <c r="B244" s="1"/>
+      <c r="C244" s="1"/>
+      <c r="D244" s="14"/>
+      <c r="E244" s="2"/>
+      <c r="F244" s="14"/>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A245" s="1"/>
+      <c r="B245" s="1"/>
+      <c r="C245" s="1"/>
+      <c r="D245" s="14"/>
+      <c r="E245" s="2"/>
+      <c r="F245" s="14"/>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A246" s="1"/>
+      <c r="B246" s="1"/>
+      <c r="C246" s="1"/>
+      <c r="D246" s="14"/>
+      <c r="E246" s="2"/>
+      <c r="F246" s="14"/>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A247" s="1"/>
+      <c r="B247" s="1"/>
+      <c r="C247" s="1"/>
+      <c r="D247" s="14"/>
+      <c r="E247" s="2"/>
+      <c r="F247" s="14"/>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A248" s="1"/>
+      <c r="B248" s="1"/>
+      <c r="C248" s="1"/>
+      <c r="D248" s="14"/>
+      <c r="E248" s="2"/>
+      <c r="F248" s="14"/>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A249" s="1"/>
+      <c r="B249" s="1"/>
+      <c r="C249" s="1"/>
+      <c r="D249" s="14"/>
+      <c r="E249" s="2"/>
+      <c r="F249" s="14"/>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A250" s="1"/>
+      <c r="B250" s="1"/>
+      <c r="C250" s="1"/>
+      <c r="D250" s="14"/>
+      <c r="E250" s="2"/>
+      <c r="F250" s="14"/>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A251" s="1"/>
+      <c r="B251" s="1"/>
+      <c r="C251" s="1"/>
+      <c r="D251" s="14"/>
+      <c r="E251" s="2"/>
+      <c r="F251" s="14"/>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A252" s="1"/>
+      <c r="B252" s="1"/>
+      <c r="C252" s="1"/>
+      <c r="D252" s="14"/>
+      <c r="E252" s="2"/>
+      <c r="F252" s="14"/>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A253" s="1"/>
+      <c r="B253" s="1"/>
+      <c r="C253" s="1"/>
+      <c r="D253" s="14"/>
+      <c r="E253" s="2"/>
+      <c r="F253" s="14"/>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A254" s="1"/>
+      <c r="B254" s="1"/>
+      <c r="C254" s="1"/>
+      <c r="D254" s="14"/>
+      <c r="E254" s="2"/>
+      <c r="F254" s="14"/>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A255" s="1"/>
+      <c r="B255" s="1"/>
+      <c r="C255" s="1"/>
+      <c r="D255" s="14"/>
+      <c r="E255" s="2"/>
+      <c r="F255" s="14"/>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A256" s="1"/>
+      <c r="B256" s="1"/>
+      <c r="C256" s="1"/>
+      <c r="D256" s="14"/>
+      <c r="E256" s="2"/>
+      <c r="F256" s="14"/>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A257" s="1"/>
+      <c r="B257" s="1"/>
+      <c r="C257" s="1"/>
+      <c r="D257" s="14"/>
+      <c r="E257" s="2"/>
+      <c r="F257" s="14"/>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A258" s="1"/>
+      <c r="B258" s="1"/>
+      <c r="C258" s="1"/>
+      <c r="D258" s="14"/>
+      <c r="E258" s="2"/>
+      <c r="F258" s="14"/>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A259" s="1"/>
+      <c r="B259" s="1"/>
+      <c r="C259" s="1"/>
+      <c r="D259" s="14"/>
+      <c r="E259" s="2"/>
+      <c r="F259" s="14"/>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A260" s="1"/>
+      <c r="B260" s="1"/>
+      <c r="C260" s="1"/>
+      <c r="D260" s="14"/>
+      <c r="E260" s="2"/>
+      <c r="F260" s="14"/>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A261" s="1"/>
+      <c r="B261" s="1"/>
+      <c r="C261" s="1"/>
+      <c r="D261" s="14"/>
+      <c r="E261" s="2"/>
+      <c r="F261" s="14"/>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A262" s="1"/>
+      <c r="B262" s="1"/>
+      <c r="C262" s="1"/>
+      <c r="D262" s="14"/>
+      <c r="E262" s="2"/>
+      <c r="F262" s="14"/>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A263" s="1"/>
+      <c r="B263" s="1"/>
+      <c r="C263" s="1"/>
+      <c r="D263" s="14"/>
+      <c r="E263" s="2"/>
+      <c r="F263" s="14"/>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A264" s="1"/>
+      <c r="B264" s="1"/>
+      <c r="C264" s="1"/>
+      <c r="D264" s="14"/>
+      <c r="E264" s="2"/>
+      <c r="F264" s="14"/>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A265" s="1"/>
+      <c r="B265" s="1"/>
+      <c r="C265" s="1"/>
+      <c r="D265" s="14"/>
+      <c r="E265" s="2"/>
+      <c r="F265" s="14"/>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A266" s="1"/>
+      <c r="B266" s="1"/>
+      <c r="C266" s="1"/>
+      <c r="D266" s="14"/>
+      <c r="E266" s="2"/>
+      <c r="F266" s="14"/>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A267" s="1"/>
+      <c r="B267" s="1"/>
+      <c r="C267" s="1"/>
+      <c r="D267" s="14"/>
+      <c r="E267" s="2"/>
+      <c r="F267" s="14"/>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A268" s="1"/>
+      <c r="B268" s="1"/>
+      <c r="C268" s="1"/>
+      <c r="D268" s="14"/>
+      <c r="E268" s="2"/>
+      <c r="F268" s="14"/>
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A269" s="1"/>
+      <c r="B269" s="1"/>
+      <c r="C269" s="1"/>
+      <c r="D269" s="14"/>
+      <c r="E269" s="2"/>
+      <c r="F269" s="14"/>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A270" s="1"/>
+      <c r="B270" s="1"/>
+      <c r="C270" s="1"/>
+      <c r="D270" s="14"/>
+      <c r="E270" s="2"/>
+      <c r="F270" s="14"/>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A271" s="1"/>
+      <c r="B271" s="1"/>
+      <c r="C271" s="1"/>
+      <c r="D271" s="14"/>
+      <c r="E271" s="2"/>
+      <c r="F271" s="14"/>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A272" s="1"/>
+      <c r="B272" s="1"/>
+      <c r="C272" s="1"/>
+      <c r="D272" s="14"/>
+      <c r="E272" s="2"/>
+      <c r="F272" s="14"/>
+    </row>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A273" s="1"/>
+      <c r="B273" s="1"/>
+      <c r="C273" s="1"/>
+      <c r="D273" s="14"/>
+      <c r="E273" s="2"/>
+      <c r="F273" s="14"/>
+    </row>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A274" s="1"/>
+      <c r="B274" s="1"/>
+      <c r="C274" s="1"/>
+      <c r="D274" s="14"/>
+      <c r="E274" s="2"/>
+      <c r="F274" s="14"/>
+    </row>
+    <row r="275" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A275" s="1"/>
+      <c r="B275" s="1"/>
+      <c r="C275" s="1"/>
+      <c r="D275" s="14"/>
+      <c r="E275" s="2"/>
+      <c r="F275" s="14"/>
+    </row>
+    <row r="276" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A276" s="1"/>
+      <c r="B276" s="1"/>
+      <c r="C276" s="1"/>
+      <c r="D276" s="14"/>
+      <c r="E276" s="2"/>
+      <c r="F276" s="14"/>
+    </row>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A277" s="1"/>
+      <c r="B277" s="1"/>
+      <c r="C277" s="1"/>
+      <c r="D277" s="14"/>
+      <c r="E277" s="2"/>
+      <c r="F277" s="14"/>
+    </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A278" s="1"/>
+      <c r="B278" s="1"/>
+      <c r="C278" s="1"/>
+      <c r="D278" s="14"/>
+      <c r="E278" s="2"/>
+      <c r="F278" s="14"/>
+    </row>
+    <row r="279" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A279" s="1"/>
+      <c r="B279" s="1"/>
+      <c r="C279" s="1"/>
+      <c r="D279" s="14"/>
+      <c r="E279" s="2"/>
+      <c r="F279" s="14"/>
+    </row>
+    <row r="280" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A280" s="1"/>
+      <c r="B280" s="1"/>
+      <c r="C280" s="1"/>
+      <c r="D280" s="14"/>
+      <c r="E280" s="2"/>
+      <c r="F280" s="14"/>
+    </row>
+    <row r="281" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A281" s="1"/>
+      <c r="B281" s="1"/>
+      <c r="C281" s="1"/>
+      <c r="D281" s="14"/>
+      <c r="E281" s="2"/>
+      <c r="F281" s="14"/>
+    </row>
+    <row r="282" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A282" s="1"/>
+      <c r="B282" s="1"/>
+      <c r="C282" s="1"/>
+      <c r="D282" s="14"/>
+      <c r="E282" s="2"/>
+      <c r="F282" s="14"/>
+    </row>
+    <row r="283" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A283" s="1"/>
+      <c r="B283" s="1"/>
+      <c r="C283" s="1"/>
+      <c r="D283" s="14"/>
+      <c r="E283" s="2"/>
+      <c r="F283" s="14"/>
+    </row>
+    <row r="284" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A284" s="1"/>
+      <c r="B284" s="1"/>
+      <c r="C284" s="1"/>
+      <c r="D284" s="14"/>
+      <c r="E284" s="2"/>
+      <c r="F284" s="14"/>
+    </row>
+    <row r="285" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A285" s="1"/>
+      <c r="B285" s="1"/>
+      <c r="C285" s="1"/>
+      <c r="D285" s="14"/>
+      <c r="E285" s="2"/>
+      <c r="F285" s="14"/>
+    </row>
+    <row r="286" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A286" s="1"/>
+      <c r="B286" s="1"/>
+      <c r="C286" s="1"/>
+      <c r="D286" s="14"/>
+      <c r="E286" s="2"/>
+      <c r="F286" s="14"/>
+    </row>
+    <row r="287" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A287" s="1"/>
+      <c r="B287" s="1"/>
+      <c r="C287" s="1"/>
+      <c r="D287" s="14"/>
+      <c r="E287" s="2"/>
+      <c r="F287" s="14"/>
+    </row>
+    <row r="288" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A288" s="1"/>
+      <c r="B288" s="1"/>
+      <c r="C288" s="1"/>
+      <c r="D288" s="14"/>
+      <c r="E288" s="2"/>
+      <c r="F288" s="14"/>
+    </row>
+    <row r="289" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A289" s="1"/>
+      <c r="B289" s="1"/>
+      <c r="C289" s="1"/>
+      <c r="D289" s="14"/>
+      <c r="E289" s="2"/>
+      <c r="F289" s="14"/>
+    </row>
+    <row r="290" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A290" s="1"/>
+      <c r="B290" s="1"/>
+      <c r="C290" s="1"/>
+      <c r="D290" s="14"/>
+      <c r="E290" s="2"/>
+      <c r="F290" s="14"/>
+    </row>
+    <row r="291" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A291" s="1"/>
+      <c r="B291" s="1"/>
+      <c r="C291" s="1"/>
+      <c r="D291" s="14"/>
+      <c r="E291" s="2"/>
+      <c r="F291" s="14"/>
+    </row>
+    <row r="292" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A292" s="1"/>
+      <c r="B292" s="1"/>
+      <c r="C292" s="1"/>
+      <c r="D292" s="14"/>
+      <c r="E292" s="2"/>
+      <c r="F292" s="14"/>
+    </row>
+    <row r="293" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A293" s="1"/>
+      <c r="B293" s="1"/>
+      <c r="C293" s="1"/>
+      <c r="D293" s="14"/>
+      <c r="E293" s="2"/>
+      <c r="F293" s="14"/>
+    </row>
+    <row r="294" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A294" s="1"/>
+      <c r="B294" s="1"/>
+      <c r="C294" s="1"/>
+      <c r="D294" s="14"/>
+      <c r="E294" s="2"/>
+      <c r="F294" s="14"/>
+    </row>
+    <row r="295" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A295" s="1"/>
+      <c r="B295" s="1"/>
+      <c r="C295" s="1"/>
+      <c r="D295" s="14"/>
+      <c r="E295" s="2"/>
+      <c r="F295" s="14"/>
+    </row>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A296" s="1"/>
+      <c r="B296" s="1"/>
+      <c r="C296" s="1"/>
+      <c r="D296" s="14"/>
+      <c r="E296" s="2"/>
+      <c r="F296" s="14"/>
+    </row>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A297" s="1"/>
+      <c r="B297" s="1"/>
+      <c r="C297" s="1"/>
+      <c r="D297" s="14"/>
+      <c r="E297" s="2"/>
+      <c r="F297" s="14"/>
+    </row>
+    <row r="298" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A298" s="1"/>
+      <c r="B298" s="1"/>
+      <c r="C298" s="1"/>
+      <c r="D298" s="14"/>
+      <c r="E298" s="2"/>
+      <c r="F298" s="14"/>
+    </row>
+    <row r="299" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A299" s="1"/>
+      <c r="B299" s="1"/>
+      <c r="C299" s="1"/>
+      <c r="D299" s="14"/>
+      <c r="E299" s="2"/>
+      <c r="F299" s="14"/>
+    </row>
+    <row r="300" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A300" s="1"/>
+      <c r="B300" s="1"/>
+      <c r="C300" s="1"/>
+      <c r="D300" s="14"/>
+      <c r="E300" s="2"/>
+      <c r="F300" s="14"/>
+    </row>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A301" s="1"/>
+      <c r="B301" s="1"/>
+      <c r="C301" s="1"/>
+      <c r="D301" s="14"/>
+      <c r="E301" s="2"/>
+      <c r="F301" s="14"/>
+    </row>
+    <row r="302" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A302" s="1"/>
+      <c r="B302" s="1"/>
+      <c r="C302" s="1"/>
+      <c r="D302" s="14"/>
+      <c r="E302" s="2"/>
+      <c r="F302" s="14"/>
+    </row>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A303" s="1"/>
+      <c r="B303" s="1"/>
+      <c r="C303" s="1"/>
+      <c r="D303" s="14"/>
+      <c r="E303" s="2"/>
+      <c r="F303" s="14"/>
+    </row>
+    <row r="304" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A304" s="1"/>
+      <c r="B304" s="1"/>
+      <c r="C304" s="1"/>
+      <c r="D304" s="14"/>
+      <c r="E304" s="2"/>
+      <c r="F304" s="14"/>
+    </row>
+    <row r="305" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A305" s="1"/>
+      <c r="B305" s="1"/>
+      <c r="C305" s="1"/>
+      <c r="D305" s="14"/>
+      <c r="E305" s="2"/>
+      <c r="F305" s="14"/>
+    </row>
+    <row r="306" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A306" s="1"/>
+      <c r="B306" s="1"/>
+      <c r="C306" s="1"/>
+      <c r="D306" s="14"/>
+      <c r="E306" s="2"/>
+      <c r="F306" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
